--- a/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
+++ b/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\nagar bhaipari and estimate misc\hawa huri jhyal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{276E0937-9F04-4223-B03E-361861839426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB31C8EF-E4EE-44A3-B027-2521CF3604FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="212">
   <si>
     <t>S.N.</t>
   </si>
@@ -1020,6 +1020,9 @@
   </si>
   <si>
     <t>Date: 2083/03/18</t>
+  </si>
+  <si>
+    <t>Detail Valuated Sheet</t>
   </si>
 </sst>
 </file>
@@ -3572,6 +3575,21 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3588,21 +3606,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -6891,7 +6894,7 @@
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="184" t="s">
-        <v>22</v>
+        <v>211</v>
       </c>
       <c r="B4" s="184"/>
       <c r="C4" s="184"/>
@@ -7744,7 +7747,7 @@
       <c r="I43" s="129"/>
       <c r="J43" s="130"/>
       <c r="K43" s="150">
-        <f>SUM(K9:K42)</f>
+        <f>SUM(K10:K42)</f>
         <v>48124.74305248</v>
       </c>
       <c r="L43" s="151"/>
@@ -8759,60 +8762,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="193" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="188"/>
-      <c r="H1" s="188"/>
-      <c r="I1" s="188"/>
-      <c r="J1" s="188"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="193"/>
+      <c r="J1" s="193"/>
     </row>
     <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="194" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
+      <c r="B2" s="194"/>
+      <c r="C2" s="194"/>
+      <c r="D2" s="194"/>
+      <c r="E2" s="194"/>
+      <c r="F2" s="194"/>
+      <c r="G2" s="194"/>
+      <c r="H2" s="194"/>
+      <c r="I2" s="194"/>
+      <c r="J2" s="194"/>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="190" t="s">
+      <c r="A3" s="195" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
+      <c r="B3" s="195"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="195"/>
+      <c r="F3" s="195"/>
+      <c r="G3" s="195"/>
+      <c r="H3" s="195"/>
+      <c r="I3" s="195"/>
+      <c r="J3" s="195"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="196" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
+      <c r="B4" s="196"/>
+      <c r="C4" s="196"/>
+      <c r="D4" s="196"/>
+      <c r="E4" s="196"/>
+      <c r="F4" s="196"/>
+      <c r="G4" s="196"/>
+      <c r="H4" s="196"/>
+      <c r="I4" s="196"/>
+      <c r="J4" s="196"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -8831,33 +8834,33 @@
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="192" t="e">
+      <c r="C6" s="197" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="193"/>
+      <c r="D6" s="198"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="192" t="e">
+      <c r="I6" s="197" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="193"/>
+      <c r="J6" s="198"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="H7" s="195"/>
-      <c r="I7" s="195"/>
-      <c r="J7" s="195"/>
+      <c r="C7" s="188"/>
+      <c r="D7" s="188"/>
+      <c r="E7" s="188"/>
+      <c r="F7" s="188"/>
+      <c r="H7" s="189"/>
+      <c r="I7" s="189"/>
+      <c r="J7" s="189"/>
     </row>
     <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
@@ -8884,32 +8887,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="190" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="196" t="s">
+      <c r="B10" s="190" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="198" t="s">
+      <c r="C10" s="192" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="198"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="198" t="s">
+      <c r="D10" s="192"/>
+      <c r="E10" s="192"/>
+      <c r="F10" s="192" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="198"/>
-      <c r="H10" s="198"/>
-      <c r="I10" s="196" t="s">
+      <c r="G10" s="192"/>
+      <c r="H10" s="192"/>
+      <c r="I10" s="190" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="196" t="s">
+      <c r="J10" s="190" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
+      <c r="A11" s="191"/>
+      <c r="B11" s="191"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -8928,8 +8931,8 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
+      <c r="I11" s="191"/>
+      <c r="J11" s="191"/>
     </row>
     <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="47">
@@ -9856,6 +9859,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -9865,12 +9874,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -13251,6 +13254,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="D160:E160"/>
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="A1:L1"/>
@@ -13258,13 +13268,6 @@
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="D161:E161"/>
-    <mergeCell ref="D162:E162"/>
-    <mergeCell ref="D156:E156"/>
-    <mergeCell ref="D157:E157"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="D160:E160"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
+++ b/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\nagar bhaipari and estimate misc\hawa huri jhyal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB31C8EF-E4EE-44A3-B027-2521CF3604FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AD889A-6D46-4AAA-8E38-E785376CEB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -132,7 +132,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="213">
   <si>
     <t>S.N.</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>Detail Valuated Sheet</t>
+  </si>
+  <si>
+    <t>Total Valuated</t>
   </si>
 </sst>
 </file>
@@ -3575,6 +3578,24 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3588,24 +3609,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -7686,11 +7689,11 @@
         <v>163</v>
       </c>
       <c r="J40" s="178">
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="K40" s="178">
         <f>H40*J40</f>
-        <v>25000</v>
+        <v>26000</v>
       </c>
       <c r="L40" s="179"/>
     </row>
@@ -7748,7 +7751,7 @@
       <c r="J43" s="130"/>
       <c r="K43" s="150">
         <f>SUM(K10:K42)</f>
-        <v>48124.74305248</v>
+        <v>49124.74305248</v>
       </c>
       <c r="L43" s="151"/>
     </row>
@@ -7766,11 +7769,11 @@
     </row>
     <row r="45" spans="2:12">
       <c r="C45" s="134" t="s">
-        <v>13</v>
+        <v>212</v>
       </c>
       <c r="D45" s="180">
         <f>+K43</f>
-        <v>48124.74305248</v>
+        <v>49124.74305248</v>
       </c>
       <c r="E45" s="180"/>
       <c r="G45" s="64"/>
@@ -7783,7 +7786,7 @@
       </c>
       <c r="D46" s="180">
         <f>13%*D45</f>
-        <v>6256.2165968223999</v>
+        <v>6386.2165968223999</v>
       </c>
       <c r="E46" s="180"/>
       <c r="G46" s="64"/>
@@ -7796,7 +7799,7 @@
       </c>
       <c r="D47" s="180">
         <f>SUM(D45:E46)</f>
-        <v>54380.9596493024</v>
+        <v>55510.9596493024</v>
       </c>
       <c r="E47" s="181"/>
       <c r="G47" s="62"/>
@@ -8762,60 +8765,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="193" t="s">
+      <c r="A1" s="188" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="193"/>
-      <c r="C1" s="193"/>
-      <c r="D1" s="193"/>
-      <c r="E1" s="193"/>
-      <c r="F1" s="193"/>
-      <c r="G1" s="193"/>
-      <c r="H1" s="193"/>
-      <c r="I1" s="193"/>
-      <c r="J1" s="193"/>
+      <c r="B1" s="188"/>
+      <c r="C1" s="188"/>
+      <c r="D1" s="188"/>
+      <c r="E1" s="188"/>
+      <c r="F1" s="188"/>
+      <c r="G1" s="188"/>
+      <c r="H1" s="188"/>
+      <c r="I1" s="188"/>
+      <c r="J1" s="188"/>
     </row>
     <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="194" t="s">
+      <c r="A2" s="189" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="194"/>
-      <c r="C2" s="194"/>
-      <c r="D2" s="194"/>
-      <c r="E2" s="194"/>
-      <c r="F2" s="194"/>
-      <c r="G2" s="194"/>
-      <c r="H2" s="194"/>
-      <c r="I2" s="194"/>
-      <c r="J2" s="194"/>
+      <c r="B2" s="189"/>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
+      <c r="I2" s="189"/>
+      <c r="J2" s="189"/>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="195" t="s">
+      <c r="A3" s="190" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="195"/>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="195"/>
-      <c r="F3" s="195"/>
-      <c r="G3" s="195"/>
-      <c r="H3" s="195"/>
-      <c r="I3" s="195"/>
-      <c r="J3" s="195"/>
+      <c r="B3" s="190"/>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+      <c r="I3" s="190"/>
+      <c r="J3" s="190"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="196" t="s">
+      <c r="A4" s="191" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="196"/>
-      <c r="C4" s="196"/>
-      <c r="D4" s="196"/>
-      <c r="E4" s="196"/>
-      <c r="F4" s="196"/>
-      <c r="G4" s="196"/>
-      <c r="H4" s="196"/>
-      <c r="I4" s="196"/>
-      <c r="J4" s="196"/>
+      <c r="B4" s="191"/>
+      <c r="C4" s="191"/>
+      <c r="D4" s="191"/>
+      <c r="E4" s="191"/>
+      <c r="F4" s="191"/>
+      <c r="G4" s="191"/>
+      <c r="H4" s="191"/>
+      <c r="I4" s="191"/>
+      <c r="J4" s="191"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -8834,33 +8837,33 @@
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="197" t="e">
+      <c r="C6" s="192" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="198"/>
+      <c r="D6" s="193"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="197" t="e">
+      <c r="I6" s="192" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="198"/>
+      <c r="J6" s="193"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="188"/>
-      <c r="D7" s="188"/>
-      <c r="E7" s="188"/>
-      <c r="F7" s="188"/>
-      <c r="H7" s="189"/>
-      <c r="I7" s="189"/>
-      <c r="J7" s="189"/>
+      <c r="C7" s="194"/>
+      <c r="D7" s="194"/>
+      <c r="E7" s="194"/>
+      <c r="F7" s="194"/>
+      <c r="H7" s="195"/>
+      <c r="I7" s="195"/>
+      <c r="J7" s="195"/>
     </row>
     <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
@@ -8887,32 +8890,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="190" t="s">
+      <c r="A10" s="196" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="190" t="s">
+      <c r="B10" s="196" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="192" t="s">
+      <c r="C10" s="198" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="192"/>
-      <c r="E10" s="192"/>
-      <c r="F10" s="192" t="s">
+      <c r="D10" s="198"/>
+      <c r="E10" s="198"/>
+      <c r="F10" s="198" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="192"/>
-      <c r="H10" s="192"/>
-      <c r="I10" s="190" t="s">
+      <c r="G10" s="198"/>
+      <c r="H10" s="198"/>
+      <c r="I10" s="196" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="190" t="s">
+      <c r="J10" s="196" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="191"/>
-      <c r="B11" s="191"/>
+      <c r="A11" s="197"/>
+      <c r="B11" s="197"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -8931,8 +8934,8 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="191"/>
-      <c r="J11" s="191"/>
+      <c r="I11" s="197"/>
+      <c r="J11" s="197"/>
     </row>
     <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="47">
@@ -9859,12 +9862,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -9874,6 +9871,12 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -13254,6 +13257,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K5:L5"/>
     <mergeCell ref="D161:E161"/>
     <mergeCell ref="D162:E162"/>
     <mergeCell ref="D156:E156"/>
@@ -13261,13 +13271,6 @@
     <mergeCell ref="D158:E158"/>
     <mergeCell ref="D159:E159"/>
     <mergeCell ref="D160:E160"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="A2:L2"/>
-    <mergeCell ref="A3:L3"/>
-    <mergeCell ref="A4:L4"/>
-    <mergeCell ref="K5:L5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
+++ b/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\nagar bhaipari and estimate misc\hawa huri jhyal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74AD889A-6D46-4AAA-8E38-E785376CEB9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33154DA-5074-42ED-8C38-5B287369D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="8" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTIMATE" sheetId="25" state="hidden" r:id="rId1"/>
@@ -21,39 +21,79 @@
     <sheet name="&lt;1000000 (2)" sheetId="32" state="hidden" r:id="rId6"/>
     <sheet name="&lt;1000000 (3)" sheetId="33" state="hidden" r:id="rId7"/>
     <sheet name="square hisaab" sheetId="36" state="hidden" r:id="rId8"/>
-    <sheet name="Sheet4" sheetId="37" r:id="rId9"/>
-    <sheet name="V (2)" sheetId="38" r:id="rId10"/>
-    <sheet name="&lt;1000000 (4)" sheetId="34" state="hidden" r:id="rId11"/>
-    <sheet name="&lt;1000000 (5)" sheetId="35" state="hidden" r:id="rId12"/>
+    <sheet name="Sheet4" sheetId="37" state="hidden" r:id="rId9"/>
+    <sheet name="V (2)" sheetId="38" state="hidden" r:id="rId10"/>
+    <sheet name="E" sheetId="39" r:id="rId11"/>
+    <sheet name="WCR (2)" sheetId="42" r:id="rId12"/>
+    <sheet name="V" sheetId="40" r:id="rId13"/>
+    <sheet name="M" sheetId="43" r:id="rId14"/>
+    <sheet name="&lt;1000000 (4)" sheetId="34" state="hidden" r:id="rId15"/>
+    <sheet name="&lt;1000000 (5)" sheetId="35" state="hidden" r:id="rId16"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId13"/>
-    <externalReference r:id="rId14"/>
-    <externalReference r:id="rId15"/>
+    <externalReference r:id="rId17"/>
+    <externalReference r:id="rId18"/>
+    <externalReference r:id="rId19"/>
+    <externalReference r:id="rId20"/>
+    <externalReference r:id="rId21"/>
+    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
+    <externalReference r:id="rId25"/>
+    <externalReference r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="cheskini100">'[1]update Rate'!$O$64</definedName>
+    <definedName name="description_103">[4]Abstract!$B$16</definedName>
+    <definedName name="description_124" localSheetId="11">#REF!</definedName>
+    <definedName name="description_124">#REF!</definedName>
+    <definedName name="description_247">[4]Abstract!$B$22</definedName>
+    <definedName name="description_248">[4]Abstract!$B$23</definedName>
+    <definedName name="description_261">[6]Abstract!$B$33</definedName>
+    <definedName name="description_262">[4]Abstract!$B$34</definedName>
+    <definedName name="description_276">[7]Abstract!$B$40</definedName>
+    <definedName name="description_3">[4]Abstract!$B$169</definedName>
+    <definedName name="description_310" localSheetId="11">[8]Abstract!$B$60</definedName>
+    <definedName name="description_310">#REF!</definedName>
+    <definedName name="description_312" localSheetId="11">[9]Abstract!$B$61</definedName>
+    <definedName name="description_312">#REF!</definedName>
+    <definedName name="description_5">[4]Abstract!$B$171</definedName>
+    <definedName name="description_6" localSheetId="11">[8]Abstract!$B$172</definedName>
+    <definedName name="description_6">#REF!</definedName>
+    <definedName name="description_759">[4]Abstract!$B$278</definedName>
+    <definedName name="description_781" localSheetId="11">[10]Abstract!$B$299</definedName>
+    <definedName name="description_781">#REF!</definedName>
+    <definedName name="description_783">[4]Abstract!$B$301</definedName>
+    <definedName name="description_784">[7]Abstract!$B$300</definedName>
     <definedName name="glass4">'[1]update Rate'!$O$88</definedName>
     <definedName name="kabja75">'[1]update Rate'!$O$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'&lt;1000000'!$A$1:$L$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'&lt;1000000 (2)'!$A$1:$L$33</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'&lt;1000000 (3)'!$A$1:$L$19</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'&lt;1000000 (4)'!$A$1:$L$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'&lt;1000000 (5)'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'&lt;1000000 (4)'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'&lt;1000000 (5)'!$A$1:$L$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">E!$A$1:$L$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">ESTIMATE!$A$1:$L$71</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="13">M!$A$1:$L$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">me!$A$1:$L$162</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'square hisaab'!$A$1:$L$39</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">V!$A$1:$L$45</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="9">'V (2)'!$A$1:$L$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'WCR (2)'!$A$1:$K$39</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'&lt;1000000'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'&lt;1000000 (2)'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'&lt;1000000 (3)'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="10">'&lt;1000000 (4)'!$1:$8</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="11">'&lt;1000000 (5)'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="14">'&lt;1000000 (4)'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="15">'&lt;1000000 (5)'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">E!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">ESTIMATE!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="13">M!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">me!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'square hisaab'!$1:$8</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="12">V!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="9">'V (2)'!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">WCR!$1:$11</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="11">'WCR (2)'!$1:$12</definedName>
     <definedName name="shandle">'[1]update Rate'!$O$92</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -132,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="750" uniqueCount="225">
   <si>
     <t>S.N.</t>
   </si>
@@ -1027,6 +1067,51 @@
   <si>
     <t>Total Valuated</t>
   </si>
+  <si>
+    <t>Detail Estimated Sheet</t>
+  </si>
+  <si>
+    <t>Bagmati Province</t>
+  </si>
+  <si>
+    <t>Total Estimated Amount:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Started : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Work Finished:           </t>
+  </si>
+  <si>
+    <t xml:space="preserve">F.Y:2082/2083            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date:2083/03/24      </t>
+  </si>
+  <si>
+    <r>
+      <t>Project:-</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="Preeti"/>
+      </rPr>
+      <t>lalaw ‰ofn9f]sf dd{t sfo{ j8f sfof{no</t>
+    </r>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Date: 2083/03/24</t>
+  </si>
+  <si>
+    <t>Detail Quantity Measurement Sheet</t>
+  </si>
+  <si>
+    <t>Date: 2083/03/05</t>
+  </si>
 </sst>
 </file>
 
@@ -1055,7 +1140,7 @@
     <numFmt numFmtId="181" formatCode="_ &quot;\&quot;* #,##0.00_ ;_ &quot;\&quot;* \-#,##0.00_ ;_ &quot;\&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="182" formatCode="0.0"/>
   </numFmts>
-  <fonts count="96">
+  <fonts count="97">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1608,6 +1693,13 @@
       <sz val="12"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
@@ -3111,7 +3203,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="211">
+  <cellXfs count="237">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3556,6 +3648,12 @@
     <xf numFmtId="0" fontId="52" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3647,6 +3745,68 @@
     <xf numFmtId="0" fontId="82" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="182" fontId="52" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="60" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="59" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="65" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="2" fontId="59" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="59" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="759">
     <cellStyle name="??" xfId="476" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4666,6 +4826,65 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1">
+        <row r="299">
+          <cell r="B299" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:4 in Foundation complete as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -4858,6 +5077,371 @@
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Clearing and Grubbing Road Land ., Clearing and grubbing road land including uprooting rank vegetation, grass, bushes, shrubs, saplings and trees girth up to 300 mm, removal of stumps of trees cut earlier and disposal of unserviceable materials and stacking of serviceable Material to be used or auctioned, up to a lead of 30 meters including removal and disposal of top organic soil not exceeding 150 mm in thickness., By Mechanical Means, In area of light jungle (less than 15 number per 100 sqm )</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 450 mm  internal dia.</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 600 mm  internal dia.</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Mechanical  Means ., Road way Excavation in  all types of soil as per Drawing and technical specifications  including  removal of stumps and other deleterious matter, all lifts and lead as per Drawing and instruction of the Engineer.</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="B169" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="B171" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 20</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="B278" t="str">
+            <v>Providing and laying Brick Masonry Work in Cement mortar  in Foundation / structure complete excluding Pointing and Plastering, as per Drawing and Technical Specifications., Cement sand mortar (1:6)</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="B301" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="estimate"/>
+      <sheetName val="WCR"/>
+      <sheetName val="V"/>
+      <sheetName val="M"/>
+      <sheetName val="original estimate"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Manual Means ., Roadway Excavation in all types of soil as per drawing and technical specification, including removal of stumps and other deleterious matter, with all lifts and lead as per Drawing and instruction of the Engineer.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Excavation for Structures Foundation, Earth work in excavation of foundation of structures, including  construction of shoring and bracing, removal of stumps and other deleterious matter and backfilling with approved Material as per Drawing and Technical Specifications., Ordinary soil by Mechanical Means, Depth upto 3 m</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="B300" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications., Using Concrete Mixer</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>Providing and laying of hand pack Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="B172" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Providing and laying  granular sub-base   on prepared surface, mixing  at OMC, and compacting  to achieve the desired density, complete as per Drawing and Technical Specifications., By Mechanical means</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5177,68 +5761,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:18" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:18" ht="19.5">
       <c r="A5" s="6"/>
@@ -5249,33 +5833,33 @@
         <v>93</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
-      <c r="O6" s="187" t="s">
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+      <c r="O6" s="189" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="187"/>
-      <c r="Q6" s="187"/>
-      <c r="R6" s="187"/>
+      <c r="P6" s="189"/>
+      <c r="Q6" s="189"/>
+      <c r="R6" s="189"/>
     </row>
     <row r="7" spans="1:18" ht="17.25" thickBot="1">
       <c r="C7" s="5"/>
@@ -6848,68 +7432,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:14" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
       <c r="A5" s="6"/>
@@ -6917,27 +7501,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:14">
       <c r="C7" s="5"/>
@@ -7771,11 +8355,11 @@
       <c r="C45" s="134" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="180">
+      <c r="D45" s="182">
         <f>+K43</f>
         <v>49124.74305248</v>
       </c>
-      <c r="E45" s="180"/>
+      <c r="E45" s="182"/>
       <c r="G45" s="64"/>
       <c r="I45" s="2"/>
       <c r="J45" s="1"/>
@@ -7784,11 +8368,11 @@
       <c r="C46" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D46" s="180">
+      <c r="D46" s="182">
         <f>13%*D45</f>
         <v>6386.2165968223999</v>
       </c>
-      <c r="E46" s="180"/>
+      <c r="E46" s="182"/>
       <c r="G46" s="64"/>
       <c r="I46" s="2"/>
       <c r="J46" s="1"/>
@@ -7797,11 +8381,11 @@
       <c r="C47" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="180">
+      <c r="D47" s="182">
         <f>SUM(D45:E46)</f>
         <v>55510.9596493024</v>
       </c>
-      <c r="E47" s="181"/>
+      <c r="E47" s="183"/>
       <c r="G47" s="62"/>
     </row>
   </sheetData>
@@ -7828,6 +8412,3925 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFBC4F36-8D5C-49D5-9BE3-AC0D9062A769}">
+  <dimension ref="A1:N45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+    </row>
+    <row r="2" spans="1:14" ht="20.25">
+      <c r="A2" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="186" t="s">
+        <v>213</v>
+      </c>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="158" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="K5" s="187" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="187"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="189" t="s">
+        <v>224</v>
+      </c>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2"/>
+      <c r="B8" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="154" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="156" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="154" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="157" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="155">
+        <v>1</v>
+      </c>
+      <c r="C9" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="155"/>
+      <c r="C10" s="132" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="143">
+        <v>5</v>
+      </c>
+      <c r="E10" s="130">
+        <f>1.1*2+0.53*3</f>
+        <v>3.79</v>
+      </c>
+      <c r="F10" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G10" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H10" s="130">
+        <f>PRODUCT(D10:G10)</f>
+        <v>4.2448E-2</v>
+      </c>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="131"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="155"/>
+      <c r="C11" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="143">
+        <v>1</v>
+      </c>
+      <c r="E11" s="130">
+        <f>1.2*2+0.44*2</f>
+        <v>3.28</v>
+      </c>
+      <c r="F11" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G11" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H11" s="130">
+        <f t="shared" ref="H11:H12" si="0">PRODUCT(D11:G11)</f>
+        <v>7.3471999999999999E-3</v>
+      </c>
+      <c r="I11" s="129"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="131"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="155"/>
+      <c r="C12" s="132" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="143">
+        <v>2</v>
+      </c>
+      <c r="E12" s="130">
+        <f>0.53*2+1.07*2</f>
+        <v>3.2</v>
+      </c>
+      <c r="F12" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G12" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H12" s="130">
+        <f t="shared" si="0"/>
+        <v>1.4336000000000002E-2</v>
+      </c>
+      <c r="I12" s="129"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="155"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129">
+        <f>SUM(H10:H12)</f>
+        <v>6.4131199999999999E-2</v>
+      </c>
+      <c r="I13" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="129">
+        <f>Sheet4!F7*1.15</f>
+        <v>247293.58499999996</v>
+      </c>
+      <c r="K13" s="129">
+        <f>H13*J13</f>
+        <v>15859.234358351998</v>
+      </c>
+      <c r="L13" s="131"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="155"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="131"/>
+      <c r="N14" s="1">
+        <f>CONVERT(H13,"m3","ft3")</f>
+        <v>2.2647719544491287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="155">
+        <v>2</v>
+      </c>
+      <c r="C15" s="173" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="143">
+        <f>1+(2*SUM(D10:D12))</f>
+        <v>17</v>
+      </c>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="130">
+        <f>PRODUCT(D15:G15)</f>
+        <v>17</v>
+      </c>
+      <c r="I15" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="129">
+        <f>1.15*15</f>
+        <v>17.25</v>
+      </c>
+      <c r="K15" s="129">
+        <f>H15*J15</f>
+        <v>293.25</v>
+      </c>
+      <c r="L15" s="131"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="155"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="131"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="155">
+        <v>3</v>
+      </c>
+      <c r="C17" s="174" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="143">
+        <f>2+1+1+1+2+(5)</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="130">
+        <f t="shared" ref="H17:H27" si="1">PRODUCT(D17:G17)</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="129">
+        <f>1.15*33</f>
+        <v>37.949999999999996</v>
+      </c>
+      <c r="K17" s="129">
+        <f>H17*J17</f>
+        <v>455.4</v>
+      </c>
+      <c r="L17" s="131"/>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="155"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="131"/>
+    </row>
+    <row r="19" spans="2:14" ht="33">
+      <c r="B19" s="155">
+        <v>4</v>
+      </c>
+      <c r="C19" s="174" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="143">
+        <f>(1+1+1+2)+(2*SUM(D10:D12))</f>
+        <v>21</v>
+      </c>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="130">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I19" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="129">
+        <f>1.15*44</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="K19" s="129">
+        <f>H19*J19</f>
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="L19" s="131"/>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="155"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="129"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="131"/>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="155">
+        <v>5</v>
+      </c>
+      <c r="C21" s="174" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="143">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="130">
+        <f t="shared" ref="H21" si="2">PRODUCT(D21:G21)</f>
+        <v>8</v>
+      </c>
+      <c r="I21" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="129">
+        <f>1.15*34</f>
+        <v>39.099999999999994</v>
+      </c>
+      <c r="K21" s="129">
+        <f>H21*J21</f>
+        <v>312.79999999999995</v>
+      </c>
+      <c r="L21" s="131"/>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="155"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="131"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="155">
+        <v>6</v>
+      </c>
+      <c r="C23" s="173" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="143">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="129">
+        <v>0.41</v>
+      </c>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129">
+        <v>0.46</v>
+      </c>
+      <c r="H23" s="130">
+        <f t="shared" si="1"/>
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="131"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="155"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="213">
+        <v>36</v>
+      </c>
+      <c r="E24" s="135">
+        <v>0.43</v>
+      </c>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135">
+        <v>0.98</v>
+      </c>
+      <c r="H24" s="138">
+        <f t="shared" ref="H24" si="3">PRODUCT(D24:G24)</f>
+        <v>15.170400000000001</v>
+      </c>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="131"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="155"/>
+      <c r="C25" s="171"/>
+      <c r="D25" s="143">
+        <v>4</v>
+      </c>
+      <c r="E25" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="F25" s="129"/>
+      <c r="G25" s="129">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H25" s="130">
+        <f t="shared" si="1"/>
+        <v>1.4336000000000002</v>
+      </c>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="131"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="155"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="143">
+        <v>1</v>
+      </c>
+      <c r="E26" s="129">
+        <f>0.44</f>
+        <v>0.44</v>
+      </c>
+      <c r="F26" s="129"/>
+      <c r="G26" s="129">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H26" s="130">
+        <f t="shared" si="1"/>
+        <v>0.42459999999999998</v>
+      </c>
+      <c r="I26" s="129"/>
+      <c r="J26" s="129"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="131"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="155"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="143">
+        <v>1</v>
+      </c>
+      <c r="E27" s="129">
+        <v>0.43</v>
+      </c>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129">
+        <v>0.3</v>
+      </c>
+      <c r="H27" s="130">
+        <f t="shared" si="1"/>
+        <v>0.129</v>
+      </c>
+      <c r="I27" s="129"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="131"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="155"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129">
+        <f>SUM(H23:H27)</f>
+        <v>19.043600000000005</v>
+      </c>
+      <c r="I28" s="129" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="129">
+        <f>1.15*Sheet4!F8</f>
+        <v>643.44799999999998</v>
+      </c>
+      <c r="K28" s="129">
+        <f>H28*J28</f>
+        <v>12253.566332800003</v>
+      </c>
+      <c r="L28" s="131"/>
+      <c r="N28" s="1">
+        <f>CONVERT(H28,"m2","ft2")</f>
+        <v>204.98360441165332</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="155"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="131"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="155">
+        <v>7</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="129">
+        <v>4</v>
+      </c>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="130">
+        <f t="shared" ref="H30:H36" si="4">PRODUCT(D30:G30)</f>
+        <v>4</v>
+      </c>
+      <c r="I30" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J30" s="130">
+        <f>1.15*389</f>
+        <v>447.34999999999997</v>
+      </c>
+      <c r="K30" s="129">
+        <f>H30*J30</f>
+        <v>1789.3999999999999</v>
+      </c>
+      <c r="L30" s="131"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="155"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="131"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="155">
+        <v>8</v>
+      </c>
+      <c r="C32" s="144" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="129">
+        <v>3</v>
+      </c>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="130">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="I32" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="130">
+        <f>1.15*534</f>
+        <v>614.09999999999991</v>
+      </c>
+      <c r="K32" s="129">
+        <f>H32*J32</f>
+        <v>1842.2999999999997</v>
+      </c>
+      <c r="L32" s="131"/>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="155"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="131"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="155">
+        <v>9</v>
+      </c>
+      <c r="C34" s="173" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="129">
+        <v>5</v>
+      </c>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="130">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="I34" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="130">
+        <f>1.15*221</f>
+        <v>254.14999999999998</v>
+      </c>
+      <c r="K34" s="129">
+        <f>H34*J34</f>
+        <v>1270.75</v>
+      </c>
+      <c r="L34" s="131"/>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="155"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="129"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="131"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="155">
+        <v>10</v>
+      </c>
+      <c r="C36" s="144" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" s="129">
+        <v>2</v>
+      </c>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="130">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="I36" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="130">
+        <f>1.15*74</f>
+        <v>85.1</v>
+      </c>
+      <c r="K36" s="129">
+        <f>H36*J36</f>
+        <v>170.2</v>
+      </c>
+      <c r="L36" s="131"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="155"/>
+      <c r="C37" s="144"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="129"/>
+      <c r="L37" s="131"/>
+    </row>
+    <row r="38" spans="2:12" s="4" customFormat="1" ht="49.5">
+      <c r="B38" s="155">
+        <v>11</v>
+      </c>
+      <c r="C38" s="176" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="127">
+        <v>1</v>
+      </c>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="178">
+        <f>PRODUCT(D38:G38)</f>
+        <v>1</v>
+      </c>
+      <c r="I38" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" s="178">
+        <v>35000</v>
+      </c>
+      <c r="K38" s="178">
+        <f>H38*J38</f>
+        <v>35000</v>
+      </c>
+      <c r="L38" s="179"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" s="155"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="129"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="131"/>
+    </row>
+    <row r="40" spans="2:12" s="4" customFormat="1" ht="33" customHeight="1">
+      <c r="B40" s="155">
+        <v>12</v>
+      </c>
+      <c r="C40" s="176" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="127">
+        <v>1</v>
+      </c>
+      <c r="E40" s="177"/>
+      <c r="F40" s="177"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="178">
+        <f>PRODUCT(D40:G40)</f>
+        <v>1</v>
+      </c>
+      <c r="I40" s="177" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="178">
+        <v>500</v>
+      </c>
+      <c r="K40" s="178">
+        <f>H40*J40</f>
+        <v>500</v>
+      </c>
+      <c r="L40" s="179"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="148"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="129"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="130"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="130"/>
+      <c r="K41" s="150">
+        <f>SUM(K10:K40)</f>
+        <v>70809.500691152003</v>
+      </c>
+      <c r="L41" s="151"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="C43" s="134" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" s="182">
+        <f>+K41</f>
+        <v>70809.500691152003</v>
+      </c>
+      <c r="E43" s="182"/>
+      <c r="G43" s="64"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="C44" s="134" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="182">
+        <f>13%*D43</f>
+        <v>9205.2350898497607</v>
+      </c>
+      <c r="E44" s="182"/>
+      <c r="G44" s="64"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="C45" s="151" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="182">
+        <f>SUM(D43:E44)</f>
+        <v>80014.735781001771</v>
+      </c>
+      <c r="E45" s="183"/>
+      <c r="G45" s="62"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="I6:L6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.39370078740157499" bottom="0.70866141732283505" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0E5568-E3E1-494B-8DF3-F163EB20479A}">
+  <dimension ref="A1:M39"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="6.28515625" customWidth="1"/>
+    <col min="2" max="2" width="39.28515625" customWidth="1"/>
+    <col min="3" max="3" width="8.85546875" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="190" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="190"/>
+      <c r="K1" s="190"/>
+    </row>
+    <row r="2" spans="1:13" ht="25.5">
+      <c r="A2" s="191" t="s">
+        <v>52</v>
+      </c>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
+      <c r="K2" s="191"/>
+    </row>
+    <row r="3" spans="1:13" s="215" customFormat="1">
+      <c r="A3" s="214" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+    </row>
+    <row r="4" spans="1:13" s="215" customFormat="1">
+      <c r="A4" s="214" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
+      <c r="K4" s="214"/>
+    </row>
+    <row r="5" spans="1:13" ht="18.75">
+      <c r="A5" s="192" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" s="192"/>
+      <c r="C5" s="192"/>
+      <c r="D5" s="192"/>
+      <c r="E5" s="192"/>
+      <c r="F5" s="192"/>
+      <c r="G5" s="192"/>
+      <c r="H5" s="192"/>
+      <c r="I5" s="192"/>
+      <c r="J5" s="192"/>
+      <c r="K5" s="192"/>
+    </row>
+    <row r="6" spans="1:13" ht="18.75">
+      <c r="A6" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="B6" s="31"/>
+      <c r="C6" s="194">
+        <f>F37</f>
+        <v>70809.500691152003</v>
+      </c>
+      <c r="D6" s="195"/>
+      <c r="E6" s="216"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="31"/>
+      <c r="J6" s="194">
+        <f>I37</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="K6" s="195"/>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="32" t="s">
+        <v>216</v>
+      </c>
+      <c r="B7" s="32"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
+      <c r="F7" s="196"/>
+      <c r="G7" s="196"/>
+      <c r="I7" s="217" t="s">
+        <v>217</v>
+      </c>
+      <c r="J7" s="217"/>
+      <c r="K7" s="217"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75">
+      <c r="A8" s="218" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="218"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="I8" s="197" t="s">
+        <v>218</v>
+      </c>
+      <c r="J8" s="197"/>
+      <c r="K8" s="197"/>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="219" t="str">
+        <f>E!B6</f>
+        <v>Location:- Shankharapur Municipality- 1</v>
+      </c>
+      <c r="B9" s="219"/>
+      <c r="C9" s="219"/>
+      <c r="D9" s="219"/>
+      <c r="E9" s="219"/>
+      <c r="F9" s="219"/>
+      <c r="I9" s="197" t="s">
+        <v>219</v>
+      </c>
+      <c r="J9" s="197"/>
+      <c r="K9" s="197"/>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="220" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="220" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="220" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="221" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="221"/>
+      <c r="F11" s="221"/>
+      <c r="G11" s="221" t="s">
+        <v>62</v>
+      </c>
+      <c r="H11" s="221"/>
+      <c r="I11" s="221"/>
+      <c r="J11" s="220" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="222" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="220"/>
+      <c r="B12" s="220"/>
+      <c r="C12" s="220"/>
+      <c r="D12" s="223" t="s">
+        <v>64</v>
+      </c>
+      <c r="E12" s="223" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="223" t="s">
+        <v>9</v>
+      </c>
+      <c r="G12" s="223" t="s">
+        <v>64</v>
+      </c>
+      <c r="H12" s="223" t="s">
+        <v>8</v>
+      </c>
+      <c r="I12" s="223" t="s">
+        <v>9</v>
+      </c>
+      <c r="J12" s="220"/>
+      <c r="K12" s="222"/>
+    </row>
+    <row r="13" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A13" s="224">
+        <f>E!B9</f>
+        <v>1</v>
+      </c>
+      <c r="B13" s="172" t="str">
+        <f>E!C9</f>
+        <v>;fn sf7</v>
+      </c>
+      <c r="C13" s="225" t="str">
+        <f>E!I13</f>
+        <v>cum</v>
+      </c>
+      <c r="D13" s="225">
+        <f>E!H13</f>
+        <v>6.4131199999999999E-2</v>
+      </c>
+      <c r="E13" s="225">
+        <f>E!J13</f>
+        <v>247293.58499999996</v>
+      </c>
+      <c r="F13" s="225">
+        <f>D13*E13</f>
+        <v>15859.234358351998</v>
+      </c>
+      <c r="G13" s="225">
+        <f>V!H13</f>
+        <v>6.4131199999999999E-2</v>
+      </c>
+      <c r="H13" s="225">
+        <f>V!J13</f>
+        <v>247293.58499999996</v>
+      </c>
+      <c r="I13" s="225">
+        <f>G13*H13</f>
+        <v>15859.234358351998</v>
+      </c>
+      <c r="J13" s="226">
+        <f>I13-F13</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="227"/>
+      <c r="M13" s="215">
+        <f>1.25*F13</f>
+        <v>19824.042947939997</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" s="215" customFormat="1">
+      <c r="A14" s="228"/>
+      <c r="B14" s="229"/>
+      <c r="C14" s="225"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="225"/>
+      <c r="J14" s="226"/>
+      <c r="K14" s="227"/>
+    </row>
+    <row r="15" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A15" s="224">
+        <f>E!B15</f>
+        <v>2</v>
+      </c>
+      <c r="B15" s="172" t="str">
+        <f>E!C15</f>
+        <v>kmnfdsf] sAhf #Æ ;fOh</v>
+      </c>
+      <c r="C15" s="225" t="str">
+        <f>E!I15</f>
+        <v>no.</v>
+      </c>
+      <c r="D15" s="225">
+        <f>E!H15</f>
+        <v>17</v>
+      </c>
+      <c r="E15" s="225">
+        <f>E!J15</f>
+        <v>17.25</v>
+      </c>
+      <c r="F15" s="225">
+        <f>D15*E15</f>
+        <v>293.25</v>
+      </c>
+      <c r="G15" s="225">
+        <f>V!H15</f>
+        <v>17</v>
+      </c>
+      <c r="H15" s="225">
+        <f>V!J15</f>
+        <v>17.25</v>
+      </c>
+      <c r="I15" s="225">
+        <f>G15*H15</f>
+        <v>293.25</v>
+      </c>
+      <c r="J15" s="226">
+        <f>I15-F15</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="227"/>
+      <c r="M15" s="215">
+        <f t="shared" ref="M15:M33" si="0">1.25*F15</f>
+        <v>366.5625</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A16" s="224"/>
+      <c r="B16" s="230"/>
+      <c r="C16" s="225"/>
+      <c r="D16" s="225"/>
+      <c r="E16" s="225"/>
+      <c r="F16" s="225"/>
+      <c r="G16" s="225"/>
+      <c r="H16" s="225"/>
+      <c r="I16" s="225"/>
+      <c r="J16" s="226"/>
+      <c r="K16" s="227"/>
+    </row>
+    <row r="17" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A17" s="224">
+        <f>E!B17</f>
+        <v>3</v>
+      </c>
+      <c r="B17" s="230" t="str">
+        <f>E!C17</f>
+        <v>Gate hook</v>
+      </c>
+      <c r="C17" s="225" t="str">
+        <f>E!I17</f>
+        <v>no.</v>
+      </c>
+      <c r="D17" s="225">
+        <f>E!H17</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="225">
+        <f>E!J17</f>
+        <v>37.949999999999996</v>
+      </c>
+      <c r="F17" s="225">
+        <f>D17*E17</f>
+        <v>455.4</v>
+      </c>
+      <c r="G17" s="225">
+        <f>V!H17</f>
+        <v>12</v>
+      </c>
+      <c r="H17" s="225">
+        <f>V!J17</f>
+        <v>37.949999999999996</v>
+      </c>
+      <c r="I17" s="225">
+        <f>G17*H17</f>
+        <v>455.4</v>
+      </c>
+      <c r="J17" s="226">
+        <f>I17-F17</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="227"/>
+      <c r="M17" s="215">
+        <f t="shared" si="0"/>
+        <v>569.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" s="215" customFormat="1">
+      <c r="A18" s="228"/>
+      <c r="B18" s="229"/>
+      <c r="C18" s="225"/>
+      <c r="D18" s="225"/>
+      <c r="E18" s="225"/>
+      <c r="F18" s="225"/>
+      <c r="G18" s="225"/>
+      <c r="H18" s="225"/>
+      <c r="I18" s="225"/>
+      <c r="J18" s="226"/>
+      <c r="K18" s="227"/>
+    </row>
+    <row r="19" spans="1:13" s="215" customFormat="1" ht="16.5">
+      <c r="A19" s="224">
+        <f>E!B19</f>
+        <v>4</v>
+      </c>
+      <c r="B19" s="174" t="s">
+        <v>199</v>
+      </c>
+      <c r="C19" s="225" t="str">
+        <f>E!I19</f>
+        <v>no.</v>
+      </c>
+      <c r="D19" s="225">
+        <f>E!H19</f>
+        <v>21</v>
+      </c>
+      <c r="E19" s="225">
+        <f>E!J19</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="F19" s="225">
+        <f>D19*E19</f>
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="G19" s="225">
+        <f>V!H19</f>
+        <v>21</v>
+      </c>
+      <c r="H19" s="225">
+        <f>V!J19</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="I19" s="225">
+        <f>G19*H19</f>
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="J19" s="226">
+        <f>I19-F19</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="227"/>
+      <c r="M19" s="215">
+        <f t="shared" ref="M19" si="1">1.25*F19</f>
+        <v>1328.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" s="215" customFormat="1">
+      <c r="A20" s="228"/>
+      <c r="B20" s="229"/>
+      <c r="C20" s="225"/>
+      <c r="D20" s="225"/>
+      <c r="E20" s="225"/>
+      <c r="F20" s="225"/>
+      <c r="G20" s="225"/>
+      <c r="H20" s="225"/>
+      <c r="I20" s="225"/>
+      <c r="J20" s="226"/>
+      <c r="K20" s="227"/>
+    </row>
+    <row r="21" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A21" s="224">
+        <f>E!B21</f>
+        <v>5</v>
+      </c>
+      <c r="B21" s="230" t="str">
+        <f>E!C21</f>
+        <v>Handle (ordinary)</v>
+      </c>
+      <c r="C21" s="225" t="str">
+        <f>E!I21</f>
+        <v>no.</v>
+      </c>
+      <c r="D21" s="225">
+        <f>E!H21</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="225">
+        <f>E!J21</f>
+        <v>39.099999999999994</v>
+      </c>
+      <c r="F21" s="225">
+        <f>D21*E21</f>
+        <v>312.79999999999995</v>
+      </c>
+      <c r="G21" s="225">
+        <f>V!H21</f>
+        <v>8</v>
+      </c>
+      <c r="H21" s="225">
+        <f>V!J21</f>
+        <v>39.099999999999994</v>
+      </c>
+      <c r="I21" s="225">
+        <f>G21*H21</f>
+        <v>312.79999999999995</v>
+      </c>
+      <c r="J21" s="226">
+        <f>I21-F21</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="227"/>
+      <c r="M21" s="215">
+        <f t="shared" ref="M21" si="2">1.25*F21</f>
+        <v>390.99999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" s="215" customFormat="1">
+      <c r="A22" s="228"/>
+      <c r="B22" s="229"/>
+      <c r="C22" s="225"/>
+      <c r="D22" s="225"/>
+      <c r="E22" s="225"/>
+      <c r="F22" s="225"/>
+      <c r="G22" s="225"/>
+      <c r="H22" s="225"/>
+      <c r="I22" s="225"/>
+      <c r="J22" s="226"/>
+      <c r="K22" s="227"/>
+    </row>
+    <row r="23" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A23" s="224">
+        <f>E!B23</f>
+        <v>6</v>
+      </c>
+      <c r="B23" s="172" t="str">
+        <f>E!C23</f>
+        <v>P]gf # dL=dL=</v>
+      </c>
+      <c r="C23" s="225" t="str">
+        <f>E!I28</f>
+        <v>sq.m</v>
+      </c>
+      <c r="D23" s="225">
+        <f>E!H28</f>
+        <v>19.043600000000005</v>
+      </c>
+      <c r="E23" s="225">
+        <f>E!J28</f>
+        <v>643.44799999999998</v>
+      </c>
+      <c r="F23" s="225">
+        <f>D23*E23</f>
+        <v>12253.566332800003</v>
+      </c>
+      <c r="G23" s="225">
+        <f>V!H28</f>
+        <v>19.043600000000005</v>
+      </c>
+      <c r="H23" s="225">
+        <f>V!J28</f>
+        <v>643.44799999999998</v>
+      </c>
+      <c r="I23" s="225">
+        <f>G23*H23</f>
+        <v>12253.566332800003</v>
+      </c>
+      <c r="J23" s="226">
+        <f>I23-F23</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="227"/>
+      <c r="M23" s="215">
+        <f t="shared" ref="M23" si="3">1.25*F23</f>
+        <v>15316.957916000003</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" s="215" customFormat="1">
+      <c r="A24" s="228"/>
+      <c r="B24" s="229"/>
+      <c r="C24" s="225"/>
+      <c r="D24" s="225"/>
+      <c r="E24" s="225"/>
+      <c r="F24" s="225"/>
+      <c r="G24" s="225"/>
+      <c r="H24" s="225"/>
+      <c r="I24" s="225"/>
+      <c r="J24" s="226"/>
+      <c r="K24" s="227"/>
+    </row>
+    <row r="25" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A25" s="224">
+        <f>E!B30</f>
+        <v>7</v>
+      </c>
+      <c r="B25" s="230" t="str">
+        <f>E!C30</f>
+        <v>Wood primer</v>
+      </c>
+      <c r="C25" s="225" t="str">
+        <f>E!I30</f>
+        <v>ltr</v>
+      </c>
+      <c r="D25" s="225">
+        <f>E!H30</f>
+        <v>4</v>
+      </c>
+      <c r="E25" s="225">
+        <f>E!J30</f>
+        <v>447.34999999999997</v>
+      </c>
+      <c r="F25" s="225">
+        <f>D25*E25</f>
+        <v>1789.3999999999999</v>
+      </c>
+      <c r="G25" s="225">
+        <f>V!H30</f>
+        <v>4</v>
+      </c>
+      <c r="H25" s="225">
+        <f>V!J30</f>
+        <v>447.34999999999997</v>
+      </c>
+      <c r="I25" s="225">
+        <f>G25*H25</f>
+        <v>1789.3999999999999</v>
+      </c>
+      <c r="J25" s="226">
+        <f>I25-F25</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="227"/>
+      <c r="M25" s="215">
+        <f t="shared" ref="M25" si="4">1.25*F25</f>
+        <v>2236.75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" s="215" customFormat="1">
+      <c r="A26" s="228"/>
+      <c r="B26" s="229"/>
+      <c r="C26" s="225"/>
+      <c r="D26" s="225"/>
+      <c r="E26" s="225"/>
+      <c r="F26" s="225"/>
+      <c r="G26" s="225"/>
+      <c r="H26" s="225"/>
+      <c r="I26" s="225"/>
+      <c r="J26" s="226"/>
+      <c r="K26" s="227"/>
+    </row>
+    <row r="27" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A27" s="224">
+        <f>E!B32</f>
+        <v>8</v>
+      </c>
+      <c r="B27" s="230" t="str">
+        <f>E!C32</f>
+        <v>Enamel paints</v>
+      </c>
+      <c r="C27" s="225" t="str">
+        <f>E!I32</f>
+        <v>ltr</v>
+      </c>
+      <c r="D27" s="225">
+        <f>E!H32</f>
+        <v>3</v>
+      </c>
+      <c r="E27" s="225">
+        <f>E!J32</f>
+        <v>614.09999999999991</v>
+      </c>
+      <c r="F27" s="225">
+        <f>D27*E27</f>
+        <v>1842.2999999999997</v>
+      </c>
+      <c r="G27" s="225">
+        <f>V!H32</f>
+        <v>3</v>
+      </c>
+      <c r="H27" s="225">
+        <f>V!J32</f>
+        <v>614.09999999999991</v>
+      </c>
+      <c r="I27" s="225">
+        <f>G27*H27</f>
+        <v>1842.2999999999997</v>
+      </c>
+      <c r="J27" s="226">
+        <f>I27-F27</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="227"/>
+      <c r="M27" s="215">
+        <f t="shared" ref="M27" si="5">1.25*F27</f>
+        <v>2302.8749999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" s="215" customFormat="1">
+      <c r="A28" s="228"/>
+      <c r="B28" s="229"/>
+      <c r="C28" s="225"/>
+      <c r="D28" s="225"/>
+      <c r="E28" s="225"/>
+      <c r="F28" s="225"/>
+      <c r="G28" s="225"/>
+      <c r="H28" s="225"/>
+      <c r="I28" s="225"/>
+      <c r="J28" s="226"/>
+      <c r="K28" s="227"/>
+    </row>
+    <row r="29" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A29" s="224">
+        <f>E!B34</f>
+        <v>9</v>
+      </c>
+      <c r="B29" s="172" t="str">
+        <f>E!C34</f>
+        <v>tf/lkg t]n</v>
+      </c>
+      <c r="C29" s="225" t="str">
+        <f>E!I34</f>
+        <v>ltr</v>
+      </c>
+      <c r="D29" s="225">
+        <f>E!H34</f>
+        <v>5</v>
+      </c>
+      <c r="E29" s="225">
+        <f>E!J34</f>
+        <v>254.14999999999998</v>
+      </c>
+      <c r="F29" s="225">
+        <f>D29*E29</f>
+        <v>1270.75</v>
+      </c>
+      <c r="G29" s="225">
+        <f>V!H34</f>
+        <v>5</v>
+      </c>
+      <c r="H29" s="225">
+        <f>V!J34</f>
+        <v>254.14999999999998</v>
+      </c>
+      <c r="I29" s="225">
+        <f>G29*H29</f>
+        <v>1270.75</v>
+      </c>
+      <c r="J29" s="226">
+        <f>I29-F29</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="227"/>
+      <c r="M29" s="215">
+        <f t="shared" ref="M29" si="6">1.25*F29</f>
+        <v>1588.4375</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" s="215" customFormat="1">
+      <c r="A30" s="228"/>
+      <c r="B30" s="229"/>
+      <c r="C30" s="225"/>
+      <c r="D30" s="225"/>
+      <c r="E30" s="225"/>
+      <c r="F30" s="225"/>
+      <c r="G30" s="225"/>
+      <c r="H30" s="225"/>
+      <c r="I30" s="225"/>
+      <c r="J30" s="226"/>
+      <c r="K30" s="227"/>
+    </row>
+    <row r="31" spans="1:13" s="215" customFormat="1" ht="15.75">
+      <c r="A31" s="224">
+        <f>E!B36</f>
+        <v>10</v>
+      </c>
+      <c r="B31" s="230" t="str">
+        <f>E!C36</f>
+        <v>1" thick Paint Brush</v>
+      </c>
+      <c r="C31" s="225" t="str">
+        <f>E!I36</f>
+        <v>no.</v>
+      </c>
+      <c r="D31" s="225">
+        <f>E!H36</f>
+        <v>2</v>
+      </c>
+      <c r="E31" s="225">
+        <f>E!J36</f>
+        <v>85.1</v>
+      </c>
+      <c r="F31" s="225">
+        <f>D31*E31</f>
+        <v>170.2</v>
+      </c>
+      <c r="G31" s="225">
+        <f>V!H36</f>
+        <v>2</v>
+      </c>
+      <c r="H31" s="225">
+        <f>V!J36</f>
+        <v>85.1</v>
+      </c>
+      <c r="I31" s="225">
+        <f>G31*H31</f>
+        <v>170.2</v>
+      </c>
+      <c r="J31" s="226">
+        <f>I31-F31</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="227"/>
+      <c r="M31" s="215">
+        <f t="shared" ref="M31" si="7">1.25*F31</f>
+        <v>212.75</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" s="215" customFormat="1">
+      <c r="A32" s="228"/>
+      <c r="B32" s="229"/>
+      <c r="C32" s="225"/>
+      <c r="D32" s="225"/>
+      <c r="E32" s="225"/>
+      <c r="F32" s="225"/>
+      <c r="G32" s="225"/>
+      <c r="H32" s="225"/>
+      <c r="I32" s="225"/>
+      <c r="J32" s="226"/>
+      <c r="K32" s="227"/>
+    </row>
+    <row r="33" spans="1:13" s="215" customFormat="1" ht="31.5">
+      <c r="A33" s="224">
+        <f>E!B38</f>
+        <v>11</v>
+      </c>
+      <c r="B33" s="230" t="str">
+        <f>E!C38</f>
+        <v>Provisional sum for unforseen materials and manpower</v>
+      </c>
+      <c r="C33" s="225" t="str">
+        <f>E!I38</f>
+        <v>PS</v>
+      </c>
+      <c r="D33" s="225">
+        <f>E!H38</f>
+        <v>1</v>
+      </c>
+      <c r="E33" s="225">
+        <f>E!J38</f>
+        <v>35000</v>
+      </c>
+      <c r="F33" s="225">
+        <f>D33*E33</f>
+        <v>35000</v>
+      </c>
+      <c r="G33" s="225">
+        <f>V!H38</f>
+        <v>1</v>
+      </c>
+      <c r="H33" s="225">
+        <f>V!J38</f>
+        <v>35000</v>
+      </c>
+      <c r="I33" s="225">
+        <f>G33*H33</f>
+        <v>35000</v>
+      </c>
+      <c r="J33" s="226">
+        <f>I33-F33</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="227"/>
+      <c r="M33" s="215">
+        <f t="shared" si="0"/>
+        <v>43750</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" s="215" customFormat="1">
+      <c r="A34" s="228"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="225"/>
+      <c r="D34" s="225"/>
+      <c r="E34" s="225"/>
+      <c r="F34" s="225"/>
+      <c r="G34" s="225"/>
+      <c r="H34" s="225"/>
+      <c r="I34" s="225"/>
+      <c r="J34" s="226"/>
+      <c r="K34" s="227"/>
+    </row>
+    <row r="35" spans="1:13" s="215" customFormat="1">
+      <c r="A35" s="224">
+        <f>E!B40</f>
+        <v>12</v>
+      </c>
+      <c r="B35" s="231" t="str">
+        <f>E!C40</f>
+        <v>Information Board  and photographs</v>
+      </c>
+      <c r="C35" s="225" t="str">
+        <f>E!I40</f>
+        <v>no.</v>
+      </c>
+      <c r="D35" s="225">
+        <f>E!H40</f>
+        <v>1</v>
+      </c>
+      <c r="E35" s="225">
+        <f>E!J40</f>
+        <v>500</v>
+      </c>
+      <c r="F35" s="225">
+        <f>D35*E35</f>
+        <v>500</v>
+      </c>
+      <c r="G35" s="225">
+        <f>V!D40</f>
+        <v>0</v>
+      </c>
+      <c r="H35" s="225">
+        <f>V!J40</f>
+        <v>500</v>
+      </c>
+      <c r="I35" s="225">
+        <f>G35*H35</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="226">
+        <f>I35-F35</f>
+        <v>-500</v>
+      </c>
+      <c r="K35" s="227"/>
+    </row>
+    <row r="36" spans="1:13" s="215" customFormat="1">
+      <c r="A36" s="229"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="225"/>
+      <c r="D36" s="225"/>
+      <c r="E36" s="225"/>
+      <c r="F36" s="225"/>
+      <c r="G36" s="225"/>
+      <c r="H36" s="225"/>
+      <c r="I36" s="225"/>
+      <c r="J36" s="226"/>
+      <c r="K36" s="227"/>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="232"/>
+      <c r="B37" s="233" t="s">
+        <v>67</v>
+      </c>
+      <c r="C37" s="233"/>
+      <c r="D37" s="234"/>
+      <c r="E37" s="234"/>
+      <c r="F37" s="234">
+        <f>SUM(F13:F35)</f>
+        <v>70809.500691152003</v>
+      </c>
+      <c r="G37" s="234"/>
+      <c r="H37" s="234"/>
+      <c r="I37" s="234">
+        <f>SUM(I13:I35)</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="J37" s="235">
+        <f>I37-F37</f>
+        <v>-500</v>
+      </c>
+      <c r="K37" s="232"/>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="232"/>
+      <c r="B38" s="233" t="s">
+        <v>171</v>
+      </c>
+      <c r="C38" s="232"/>
+      <c r="D38" s="232"/>
+      <c r="E38" s="232"/>
+      <c r="F38" s="234">
+        <f>13%*F37</f>
+        <v>9205.2350898497607</v>
+      </c>
+      <c r="G38" s="232"/>
+      <c r="H38" s="232"/>
+      <c r="I38" s="234">
+        <f>13%*I37</f>
+        <v>9140.2350898497607</v>
+      </c>
+      <c r="J38" s="235">
+        <f t="shared" ref="J38:J39" si="8">I38-F38</f>
+        <v>-65</v>
+      </c>
+      <c r="K38" s="232"/>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="232"/>
+      <c r="B39" s="233" t="s">
+        <v>221</v>
+      </c>
+      <c r="C39" s="232"/>
+      <c r="D39" s="232"/>
+      <c r="E39" s="232"/>
+      <c r="F39" s="234">
+        <f>SUM(F37:F38)</f>
+        <v>80014.735781001771</v>
+      </c>
+      <c r="G39" s="232"/>
+      <c r="H39" s="232"/>
+      <c r="I39" s="234">
+        <f>SUM(I37:I38)</f>
+        <v>79449.735781001771</v>
+      </c>
+      <c r="J39" s="235">
+        <f t="shared" si="8"/>
+        <v>-565</v>
+      </c>
+      <c r="K39" s="232"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="82" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter>
+    <oddFooter xml:space="preserve">&amp;LPrepared By:
+&amp;CChecked By:
+&amp;RApproved By:
+</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1975F0B8-627D-4ADD-94F4-E510506642CE}">
+  <dimension ref="A1:N45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+    </row>
+    <row r="2" spans="1:14" ht="20.25">
+      <c r="A2" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="186" t="s">
+        <v>211</v>
+      </c>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="158" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="K5" s="187" t="s">
+        <v>101</v>
+      </c>
+      <c r="L5" s="187"/>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="189" t="s">
+        <v>222</v>
+      </c>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2"/>
+      <c r="B8" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="154" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="156" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="154" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="157" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="155">
+        <v>1</v>
+      </c>
+      <c r="C9" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="155"/>
+      <c r="C10" s="132" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="143">
+        <v>5</v>
+      </c>
+      <c r="E10" s="130">
+        <f>1.1*2+0.53*3</f>
+        <v>3.79</v>
+      </c>
+      <c r="F10" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G10" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H10" s="130">
+        <f>PRODUCT(D10:G10)</f>
+        <v>4.2448E-2</v>
+      </c>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="131"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="155"/>
+      <c r="C11" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="143">
+        <v>1</v>
+      </c>
+      <c r="E11" s="130">
+        <f>1.2*2+0.44*2</f>
+        <v>3.28</v>
+      </c>
+      <c r="F11" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G11" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H11" s="130">
+        <f t="shared" ref="H11:H12" si="0">PRODUCT(D11:G11)</f>
+        <v>7.3471999999999999E-3</v>
+      </c>
+      <c r="I11" s="129"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="131"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="155"/>
+      <c r="C12" s="132" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="143">
+        <v>2</v>
+      </c>
+      <c r="E12" s="130">
+        <f>0.53*2+1.07*2</f>
+        <v>3.2</v>
+      </c>
+      <c r="F12" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G12" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H12" s="130">
+        <f t="shared" si="0"/>
+        <v>1.4336000000000002E-2</v>
+      </c>
+      <c r="I12" s="129"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="155"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129">
+        <f>SUM(H10:H12)</f>
+        <v>6.4131199999999999E-2</v>
+      </c>
+      <c r="I13" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="129">
+        <f>Sheet4!F7*1.15</f>
+        <v>247293.58499999996</v>
+      </c>
+      <c r="K13" s="129">
+        <f>H13*J13</f>
+        <v>15859.234358351998</v>
+      </c>
+      <c r="L13" s="131"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="155"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="131"/>
+      <c r="N14" s="1">
+        <f>CONVERT(H13,"m3","ft3")</f>
+        <v>2.2647719544491287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="155">
+        <v>2</v>
+      </c>
+      <c r="C15" s="173" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="143">
+        <f>1+(2*SUM(D10:D12))</f>
+        <v>17</v>
+      </c>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="130">
+        <f>PRODUCT(D15:G15)</f>
+        <v>17</v>
+      </c>
+      <c r="I15" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="129">
+        <f>1.15*15</f>
+        <v>17.25</v>
+      </c>
+      <c r="K15" s="129">
+        <f>H15*J15</f>
+        <v>293.25</v>
+      </c>
+      <c r="L15" s="131"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="155"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="131"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="155">
+        <v>3</v>
+      </c>
+      <c r="C17" s="174" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="143">
+        <f>2+1+1+1+2+(5)</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="130">
+        <f t="shared" ref="H17:H27" si="1">PRODUCT(D17:G17)</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="129">
+        <f>1.15*33</f>
+        <v>37.949999999999996</v>
+      </c>
+      <c r="K17" s="129">
+        <f>H17*J17</f>
+        <v>455.4</v>
+      </c>
+      <c r="L17" s="131"/>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="155"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="131"/>
+    </row>
+    <row r="19" spans="2:14" ht="33">
+      <c r="B19" s="155">
+        <v>4</v>
+      </c>
+      <c r="C19" s="174" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="143">
+        <f>(1+1+1+2)+(2*SUM(D10:D12))</f>
+        <v>21</v>
+      </c>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="130">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I19" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="129">
+        <f>1.15*44</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="K19" s="129">
+        <f>H19*J19</f>
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="L19" s="131"/>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="155"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="129"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="131"/>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="155">
+        <v>5</v>
+      </c>
+      <c r="C21" s="174" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="143">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="130">
+        <f t="shared" ref="H21" si="2">PRODUCT(D21:G21)</f>
+        <v>8</v>
+      </c>
+      <c r="I21" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="129">
+        <f>1.15*34</f>
+        <v>39.099999999999994</v>
+      </c>
+      <c r="K21" s="129">
+        <f>H21*J21</f>
+        <v>312.79999999999995</v>
+      </c>
+      <c r="L21" s="131"/>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="155"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="131"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="155">
+        <v>6</v>
+      </c>
+      <c r="C23" s="173" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="143">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="129">
+        <v>0.41</v>
+      </c>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129">
+        <v>0.46</v>
+      </c>
+      <c r="H23" s="130">
+        <f t="shared" si="1"/>
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="131"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="155"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="213">
+        <v>36</v>
+      </c>
+      <c r="E24" s="135">
+        <v>0.43</v>
+      </c>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135">
+        <v>0.98</v>
+      </c>
+      <c r="H24" s="138">
+        <f>PRODUCT(D24:G24)</f>
+        <v>15.170400000000001</v>
+      </c>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="131"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="155"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="143">
+        <v>4</v>
+      </c>
+      <c r="E25" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="F25" s="129"/>
+      <c r="G25" s="129">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H25" s="130">
+        <f t="shared" si="1"/>
+        <v>1.4336000000000002</v>
+      </c>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="131"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="155"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="143">
+        <v>1</v>
+      </c>
+      <c r="E26" s="129">
+        <f>0.44</f>
+        <v>0.44</v>
+      </c>
+      <c r="F26" s="129"/>
+      <c r="G26" s="129">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H26" s="130">
+        <f t="shared" si="1"/>
+        <v>0.42459999999999998</v>
+      </c>
+      <c r="I26" s="129"/>
+      <c r="J26" s="129"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="131"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="155"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="143">
+        <v>1</v>
+      </c>
+      <c r="E27" s="129">
+        <v>0.43</v>
+      </c>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129">
+        <v>0.3</v>
+      </c>
+      <c r="H27" s="130">
+        <f t="shared" si="1"/>
+        <v>0.129</v>
+      </c>
+      <c r="I27" s="129"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="131"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="155"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129">
+        <f>SUM(H23:H27)</f>
+        <v>19.043600000000005</v>
+      </c>
+      <c r="I28" s="129" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="129">
+        <f>1.15*Sheet4!F8</f>
+        <v>643.44799999999998</v>
+      </c>
+      <c r="K28" s="129">
+        <f>H28*J28</f>
+        <v>12253.566332800003</v>
+      </c>
+      <c r="L28" s="131"/>
+      <c r="N28" s="1">
+        <f>CONVERT(H28,"m2","ft2")</f>
+        <v>204.98360441165332</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="155"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="131"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="155">
+        <v>7</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="129">
+        <v>4</v>
+      </c>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="130">
+        <f t="shared" ref="H30:H36" si="3">PRODUCT(D30:G30)</f>
+        <v>4</v>
+      </c>
+      <c r="I30" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J30" s="130">
+        <f>1.15*389</f>
+        <v>447.34999999999997</v>
+      </c>
+      <c r="K30" s="129">
+        <f>H30*J30</f>
+        <v>1789.3999999999999</v>
+      </c>
+      <c r="L30" s="131"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="155"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="131"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="155">
+        <v>8</v>
+      </c>
+      <c r="C32" s="144" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="129">
+        <v>3</v>
+      </c>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="130">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I32" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="130">
+        <f>1.15*534</f>
+        <v>614.09999999999991</v>
+      </c>
+      <c r="K32" s="129">
+        <f>H32*J32</f>
+        <v>1842.2999999999997</v>
+      </c>
+      <c r="L32" s="131"/>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="155"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="131"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="155">
+        <v>9</v>
+      </c>
+      <c r="C34" s="173" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="129">
+        <v>5</v>
+      </c>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="130">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="I34" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="130">
+        <f>1.15*221</f>
+        <v>254.14999999999998</v>
+      </c>
+      <c r="K34" s="129">
+        <f>H34*J34</f>
+        <v>1270.75</v>
+      </c>
+      <c r="L34" s="131"/>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="155"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="129"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="131"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="155">
+        <v>10</v>
+      </c>
+      <c r="C36" s="144" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" s="129">
+        <v>2</v>
+      </c>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="130">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I36" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="130">
+        <f>1.15*74</f>
+        <v>85.1</v>
+      </c>
+      <c r="K36" s="129">
+        <f>H36*J36</f>
+        <v>170.2</v>
+      </c>
+      <c r="L36" s="131"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="155"/>
+      <c r="C37" s="144"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="129"/>
+      <c r="L37" s="131"/>
+    </row>
+    <row r="38" spans="2:12" s="4" customFormat="1" ht="49.5">
+      <c r="B38" s="155">
+        <v>11</v>
+      </c>
+      <c r="C38" s="176" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="127">
+        <v>1</v>
+      </c>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="178">
+        <f>PRODUCT(D38:G38)</f>
+        <v>1</v>
+      </c>
+      <c r="I38" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" s="178">
+        <v>35000</v>
+      </c>
+      <c r="K38" s="178">
+        <f>H38*J38</f>
+        <v>35000</v>
+      </c>
+      <c r="L38" s="179"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" s="155"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="129"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="131"/>
+    </row>
+    <row r="40" spans="2:12" s="4" customFormat="1" ht="33" customHeight="1">
+      <c r="B40" s="155">
+        <v>12</v>
+      </c>
+      <c r="C40" s="176" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="127">
+        <v>0</v>
+      </c>
+      <c r="E40" s="177"/>
+      <c r="F40" s="177"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="178">
+        <f>PRODUCT(D40:G40)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="177" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="178">
+        <v>500</v>
+      </c>
+      <c r="K40" s="178">
+        <f>H40*J40</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="179"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="148"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="129"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="130"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="130"/>
+      <c r="K41" s="150">
+        <f>SUM(K10:K40)</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="L41" s="151"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="2:12">
+      <c r="C43" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="D43" s="182">
+        <f>+K41</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="E43" s="182"/>
+      <c r="G43" s="64"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="2:12">
+      <c r="C44" s="134" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="182">
+        <f>13%*D43</f>
+        <v>9140.2350898497607</v>
+      </c>
+      <c r="E44" s="182"/>
+      <c r="G44" s="64"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="2:12">
+      <c r="C45" s="151" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="182">
+        <f>SUM(D43:E44)</f>
+        <v>79449.735781001771</v>
+      </c>
+      <c r="E45" s="183"/>
+      <c r="G45" s="62"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="I6:L6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.39370078740157499" bottom="0.70866141732283505" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" scale="80" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{102C179B-3491-4C33-909E-01CE6F245D66}">
+  <dimension ref="A1:N45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="3.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="26.140625" style="8" customWidth="1"/>
+    <col min="4" max="4" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="5.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" style="1" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="9.7109375" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="184" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
+    </row>
+    <row r="2" spans="1:14" ht="20.25">
+      <c r="A2" s="185" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="184" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="186" t="s">
+        <v>223</v>
+      </c>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
+    </row>
+    <row r="5" spans="1:14" ht="20.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="158" t="s">
+        <v>180</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="L5" s="180" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6" s="188" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
+      <c r="H6" s="113"/>
+      <c r="J6" s="236"/>
+      <c r="K6" s="236"/>
+      <c r="L6" s="181" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="C7" s="5"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="113"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="113"/>
+      <c r="H7" s="113"/>
+      <c r="J7" s="114"/>
+      <c r="K7" s="113"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="2"/>
+      <c r="B8" s="120" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" s="121" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="156" t="s">
+        <v>2</v>
+      </c>
+      <c r="E8" s="154" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="154" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="154" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="154" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="156" t="s">
+        <v>7</v>
+      </c>
+      <c r="J8" s="154" t="s">
+        <v>8</v>
+      </c>
+      <c r="K8" s="154" t="s">
+        <v>9</v>
+      </c>
+      <c r="L8" s="157" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9" s="155">
+        <v>1</v>
+      </c>
+      <c r="C9" s="172" t="s">
+        <v>186</v>
+      </c>
+      <c r="D9" s="129"/>
+      <c r="E9" s="130"/>
+      <c r="F9" s="130"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="129"/>
+      <c r="J9" s="130"/>
+      <c r="K9" s="130"/>
+      <c r="L9" s="131"/>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10" s="155"/>
+      <c r="C10" s="132" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="143">
+        <v>5</v>
+      </c>
+      <c r="E10" s="130">
+        <f>1.1*2+0.53*3</f>
+        <v>3.79</v>
+      </c>
+      <c r="F10" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G10" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H10" s="130">
+        <f>PRODUCT(D10:G10)</f>
+        <v>4.2448E-2</v>
+      </c>
+      <c r="I10" s="129"/>
+      <c r="J10" s="130"/>
+      <c r="K10" s="130"/>
+      <c r="L10" s="131"/>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11" s="155"/>
+      <c r="C11" s="132" t="s">
+        <v>176</v>
+      </c>
+      <c r="D11" s="143">
+        <v>1</v>
+      </c>
+      <c r="E11" s="130">
+        <f>1.2*2+0.44*2</f>
+        <v>3.28</v>
+      </c>
+      <c r="F11" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G11" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H11" s="130">
+        <f t="shared" ref="H11:H12" si="0">PRODUCT(D11:G11)</f>
+        <v>7.3471999999999999E-3</v>
+      </c>
+      <c r="I11" s="129"/>
+      <c r="J11" s="130"/>
+      <c r="K11" s="130"/>
+      <c r="L11" s="131"/>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12" s="155"/>
+      <c r="C12" s="132" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="143">
+        <v>2</v>
+      </c>
+      <c r="E12" s="130">
+        <f>0.53*2+1.07*2</f>
+        <v>3.2</v>
+      </c>
+      <c r="F12" s="130">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="G12" s="135">
+        <v>3.2000000000000001E-2</v>
+      </c>
+      <c r="H12" s="130">
+        <f t="shared" si="0"/>
+        <v>1.4336000000000002E-2</v>
+      </c>
+      <c r="I12" s="129"/>
+      <c r="J12" s="130"/>
+      <c r="K12" s="130"/>
+      <c r="L12" s="131"/>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13" s="155"/>
+      <c r="C13" s="140"/>
+      <c r="D13" s="129"/>
+      <c r="E13" s="129"/>
+      <c r="F13" s="129"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="129">
+        <f>SUM(H10:H12)</f>
+        <v>6.4131199999999999E-2</v>
+      </c>
+      <c r="I13" s="129" t="s">
+        <v>24</v>
+      </c>
+      <c r="J13" s="129">
+        <f>Sheet4!F7*1.15</f>
+        <v>247293.58499999996</v>
+      </c>
+      <c r="K13" s="129">
+        <f>H13*J13</f>
+        <v>15859.234358351998</v>
+      </c>
+      <c r="L13" s="131"/>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14" s="155"/>
+      <c r="C14" s="140"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="131"/>
+      <c r="N14" s="1">
+        <f>CONVERT(H13,"m3","ft3")</f>
+        <v>2.2647719544491287</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15" s="155">
+        <v>2</v>
+      </c>
+      <c r="C15" s="173" t="s">
+        <v>197</v>
+      </c>
+      <c r="D15" s="143">
+        <f>1+(2*SUM(D10:D12))</f>
+        <v>17</v>
+      </c>
+      <c r="E15" s="129"/>
+      <c r="F15" s="129"/>
+      <c r="G15" s="129"/>
+      <c r="H15" s="130">
+        <f>PRODUCT(D15:G15)</f>
+        <v>17</v>
+      </c>
+      <c r="I15" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="129">
+        <f>1.15*15</f>
+        <v>17.25</v>
+      </c>
+      <c r="K15" s="129">
+        <f>H15*J15</f>
+        <v>293.25</v>
+      </c>
+      <c r="L15" s="131"/>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16" s="155"/>
+      <c r="C16" s="173"/>
+      <c r="D16" s="143"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="129"/>
+      <c r="G16" s="129"/>
+      <c r="H16" s="130"/>
+      <c r="I16" s="129"/>
+      <c r="J16" s="129"/>
+      <c r="K16" s="129"/>
+      <c r="L16" s="131"/>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17" s="155">
+        <v>3</v>
+      </c>
+      <c r="C17" s="174" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="143">
+        <f>2+1+1+1+2+(5)</f>
+        <v>12</v>
+      </c>
+      <c r="E17" s="129"/>
+      <c r="F17" s="129"/>
+      <c r="G17" s="129"/>
+      <c r="H17" s="130">
+        <f t="shared" ref="H17:H27" si="1">PRODUCT(D17:G17)</f>
+        <v>12</v>
+      </c>
+      <c r="I17" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="129">
+        <f>1.15*33</f>
+        <v>37.949999999999996</v>
+      </c>
+      <c r="K17" s="129">
+        <f>H17*J17</f>
+        <v>455.4</v>
+      </c>
+      <c r="L17" s="131"/>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18" s="155"/>
+      <c r="C18" s="174"/>
+      <c r="D18" s="143"/>
+      <c r="E18" s="129"/>
+      <c r="F18" s="129"/>
+      <c r="G18" s="129"/>
+      <c r="H18" s="130"/>
+      <c r="I18" s="129"/>
+      <c r="J18" s="129"/>
+      <c r="K18" s="129"/>
+      <c r="L18" s="131"/>
+    </row>
+    <row r="19" spans="2:14" ht="33">
+      <c r="B19" s="155">
+        <v>4</v>
+      </c>
+      <c r="C19" s="174" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="143">
+        <f>(1+1+1+2)+(2*SUM(D10:D12))</f>
+        <v>21</v>
+      </c>
+      <c r="E19" s="129"/>
+      <c r="F19" s="129"/>
+      <c r="G19" s="129"/>
+      <c r="H19" s="130">
+        <f t="shared" si="1"/>
+        <v>21</v>
+      </c>
+      <c r="I19" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J19" s="129">
+        <f>1.15*44</f>
+        <v>50.599999999999994</v>
+      </c>
+      <c r="K19" s="129">
+        <f>H19*J19</f>
+        <v>1062.5999999999999</v>
+      </c>
+      <c r="L19" s="131"/>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20" s="155"/>
+      <c r="C20" s="174"/>
+      <c r="D20" s="143"/>
+      <c r="E20" s="129"/>
+      <c r="F20" s="129"/>
+      <c r="G20" s="129"/>
+      <c r="H20" s="130"/>
+      <c r="I20" s="129"/>
+      <c r="J20" s="129"/>
+      <c r="K20" s="129"/>
+      <c r="L20" s="131"/>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21" s="155">
+        <v>5</v>
+      </c>
+      <c r="C21" s="174" t="s">
+        <v>209</v>
+      </c>
+      <c r="D21" s="143">
+        <f>8</f>
+        <v>8</v>
+      </c>
+      <c r="E21" s="129"/>
+      <c r="F21" s="129"/>
+      <c r="G21" s="129"/>
+      <c r="H21" s="130">
+        <f t="shared" ref="H21" si="2">PRODUCT(D21:G21)</f>
+        <v>8</v>
+      </c>
+      <c r="I21" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J21" s="129">
+        <f>1.15*34</f>
+        <v>39.099999999999994</v>
+      </c>
+      <c r="K21" s="129">
+        <f>H21*J21</f>
+        <v>312.79999999999995</v>
+      </c>
+      <c r="L21" s="131"/>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22" s="155"/>
+      <c r="C22" s="174"/>
+      <c r="D22" s="143"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="129"/>
+      <c r="H22" s="130"/>
+      <c r="I22" s="129"/>
+      <c r="J22" s="129"/>
+      <c r="K22" s="129"/>
+      <c r="L22" s="131"/>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23" s="155">
+        <v>6</v>
+      </c>
+      <c r="C23" s="173" t="s">
+        <v>201</v>
+      </c>
+      <c r="D23" s="143">
+        <f>5*2</f>
+        <v>10</v>
+      </c>
+      <c r="E23" s="129">
+        <v>0.41</v>
+      </c>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129">
+        <v>0.46</v>
+      </c>
+      <c r="H23" s="130">
+        <f t="shared" si="1"/>
+        <v>1.8859999999999999</v>
+      </c>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="131"/>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24" s="155"/>
+      <c r="C24" s="171"/>
+      <c r="D24" s="213">
+        <v>36</v>
+      </c>
+      <c r="E24" s="135">
+        <v>0.43</v>
+      </c>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135">
+        <v>0.98</v>
+      </c>
+      <c r="H24" s="138">
+        <f>PRODUCT(D24:G24)</f>
+        <v>15.170400000000001</v>
+      </c>
+      <c r="I24" s="129"/>
+      <c r="J24" s="129"/>
+      <c r="K24" s="129"/>
+      <c r="L24" s="131"/>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25" s="155"/>
+      <c r="C25" s="173"/>
+      <c r="D25" s="143">
+        <v>4</v>
+      </c>
+      <c r="E25" s="129">
+        <v>0.32</v>
+      </c>
+      <c r="F25" s="129"/>
+      <c r="G25" s="129">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="H25" s="130">
+        <f t="shared" si="1"/>
+        <v>1.4336000000000002</v>
+      </c>
+      <c r="I25" s="129"/>
+      <c r="J25" s="129"/>
+      <c r="K25" s="129"/>
+      <c r="L25" s="131"/>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26" s="155"/>
+      <c r="C26" s="171"/>
+      <c r="D26" s="143">
+        <v>1</v>
+      </c>
+      <c r="E26" s="129">
+        <f>0.44</f>
+        <v>0.44</v>
+      </c>
+      <c r="F26" s="129"/>
+      <c r="G26" s="129">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="H26" s="130">
+        <f t="shared" si="1"/>
+        <v>0.42459999999999998</v>
+      </c>
+      <c r="I26" s="129"/>
+      <c r="J26" s="129"/>
+      <c r="K26" s="129"/>
+      <c r="L26" s="131"/>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27" s="155"/>
+      <c r="C27" s="171"/>
+      <c r="D27" s="143">
+        <v>1</v>
+      </c>
+      <c r="E27" s="129">
+        <v>0.43</v>
+      </c>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129">
+        <v>0.3</v>
+      </c>
+      <c r="H27" s="130">
+        <f t="shared" si="1"/>
+        <v>0.129</v>
+      </c>
+      <c r="I27" s="129"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="131"/>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28" s="155"/>
+      <c r="C28" s="140"/>
+      <c r="D28" s="129"/>
+      <c r="E28" s="129"/>
+      <c r="F28" s="129"/>
+      <c r="G28" s="129"/>
+      <c r="H28" s="129">
+        <f>SUM(H23:H27)</f>
+        <v>19.043600000000005</v>
+      </c>
+      <c r="I28" s="129" t="s">
+        <v>90</v>
+      </c>
+      <c r="J28" s="129">
+        <f>1.15*Sheet4!F8</f>
+        <v>643.44799999999998</v>
+      </c>
+      <c r="K28" s="129">
+        <f>H28*J28</f>
+        <v>12253.566332800003</v>
+      </c>
+      <c r="L28" s="131"/>
+      <c r="N28" s="1">
+        <f>CONVERT(H28,"m2","ft2")</f>
+        <v>204.98360441165332</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29" s="155"/>
+      <c r="C29" s="144"/>
+      <c r="D29" s="129"/>
+      <c r="E29" s="130"/>
+      <c r="F29" s="130"/>
+      <c r="G29" s="135"/>
+      <c r="H29" s="130"/>
+      <c r="I29" s="129"/>
+      <c r="J29" s="130"/>
+      <c r="K29" s="130"/>
+      <c r="L29" s="131"/>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30" s="155">
+        <v>7</v>
+      </c>
+      <c r="C30" s="144" t="s">
+        <v>200</v>
+      </c>
+      <c r="D30" s="129">
+        <v>4</v>
+      </c>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="135"/>
+      <c r="H30" s="130">
+        <f t="shared" ref="H30:H36" si="3">PRODUCT(D30:G30)</f>
+        <v>4</v>
+      </c>
+      <c r="I30" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J30" s="130">
+        <f>1.15*389</f>
+        <v>447.34999999999997</v>
+      </c>
+      <c r="K30" s="129">
+        <f>H30*J30</f>
+        <v>1789.3999999999999</v>
+      </c>
+      <c r="L30" s="131"/>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31" s="155"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="129"/>
+      <c r="E31" s="130"/>
+      <c r="F31" s="130"/>
+      <c r="G31" s="135"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="129"/>
+      <c r="J31" s="130"/>
+      <c r="K31" s="129"/>
+      <c r="L31" s="131"/>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32" s="155">
+        <v>8</v>
+      </c>
+      <c r="C32" s="144" t="s">
+        <v>203</v>
+      </c>
+      <c r="D32" s="129">
+        <v>3</v>
+      </c>
+      <c r="E32" s="130"/>
+      <c r="F32" s="130"/>
+      <c r="G32" s="135"/>
+      <c r="H32" s="130">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I32" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J32" s="130">
+        <f>1.15*534</f>
+        <v>614.09999999999991</v>
+      </c>
+      <c r="K32" s="129">
+        <f>H32*J32</f>
+        <v>1842.2999999999997</v>
+      </c>
+      <c r="L32" s="131"/>
+    </row>
+    <row r="33" spans="2:12">
+      <c r="B33" s="155"/>
+      <c r="C33" s="144"/>
+      <c r="D33" s="129"/>
+      <c r="E33" s="130"/>
+      <c r="F33" s="130"/>
+      <c r="G33" s="135"/>
+      <c r="H33" s="130"/>
+      <c r="I33" s="129"/>
+      <c r="J33" s="130"/>
+      <c r="K33" s="129"/>
+      <c r="L33" s="131"/>
+    </row>
+    <row r="34" spans="2:12">
+      <c r="B34" s="155">
+        <v>9</v>
+      </c>
+      <c r="C34" s="173" t="s">
+        <v>204</v>
+      </c>
+      <c r="D34" s="129">
+        <v>5</v>
+      </c>
+      <c r="E34" s="130"/>
+      <c r="F34" s="130"/>
+      <c r="G34" s="135"/>
+      <c r="H34" s="130">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="I34" s="129" t="s">
+        <v>202</v>
+      </c>
+      <c r="J34" s="130">
+        <f>1.15*221</f>
+        <v>254.14999999999998</v>
+      </c>
+      <c r="K34" s="129">
+        <f>H34*J34</f>
+        <v>1270.75</v>
+      </c>
+      <c r="L34" s="131"/>
+    </row>
+    <row r="35" spans="2:12">
+      <c r="B35" s="155"/>
+      <c r="C35" s="173"/>
+      <c r="D35" s="129"/>
+      <c r="E35" s="130"/>
+      <c r="F35" s="130"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="130"/>
+      <c r="I35" s="129"/>
+      <c r="J35" s="130"/>
+      <c r="K35" s="129"/>
+      <c r="L35" s="131"/>
+    </row>
+    <row r="36" spans="2:12">
+      <c r="B36" s="155">
+        <v>10</v>
+      </c>
+      <c r="C36" s="144" t="s">
+        <v>205</v>
+      </c>
+      <c r="D36" s="129">
+        <v>2</v>
+      </c>
+      <c r="E36" s="130"/>
+      <c r="F36" s="130"/>
+      <c r="G36" s="135"/>
+      <c r="H36" s="130">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I36" s="129" t="s">
+        <v>34</v>
+      </c>
+      <c r="J36" s="130">
+        <f>1.15*74</f>
+        <v>85.1</v>
+      </c>
+      <c r="K36" s="129">
+        <f>H36*J36</f>
+        <v>170.2</v>
+      </c>
+      <c r="L36" s="131"/>
+    </row>
+    <row r="37" spans="2:12">
+      <c r="B37" s="155"/>
+      <c r="C37" s="144"/>
+      <c r="D37" s="129"/>
+      <c r="E37" s="130"/>
+      <c r="F37" s="130"/>
+      <c r="G37" s="135"/>
+      <c r="H37" s="130"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="130"/>
+      <c r="K37" s="129"/>
+      <c r="L37" s="131"/>
+    </row>
+    <row r="38" spans="2:12" s="4" customFormat="1" ht="49.5">
+      <c r="B38" s="155">
+        <v>11</v>
+      </c>
+      <c r="C38" s="176" t="s">
+        <v>208</v>
+      </c>
+      <c r="D38" s="127">
+        <v>1</v>
+      </c>
+      <c r="E38" s="177"/>
+      <c r="F38" s="177"/>
+      <c r="G38" s="177"/>
+      <c r="H38" s="178">
+        <f>PRODUCT(D38:G38)</f>
+        <v>1</v>
+      </c>
+      <c r="I38" s="177" t="s">
+        <v>163</v>
+      </c>
+      <c r="J38" s="178">
+        <v>35000</v>
+      </c>
+      <c r="K38" s="178">
+        <f>H38*J38</f>
+        <v>35000</v>
+      </c>
+      <c r="L38" s="179"/>
+    </row>
+    <row r="39" spans="2:12">
+      <c r="B39" s="155"/>
+      <c r="C39" s="144"/>
+      <c r="D39" s="129"/>
+      <c r="E39" s="130"/>
+      <c r="F39" s="130"/>
+      <c r="G39" s="135"/>
+      <c r="H39" s="130"/>
+      <c r="I39" s="129"/>
+      <c r="J39" s="130"/>
+      <c r="K39" s="130"/>
+      <c r="L39" s="131"/>
+    </row>
+    <row r="40" spans="2:12" s="4" customFormat="1" ht="33" customHeight="1">
+      <c r="B40" s="155">
+        <v>12</v>
+      </c>
+      <c r="C40" s="176" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="127">
+        <v>0</v>
+      </c>
+      <c r="E40" s="177"/>
+      <c r="F40" s="177"/>
+      <c r="G40" s="177"/>
+      <c r="H40" s="178">
+        <f>PRODUCT(D40:G40)</f>
+        <v>0</v>
+      </c>
+      <c r="I40" s="177" t="s">
+        <v>34</v>
+      </c>
+      <c r="J40" s="178">
+        <v>500</v>
+      </c>
+      <c r="K40" s="178">
+        <f>H40*J40</f>
+        <v>0</v>
+      </c>
+      <c r="L40" s="179"/>
+    </row>
+    <row r="41" spans="2:12">
+      <c r="B41" s="148"/>
+      <c r="C41" s="149"/>
+      <c r="D41" s="129"/>
+      <c r="E41" s="130"/>
+      <c r="F41" s="130"/>
+      <c r="G41" s="130"/>
+      <c r="H41" s="130"/>
+      <c r="I41" s="129"/>
+      <c r="J41" s="130"/>
+      <c r="K41" s="150">
+        <f>SUM(K10:K40)</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="L41" s="151"/>
+    </row>
+    <row r="42" spans="2:12">
+      <c r="C42" s="9"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="10"/>
+      <c r="K42" s="118"/>
+      <c r="L42" s="8"/>
+    </row>
+    <row r="43" spans="2:12" hidden="1">
+      <c r="C43" s="134" t="s">
+        <v>212</v>
+      </c>
+      <c r="D43" s="182">
+        <f>+K41</f>
+        <v>70309.500691152003</v>
+      </c>
+      <c r="E43" s="182"/>
+      <c r="G43" s="64"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="1"/>
+    </row>
+    <row r="44" spans="2:12" hidden="1">
+      <c r="C44" s="134" t="s">
+        <v>171</v>
+      </c>
+      <c r="D44" s="182">
+        <f>13%*D43</f>
+        <v>9140.2350898497607</v>
+      </c>
+      <c r="E44" s="182"/>
+      <c r="G44" s="64"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="1"/>
+    </row>
+    <row r="45" spans="2:12" hidden="1">
+      <c r="C45" s="151" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="182">
+        <f>SUM(D43:E44)</f>
+        <v>79449.735781001771</v>
+      </c>
+      <c r="E45" s="183"/>
+      <c r="G45" s="62"/>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="A4:L4"/>
+    <mergeCell ref="B6:G6"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.511811023622047" right="0.511811023622047" top="0.39370078740157499" bottom="0.70866141732283505" header="0.31496062992126" footer="0.31496062992126"/>
+  <pageSetup paperSize="9" fitToHeight="2" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;RPage &amp;P of &amp;N</oddHeader>
+    <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3EDFBFC3-6CBB-4427-8EDC-BA8E637E0A67}">
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
@@ -7848,68 +12351,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -7917,27 +12420,27 @@
         <v>181</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -8231,11 +12734,11 @@
       <c r="C20" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="180">
+      <c r="D20" s="182">
         <f>+K18</f>
         <v>84443.872931622609</v>
       </c>
-      <c r="E20" s="180"/>
+      <c r="E20" s="182"/>
       <c r="G20" s="64"/>
       <c r="I20" s="2"/>
       <c r="J20" s="1"/>
@@ -8244,11 +12747,11 @@
       <c r="C21" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="180">
+      <c r="D21" s="182">
         <f>13%*D20</f>
         <v>10977.703481110939</v>
       </c>
-      <c r="E21" s="180"/>
+      <c r="E21" s="182"/>
       <c r="G21" s="64"/>
       <c r="I21" s="2"/>
       <c r="J21" s="1"/>
@@ -8257,11 +12760,11 @@
       <c r="C22" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="180">
+      <c r="D22" s="182">
         <f>SUM(D20:E21)</f>
         <v>95421.576412733542</v>
       </c>
-      <c r="E22" s="181"/>
+      <c r="E22" s="183"/>
       <c r="G22" s="62"/>
     </row>
   </sheetData>
@@ -8287,7 +12790,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6739B77E-58D6-4632-8521-12A45F420915}">
   <dimension ref="A1:L22"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5"/>
@@ -8308,68 +12811,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -8377,27 +12880,27 @@
         <v>181</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -8691,11 +13194,11 @@
       <c r="C20" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="180">
+      <c r="D20" s="182">
         <f>+K18</f>
         <v>84443.872931622609</v>
       </c>
-      <c r="E20" s="180"/>
+      <c r="E20" s="182"/>
       <c r="G20" s="64"/>
       <c r="I20" s="2"/>
       <c r="J20" s="1"/>
@@ -8704,11 +13207,11 @@
       <c r="C21" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="180">
+      <c r="D21" s="182">
         <f>13%*D20</f>
         <v>10977.703481110939</v>
       </c>
-      <c r="E21" s="180"/>
+      <c r="E21" s="182"/>
       <c r="G21" s="64"/>
       <c r="I21" s="2"/>
       <c r="J21" s="1"/>
@@ -8717,11 +13220,11 @@
       <c r="C22" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="180">
+      <c r="D22" s="182">
         <f>SUM(D20:E21)</f>
         <v>95421.576412733542</v>
       </c>
-      <c r="E22" s="181"/>
+      <c r="E22" s="183"/>
       <c r="G22" s="62"/>
     </row>
   </sheetData>
@@ -8765,60 +13268,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="188" t="s">
+      <c r="A1" s="190" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="188"/>
-      <c r="C1" s="188"/>
-      <c r="D1" s="188"/>
-      <c r="E1" s="188"/>
-      <c r="F1" s="188"/>
-      <c r="G1" s="188"/>
-      <c r="H1" s="188"/>
-      <c r="I1" s="188"/>
-      <c r="J1" s="188"/>
+      <c r="B1" s="190"/>
+      <c r="C1" s="190"/>
+      <c r="D1" s="190"/>
+      <c r="E1" s="190"/>
+      <c r="F1" s="190"/>
+      <c r="G1" s="190"/>
+      <c r="H1" s="190"/>
+      <c r="I1" s="190"/>
+      <c r="J1" s="190"/>
     </row>
     <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="189" t="s">
+      <c r="A2" s="191" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="189"/>
-      <c r="C2" s="189"/>
-      <c r="D2" s="189"/>
-      <c r="E2" s="189"/>
-      <c r="F2" s="189"/>
-      <c r="G2" s="189"/>
-      <c r="H2" s="189"/>
-      <c r="I2" s="189"/>
-      <c r="J2" s="189"/>
+      <c r="B2" s="191"/>
+      <c r="C2" s="191"/>
+      <c r="D2" s="191"/>
+      <c r="E2" s="191"/>
+      <c r="F2" s="191"/>
+      <c r="G2" s="191"/>
+      <c r="H2" s="191"/>
+      <c r="I2" s="191"/>
+      <c r="J2" s="191"/>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="190" t="s">
+      <c r="A3" s="192" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="190"/>
-      <c r="C3" s="190"/>
-      <c r="D3" s="190"/>
-      <c r="E3" s="190"/>
-      <c r="F3" s="190"/>
-      <c r="G3" s="190"/>
-      <c r="H3" s="190"/>
-      <c r="I3" s="190"/>
-      <c r="J3" s="190"/>
+      <c r="B3" s="192"/>
+      <c r="C3" s="192"/>
+      <c r="D3" s="192"/>
+      <c r="E3" s="192"/>
+      <c r="F3" s="192"/>
+      <c r="G3" s="192"/>
+      <c r="H3" s="192"/>
+      <c r="I3" s="192"/>
+      <c r="J3" s="192"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="191" t="s">
+      <c r="A4" s="193" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="191"/>
-      <c r="C4" s="191"/>
-      <c r="D4" s="191"/>
-      <c r="E4" s="191"/>
-      <c r="F4" s="191"/>
-      <c r="G4" s="191"/>
-      <c r="H4" s="191"/>
-      <c r="I4" s="191"/>
-      <c r="J4" s="191"/>
+      <c r="B4" s="193"/>
+      <c r="C4" s="193"/>
+      <c r="D4" s="193"/>
+      <c r="E4" s="193"/>
+      <c r="F4" s="193"/>
+      <c r="G4" s="193"/>
+      <c r="H4" s="193"/>
+      <c r="I4" s="193"/>
+      <c r="J4" s="193"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -8837,33 +13340,33 @@
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="192" t="e">
+      <c r="C6" s="194" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="193"/>
+      <c r="D6" s="195"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="192" t="e">
+      <c r="I6" s="194" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="193"/>
+      <c r="J6" s="195"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="194"/>
-      <c r="D7" s="194"/>
-      <c r="E7" s="194"/>
-      <c r="F7" s="194"/>
-      <c r="H7" s="195"/>
-      <c r="I7" s="195"/>
-      <c r="J7" s="195"/>
+      <c r="C7" s="196"/>
+      <c r="D7" s="196"/>
+      <c r="E7" s="196"/>
+      <c r="F7" s="196"/>
+      <c r="H7" s="197"/>
+      <c r="I7" s="197"/>
+      <c r="J7" s="197"/>
     </row>
     <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
@@ -8890,32 +13393,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="196" t="s">
+      <c r="A10" s="198" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="196" t="s">
+      <c r="B10" s="198" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="198" t="s">
+      <c r="C10" s="200" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="198"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="198" t="s">
+      <c r="D10" s="200"/>
+      <c r="E10" s="200"/>
+      <c r="F10" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="198"/>
-      <c r="H10" s="198"/>
-      <c r="I10" s="196" t="s">
+      <c r="G10" s="200"/>
+      <c r="H10" s="200"/>
+      <c r="I10" s="198" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="196" t="s">
+      <c r="J10" s="198" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="197"/>
-      <c r="B11" s="197"/>
+      <c r="A11" s="199"/>
+      <c r="B11" s="199"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -8934,8 +13437,8 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="197"/>
-      <c r="J11" s="197"/>
+      <c r="I11" s="199"/>
+      <c r="J11" s="199"/>
     </row>
     <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="47">
@@ -9913,68 +14416,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -9982,27 +14485,27 @@
         <v>168</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -13160,10 +17663,10 @@
       <c r="C156" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="D156" s="200" t="s">
+      <c r="D156" s="202" t="s">
         <v>71</v>
       </c>
-      <c r="E156" s="200"/>
+      <c r="E156" s="202"/>
       <c r="F156" s="124" t="s">
         <v>72</v>
       </c>
@@ -13173,11 +17676,11 @@
       <c r="C157" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D157" s="180">
+      <c r="D157" s="182">
         <f>+K154</f>
         <v>877810.68270516139</v>
       </c>
-      <c r="E157" s="180"/>
+      <c r="E157" s="182"/>
       <c r="F157" s="152"/>
       <c r="H157" s="64"/>
     </row>
@@ -13185,10 +17688,10 @@
       <c r="C158" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="D158" s="180">
+      <c r="D158" s="182">
         <v>200000</v>
       </c>
-      <c r="E158" s="180"/>
+      <c r="E158" s="182"/>
       <c r="F158" s="153">
         <v>100</v>
       </c>
@@ -13198,11 +17701,11 @@
       <c r="C159" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="D159" s="180">
+      <c r="D159" s="182">
         <f>0.95*D158</f>
         <v>190000</v>
       </c>
-      <c r="E159" s="180"/>
+      <c r="E159" s="182"/>
       <c r="F159" s="153">
         <f>D159/D157*100</f>
         <v>21.644758231293604</v>
@@ -13213,11 +17716,11 @@
       <c r="C160" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="D160" s="180">
+      <c r="D160" s="182">
         <f>D157-D159</f>
         <v>687810.68270516139</v>
       </c>
-      <c r="E160" s="180"/>
+      <c r="E160" s="182"/>
       <c r="F160" s="153">
         <f>D160/D158*100</f>
         <v>343.90534135258071</v>
@@ -13228,11 +17731,11 @@
       <c r="C161" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="D161" s="180">
+      <c r="D161" s="182">
         <f>F161*D158/100</f>
         <v>4000</v>
       </c>
-      <c r="E161" s="180"/>
+      <c r="E161" s="182"/>
       <c r="F161" s="153">
         <v>2</v>
       </c>
@@ -13242,11 +17745,11 @@
       <c r="C162" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="D162" s="199">
+      <c r="D162" s="201">
         <f>F162*D158/100</f>
         <v>6000</v>
       </c>
-      <c r="E162" s="199"/>
+      <c r="E162" s="201"/>
       <c r="F162" s="153">
         <v>3</v>
       </c>
@@ -13299,29 +17802,29 @@
       <c r="A1" s="90">
         <v>152</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="203" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
     </row>
     <row r="2" spans="1:8" ht="15.75">
       <c r="A2" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="205" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="206"/>
     </row>
     <row r="3" spans="1:8" ht="31.5">
       <c r="A3" s="92"/>
@@ -13349,7 +17852,7 @@
     </row>
     <row r="4" spans="1:8" ht="16.5">
       <c r="A4" s="92"/>
-      <c r="B4" s="205" t="s">
+      <c r="B4" s="207" t="s">
         <v>116</v>
       </c>
       <c r="C4" s="94" t="s">
@@ -13372,7 +17875,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.5">
       <c r="A5" s="92"/>
-      <c r="B5" s="206"/>
+      <c r="B5" s="208"/>
       <c r="C5" s="99" t="s">
         <v>119</v>
       </c>
@@ -13396,7 +17899,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.5">
       <c r="A6" s="92"/>
-      <c r="B6" s="207" t="s">
+      <c r="B6" s="209" t="s">
         <v>120</v>
       </c>
       <c r="C6" s="96" t="s">
@@ -13420,7 +17923,7 @@
     </row>
     <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="92"/>
-      <c r="B7" s="208"/>
+      <c r="B7" s="210"/>
       <c r="C7" s="99" t="s">
         <v>123</v>
       </c>
@@ -13545,68 +18048,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -13614,27 +18117,27 @@
         <v>173</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -13979,11 +18482,11 @@
       <c r="C22" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="180">
+      <c r="D22" s="182">
         <f>+K20</f>
         <v>152392.78213992011</v>
       </c>
-      <c r="E22" s="180"/>
+      <c r="E22" s="182"/>
       <c r="G22" s="64"/>
       <c r="I22" s="2"/>
       <c r="J22" s="1"/>
@@ -13992,11 +18495,11 @@
       <c r="C23" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="180">
+      <c r="D23" s="182">
         <f>13%*D22</f>
         <v>19811.061678189613</v>
       </c>
-      <c r="E23" s="180"/>
+      <c r="E23" s="182"/>
       <c r="G23" s="64"/>
       <c r="I23" s="2"/>
       <c r="J23" s="1"/>
@@ -14005,11 +18508,11 @@
       <c r="C24" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="180">
+      <c r="D24" s="182">
         <f>SUM(D22:E23)</f>
         <v>172203.84381810972</v>
       </c>
-      <c r="E24" s="181"/>
+      <c r="E24" s="183"/>
       <c r="G24" s="62"/>
     </row>
   </sheetData>
@@ -14056,68 +18559,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -14125,27 +18628,27 @@
         <v>173</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -14723,11 +19226,11 @@
       <c r="C32" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="180">
+      <c r="D32" s="182">
         <f>+K30</f>
         <v>136152.90338529783</v>
       </c>
-      <c r="E32" s="180"/>
+      <c r="E32" s="182"/>
       <c r="G32" s="64"/>
       <c r="I32" s="2"/>
       <c r="J32" s="1"/>
@@ -14736,11 +19239,11 @@
       <c r="C33" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="180">
+      <c r="D33" s="182">
         <f>13%*D32</f>
         <v>17699.87744008872</v>
       </c>
-      <c r="E33" s="180"/>
+      <c r="E33" s="182"/>
       <c r="G33" s="64"/>
       <c r="I33" s="2"/>
       <c r="J33" s="1"/>
@@ -14749,11 +19252,11 @@
       <c r="C34" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D34" s="180">
+      <c r="D34" s="182">
         <f>SUM(D32:E33)</f>
         <v>153852.78082538655</v>
       </c>
-      <c r="E34" s="181"/>
+      <c r="E34" s="183"/>
       <c r="G34" s="62"/>
     </row>
   </sheetData>
@@ -14799,68 +19302,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -14868,27 +19371,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -15104,11 +19607,11 @@
       <c r="C17" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="180">
+      <c r="D17" s="182">
         <f>+K15</f>
         <v>82403.803018409788</v>
       </c>
-      <c r="E17" s="180"/>
+      <c r="E17" s="182"/>
       <c r="G17" s="64"/>
       <c r="I17" s="2"/>
       <c r="J17" s="1"/>
@@ -15117,11 +19620,11 @@
       <c r="C18" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="180">
+      <c r="D18" s="182">
         <f>13%*D17</f>
         <v>10712.494392393273</v>
       </c>
-      <c r="E18" s="180"/>
+      <c r="E18" s="182"/>
       <c r="G18" s="64"/>
       <c r="I18" s="2"/>
       <c r="J18" s="1"/>
@@ -15130,11 +19633,11 @@
       <c r="C19" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="180">
+      <c r="D19" s="182">
         <f>SUM(D17:E18)</f>
         <v>93116.297410803061</v>
       </c>
-      <c r="E19" s="181"/>
+      <c r="E19" s="183"/>
       <c r="G19" s="62"/>
     </row>
   </sheetData>
@@ -15181,68 +19684,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="182" t="s">
+      <c r="A1" s="184" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="182"/>
-      <c r="C1" s="182"/>
-      <c r="D1" s="182"/>
-      <c r="E1" s="182"/>
-      <c r="F1" s="182"/>
-      <c r="G1" s="182"/>
-      <c r="H1" s="182"/>
-      <c r="I1" s="182"/>
-      <c r="J1" s="182"/>
-      <c r="K1" s="182"/>
-      <c r="L1" s="182"/>
+      <c r="B1" s="184"/>
+      <c r="C1" s="184"/>
+      <c r="D1" s="184"/>
+      <c r="E1" s="184"/>
+      <c r="F1" s="184"/>
+      <c r="G1" s="184"/>
+      <c r="H1" s="184"/>
+      <c r="I1" s="184"/>
+      <c r="J1" s="184"/>
+      <c r="K1" s="184"/>
+      <c r="L1" s="184"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="183" t="s">
+      <c r="A2" s="185" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="183"/>
-      <c r="C2" s="183"/>
-      <c r="D2" s="183"/>
-      <c r="E2" s="183"/>
-      <c r="F2" s="183"/>
-      <c r="G2" s="183"/>
-      <c r="H2" s="183"/>
-      <c r="I2" s="183"/>
-      <c r="J2" s="183"/>
-      <c r="K2" s="183"/>
-      <c r="L2" s="183"/>
+      <c r="B2" s="185"/>
+      <c r="C2" s="185"/>
+      <c r="D2" s="185"/>
+      <c r="E2" s="185"/>
+      <c r="F2" s="185"/>
+      <c r="G2" s="185"/>
+      <c r="H2" s="185"/>
+      <c r="I2" s="185"/>
+      <c r="J2" s="185"/>
+      <c r="K2" s="185"/>
+      <c r="L2" s="185"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="182" t="s">
+      <c r="A3" s="184" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="182"/>
-      <c r="C3" s="182"/>
-      <c r="D3" s="182"/>
-      <c r="E3" s="182"/>
-      <c r="F3" s="182"/>
-      <c r="G3" s="182"/>
-      <c r="H3" s="182"/>
-      <c r="I3" s="182"/>
-      <c r="J3" s="182"/>
-      <c r="K3" s="182"/>
-      <c r="L3" s="182"/>
+      <c r="B3" s="184"/>
+      <c r="C3" s="184"/>
+      <c r="D3" s="184"/>
+      <c r="E3" s="184"/>
+      <c r="F3" s="184"/>
+      <c r="G3" s="184"/>
+      <c r="H3" s="184"/>
+      <c r="I3" s="184"/>
+      <c r="J3" s="184"/>
+      <c r="K3" s="184"/>
+      <c r="L3" s="184"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="184" t="s">
+      <c r="A4" s="186" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="184"/>
-      <c r="C4" s="184"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="184"/>
-      <c r="F4" s="184"/>
-      <c r="G4" s="184"/>
-      <c r="H4" s="184"/>
-      <c r="I4" s="184"/>
-      <c r="J4" s="184"/>
-      <c r="K4" s="184"/>
-      <c r="L4" s="184"/>
+      <c r="B4" s="186"/>
+      <c r="C4" s="186"/>
+      <c r="D4" s="186"/>
+      <c r="E4" s="186"/>
+      <c r="F4" s="186"/>
+      <c r="G4" s="186"/>
+      <c r="H4" s="186"/>
+      <c r="I4" s="186"/>
+      <c r="J4" s="186"/>
+      <c r="K4" s="186"/>
+      <c r="L4" s="186"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -15250,27 +19753,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="185" t="s">
+      <c r="K5" s="187" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="185"/>
+      <c r="L5" s="187"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="186" t="s">
+      <c r="B6" s="188" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="186"/>
-      <c r="D6" s="186"/>
-      <c r="E6" s="186"/>
-      <c r="F6" s="186"/>
-      <c r="G6" s="186"/>
+      <c r="C6" s="188"/>
+      <c r="D6" s="188"/>
+      <c r="E6" s="188"/>
+      <c r="F6" s="188"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="187" t="s">
+      <c r="I6" s="189" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="187"/>
-      <c r="K6" s="187"/>
-      <c r="L6" s="187"/>
+      <c r="J6" s="189"/>
+      <c r="K6" s="189"/>
+      <c r="L6" s="189"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -15921,11 +20424,11 @@
       <c r="C37" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="180">
+      <c r="D37" s="182">
         <f>+K35</f>
         <v>56595.388680275566</v>
       </c>
-      <c r="E37" s="180"/>
+      <c r="E37" s="182"/>
       <c r="G37" s="64"/>
       <c r="I37" s="2"/>
       <c r="J37" s="1"/>
@@ -15934,11 +20437,11 @@
       <c r="C38" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D38" s="180">
+      <c r="D38" s="182">
         <f>13%*D37</f>
         <v>7357.4005284358236</v>
       </c>
-      <c r="E38" s="180"/>
+      <c r="E38" s="182"/>
       <c r="G38" s="64"/>
       <c r="I38" s="2"/>
       <c r="J38" s="1"/>
@@ -15947,11 +20450,11 @@
       <c r="C39" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="180">
+      <c r="D39" s="182">
         <f>SUM(D37:E38)</f>
         <v>63952.789208711387</v>
       </c>
-      <c r="E39" s="181"/>
+      <c r="E39" s="183"/>
       <c r="G39" s="62"/>
     </row>
   </sheetData>
@@ -15991,41 +20494,41 @@
         <f>#REF!+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="201" t="s">
+      <c r="B1" s="203" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="202"/>
-      <c r="D1" s="202"/>
-      <c r="E1" s="202"/>
-      <c r="F1" s="202"/>
-      <c r="G1" s="202"/>
-      <c r="H1" s="202"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
+      <c r="G1" s="204"/>
+      <c r="H1" s="204"/>
     </row>
     <row r="2" spans="1:8" ht="19.5">
       <c r="A2" s="170" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="203" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="202"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="202"/>
-      <c r="F2" s="202"/>
-      <c r="G2" s="202"/>
-      <c r="H2" s="202"/>
+      <c r="C2" s="204"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="204"/>
     </row>
     <row r="3" spans="1:8" ht="15.75">
       <c r="A3" s="92"/>
-      <c r="B3" s="204" t="s">
+      <c r="B3" s="206" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="204"/>
-      <c r="D3" s="204"/>
-      <c r="E3" s="204"/>
-      <c r="F3" s="204"/>
-      <c r="G3" s="204"/>
-      <c r="H3" s="204"/>
+      <c r="C3" s="206"/>
+      <c r="D3" s="206"/>
+      <c r="E3" s="206"/>
+      <c r="F3" s="206"/>
+      <c r="G3" s="206"/>
+      <c r="H3" s="206"/>
     </row>
     <row r="4" spans="1:8" ht="63">
       <c r="A4" s="92"/>
@@ -16053,7 +20556,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.5">
       <c r="A5" s="92"/>
-      <c r="B5" s="205" t="s">
+      <c r="B5" s="207" t="s">
         <v>116</v>
       </c>
       <c r="C5" s="94" t="s">
@@ -16076,7 +20579,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.5">
       <c r="A6" s="92"/>
-      <c r="B6" s="209"/>
+      <c r="B6" s="211"/>
       <c r="C6" s="99" t="s">
         <v>119</v>
       </c>
@@ -16100,7 +20603,7 @@
     </row>
     <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="92"/>
-      <c r="B7" s="207" t="s">
+      <c r="B7" s="209" t="s">
         <v>120</v>
       </c>
       <c r="C7" s="96" t="s">
@@ -16123,7 +20626,7 @@
     </row>
     <row r="8" spans="1:8" ht="16.5">
       <c r="A8" s="92"/>
-      <c r="B8" s="210"/>
+      <c r="B8" s="212"/>
       <c r="C8" s="163" t="s">
         <v>196</v>
       </c>
@@ -16144,7 +20647,7 @@
     </row>
     <row r="9" spans="1:8" ht="16.5">
       <c r="A9" s="92"/>
-      <c r="B9" s="210"/>
+      <c r="B9" s="212"/>
       <c r="C9" s="163" t="s">
         <v>188</v>
       </c>
@@ -16165,7 +20668,7 @@
     </row>
     <row r="10" spans="1:8" ht="16.5">
       <c r="A10" s="92"/>
-      <c r="B10" s="210"/>
+      <c r="B10" s="212"/>
       <c r="C10" s="163" t="s">
         <v>189</v>
       </c>
@@ -16186,7 +20689,7 @@
     </row>
     <row r="11" spans="1:8" ht="16.5">
       <c r="A11" s="92"/>
-      <c r="B11" s="210"/>
+      <c r="B11" s="212"/>
       <c r="C11" s="163" t="s">
         <v>190</v>
       </c>
@@ -16207,7 +20710,7 @@
     </row>
     <row r="12" spans="1:8" ht="16.5">
       <c r="A12" s="92"/>
-      <c r="B12" s="208"/>
+      <c r="B12" s="210"/>
       <c r="C12" s="99" t="s">
         <v>191</v>
       </c>

--- a/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
+++ b/बजेट माग estimate/nagar bhaipari and estimate misc/hawa huri jhyal/hawa huri jhyal 2082_2083.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\बजेट माग estimate\nagar bhaipari and estimate misc\hawa huri jhyal\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A33154DA-5074-42ED-8C38-5B287369D9C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEA2042-F912-4B52-A47E-34C84938DC0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="10" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="10" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ESTIMATE" sheetId="25" state="hidden" r:id="rId1"/>
@@ -40,31 +40,30 @@
     <externalReference r:id="rId23"/>
     <externalReference r:id="rId24"/>
     <externalReference r:id="rId25"/>
-    <externalReference r:id="rId26"/>
   </externalReferences>
   <definedNames>
     <definedName name="cheskini100">'[1]update Rate'!$O$64</definedName>
-    <definedName name="description_103">[4]Abstract!$B$16</definedName>
+    <definedName name="description_103">[2]Abstract!$B$16</definedName>
     <definedName name="description_124" localSheetId="11">#REF!</definedName>
     <definedName name="description_124">#REF!</definedName>
-    <definedName name="description_247">[4]Abstract!$B$22</definedName>
-    <definedName name="description_248">[4]Abstract!$B$23</definedName>
-    <definedName name="description_261">[6]Abstract!$B$33</definedName>
-    <definedName name="description_262">[4]Abstract!$B$34</definedName>
-    <definedName name="description_276">[7]Abstract!$B$40</definedName>
-    <definedName name="description_3">[4]Abstract!$B$169</definedName>
-    <definedName name="description_310" localSheetId="11">[8]Abstract!$B$60</definedName>
+    <definedName name="description_247">[2]Abstract!$B$22</definedName>
+    <definedName name="description_248">[2]Abstract!$B$23</definedName>
+    <definedName name="description_261">[3]Abstract!$B$33</definedName>
+    <definedName name="description_262">[2]Abstract!$B$34</definedName>
+    <definedName name="description_276">[4]Abstract!$B$40</definedName>
+    <definedName name="description_3">[2]Abstract!$B$169</definedName>
+    <definedName name="description_310" localSheetId="11">[5]Abstract!$B$60</definedName>
     <definedName name="description_310">#REF!</definedName>
-    <definedName name="description_312" localSheetId="11">[9]Abstract!$B$61</definedName>
+    <definedName name="description_312" localSheetId="11">[6]Abstract!$B$61</definedName>
     <definedName name="description_312">#REF!</definedName>
-    <definedName name="description_5">[4]Abstract!$B$171</definedName>
-    <definedName name="description_6" localSheetId="11">[8]Abstract!$B$172</definedName>
+    <definedName name="description_5">[2]Abstract!$B$171</definedName>
+    <definedName name="description_6" localSheetId="11">[5]Abstract!$B$172</definedName>
     <definedName name="description_6">#REF!</definedName>
-    <definedName name="description_759">[4]Abstract!$B$278</definedName>
-    <definedName name="description_781" localSheetId="11">[10]Abstract!$B$299</definedName>
+    <definedName name="description_759">[2]Abstract!$B$278</definedName>
+    <definedName name="description_781" localSheetId="11">[7]Abstract!$B$299</definedName>
     <definedName name="description_781">#REF!</definedName>
-    <definedName name="description_783">[4]Abstract!$B$301</definedName>
-    <definedName name="description_784">[7]Abstract!$B$300</definedName>
+    <definedName name="description_783">[2]Abstract!$B$301</definedName>
+    <definedName name="description_784">[4]Abstract!$B$300</definedName>
     <definedName name="glass4">'[1]update Rate'!$O$88</definedName>
     <definedName name="kabja75">'[1]update Rate'!$O$63</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'&lt;1000000'!$A$1:$L$24</definedName>
@@ -1110,7 +1109,7 @@
     <t>Detail Quantity Measurement Sheet</t>
   </si>
   <si>
-    <t>Date: 2083/03/05</t>
+    <t>Date: 2083/01/22</t>
   </si>
 </sst>
 </file>
@@ -3203,7 +3202,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="237">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3654,126 +3653,14 @@
     <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="80" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="182" fontId="52" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="60" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3806,7 +3693,118 @@
     </xf>
     <xf numFmtId="2" fontId="59" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="59" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="32" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="63" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="32" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="51" fillId="0" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="759">
     <cellStyle name="??" xfId="476" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -4826,7 +4824,347 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="16">
+          <cell r="B16" t="str">
+            <v>Clearing and Grubbing Road Land ., Clearing and grubbing road land including uprooting rank vegetation, grass, bushes, shrubs, saplings and trees girth up to 300 mm, removal of stumps of trees cut earlier and disposal of unserviceable materials and stacking of serviceable Material to be used or auctioned, up to a lead of 30 meters including removal and disposal of top organic soil not exceeding 150 mm in thickness., By Mechanical Means, In area of light jungle (less than 15 number per 100 sqm )</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="B22" t="str">
+            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 450 mm  internal dia.</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="B23" t="str">
+            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 600 mm  internal dia.</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="B34" t="str">
+            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Mechanical  Means ., Road way Excavation in  all types of soil as per Drawing and technical specifications  including  removal of stumps and other deleterious matter, all lifts and lead as per Drawing and instruction of the Engineer.</v>
+          </cell>
+        </row>
+        <row r="169">
+          <cell r="B169" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</v>
+          </cell>
+        </row>
+        <row r="171">
+          <cell r="B171" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 20</v>
+          </cell>
+        </row>
+        <row r="278">
+          <cell r="B278" t="str">
+            <v>Providing and laying Brick Masonry Work in Cement mortar  in Foundation / structure complete excluding Pointing and Plastering, as per Drawing and Technical Specifications., Cement sand mortar (1:6)</v>
+          </cell>
+        </row>
+        <row r="301">
+          <cell r="B301" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="33">
+          <cell r="B33" t="str">
+            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Manual Means ., Roadway Excavation in all types of soil as per drawing and technical specification, including removal of stumps and other deleterious matter, with all lifts and lead as per Drawing and instruction of the Engineer.</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="40">
+          <cell r="B40" t="str">
+            <v>Excavation for Structures Foundation, Earth work in excavation of foundation of structures, including  construction of shoring and bracing, removal of stumps and other deleterious matter and backfilling with approved Material as per Drawing and Technical Specifications., Ordinary soil by Mechanical Means, Depth upto 3 m</v>
+          </cell>
+        </row>
+        <row r="300">
+          <cell r="B300" t="str">
+            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications., Using Concrete Mixer</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1">
+        <row r="60">
+          <cell r="B60" t="str">
+            <v>Providing and laying of hand pack Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
+          </cell>
+        </row>
+        <row r="172">
+          <cell r="B172" t="str">
+            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9" refreshError="1"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="Datasheet"/>
+      <sheetName val="Abstract"/>
+      <sheetName val="Quantity_Sheet"/>
+      <sheetName val="District_Rate"/>
+      <sheetName val="Equipment_Rate"/>
+      <sheetName val="Summary_of_Rates"/>
+      <sheetName val="rate (roadway)"/>
+      <sheetName val="manhole"/>
+      <sheetName val="bistar"/>
+      <sheetName val="Rate_Analysis"/>
+      <sheetName val="DWC pipe Rate-analysis"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
+      <sheetName val="Sheet3"/>
+      <sheetName val="Sheet4"/>
+      <sheetName val="Loading_Unloading"/>
+      <sheetName val="Collection"/>
+      <sheetName val="Transportation"/>
+      <sheetName val="References"/>
+      <sheetName val="BOQ"/>
+      <sheetName val="PPMO_BOQ"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1">
+        <row r="61">
+          <cell r="B61" t="str">
+            <v>Providing and laying  granular sub-base   on prepared surface, mixing  at OMC, and compacting  to achieve the desired density, complete as per Drawing and Technical Specifications., By Mechanical means</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10"/>
+      <sheetData sheetId="11"/>
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18"/>
+      <sheetData sheetId="19"/>
+      <sheetData sheetId="20"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -4885,7 +5223,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5034,7 +5372,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -5077,371 +5415,6 @@
       <sheetData sheetId="10" refreshError="1"/>
       <sheetData sheetId="11" refreshError="1"/>
       <sheetData sheetId="12" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Datasheet"/>
-      <sheetName val="Abstract"/>
-      <sheetName val="Quantity_Sheet"/>
-      <sheetName val="District_Rate"/>
-      <sheetName val="Equipment_Rate"/>
-      <sheetName val="Summary_of_Rates"/>
-      <sheetName val="rate (roadway)"/>
-      <sheetName val="manhole"/>
-      <sheetName val="bistar"/>
-      <sheetName val="Rate_Analysis"/>
-      <sheetName val="DWC pipe Rate-analysis"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Loading_Unloading"/>
-      <sheetName val="Collection"/>
-      <sheetName val="Transportation"/>
-      <sheetName val="References"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="PPMO_BOQ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="16">
-          <cell r="B16" t="str">
-            <v>Clearing and Grubbing Road Land ., Clearing and grubbing road land including uprooting rank vegetation, grass, bushes, shrubs, saplings and trees girth up to 300 mm, removal of stumps of trees cut earlier and disposal of unserviceable materials and stacking of serviceable Material to be used or auctioned, up to a lead of 30 meters including removal and disposal of top organic soil not exceeding 150 mm in thickness., By Mechanical Means, In area of light jungle (less than 15 number per 100 sqm )</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="B22" t="str">
-            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 450 mm  internal dia.</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="B23" t="str">
-            <v>Providing and Laying Reinforced cement concrete NP3 Flush jointed pipe for culverts including fixing with cement mortar 1:2 as per Drawing and Technical Specifications., 600 mm  internal dia.</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="B34" t="str">
-            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Mechanical  Means ., Road way Excavation in  all types of soil as per Drawing and technical specifications  including  removal of stumps and other deleterious matter, all lifts and lead as per Drawing and instruction of the Engineer.</v>
-          </cell>
-        </row>
-        <row r="169">
-          <cell r="B169" t="str">
-            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 15</v>
-          </cell>
-        </row>
-        <row r="171">
-          <cell r="B171" t="str">
-            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications, PCC Grade M 20</v>
-          </cell>
-        </row>
-        <row r="278">
-          <cell r="B278" t="str">
-            <v>Providing and laying Brick Masonry Work in Cement mortar  in Foundation / structure complete excluding Pointing and Plastering, as per Drawing and Technical Specifications., Cement sand mortar (1:6)</v>
-          </cell>
-        </row>
-        <row r="301">
-          <cell r="B301" t="str">
-            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications.</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-      <xxl21:relativeUrl r:id="rId3"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="estimate"/>
-      <sheetName val="WCR"/>
-      <sheetName val="V"/>
-      <sheetName val="M"/>
-      <sheetName val="original estimate"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Datasheet"/>
-      <sheetName val="Abstract"/>
-      <sheetName val="Quantity_Sheet"/>
-      <sheetName val="District_Rate"/>
-      <sheetName val="Equipment_Rate"/>
-      <sheetName val="Summary_of_Rates"/>
-      <sheetName val="rate (roadway)"/>
-      <sheetName val="manhole"/>
-      <sheetName val="bistar"/>
-      <sheetName val="Rate_Analysis"/>
-      <sheetName val="DWC pipe Rate-analysis"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Loading_Unloading"/>
-      <sheetName val="Collection"/>
-      <sheetName val="Transportation"/>
-      <sheetName val="References"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="PPMO_BOQ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="33">
-          <cell r="B33" t="str">
-            <v>Earthwork Excavation in Cutting., Roadway Excavation in all types of Soil by Manual Means ., Roadway Excavation in all types of soil as per drawing and technical specification, including removal of stumps and other deleterious matter, with all lifts and lead as per Drawing and instruction of the Engineer.</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink7.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Datasheet"/>
-      <sheetName val="Abstract"/>
-      <sheetName val="Quantity_Sheet"/>
-      <sheetName val="District_Rate"/>
-      <sheetName val="Equipment_Rate"/>
-      <sheetName val="Summary_of_Rates"/>
-      <sheetName val="rate (roadway)"/>
-      <sheetName val="manhole"/>
-      <sheetName val="bistar"/>
-      <sheetName val="Rate_Analysis"/>
-      <sheetName val="DWC pipe Rate-analysis"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Loading_Unloading"/>
-      <sheetName val="Collection"/>
-      <sheetName val="Transportation"/>
-      <sheetName val="References"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="PPMO_BOQ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="40">
-          <cell r="B40" t="str">
-            <v>Excavation for Structures Foundation, Earth work in excavation of foundation of structures, including  construction of shoring and bracing, removal of stumps and other deleterious matter and backfilling with approved Material as per Drawing and Technical Specifications., Ordinary soil by Mechanical Means, Depth upto 3 m</v>
-          </cell>
-        </row>
-        <row r="300">
-          <cell r="B300" t="str">
-            <v>Random Rubble Masonry, Providing and laying of Stone Masonry Work in Cement Mortar 1:6 in Foundation complete as per Drawing and Technical Specifications., Using Concrete Mixer</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink8.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Datasheet"/>
-      <sheetName val="Abstract"/>
-      <sheetName val="Quantity_Sheet"/>
-      <sheetName val="District_Rate"/>
-      <sheetName val="Equipment_Rate"/>
-      <sheetName val="Summary_of_Rates"/>
-      <sheetName val="rate (roadway)"/>
-      <sheetName val="manhole"/>
-      <sheetName val="bistar"/>
-      <sheetName val="Rate_Analysis"/>
-      <sheetName val="DWC pipe Rate-analysis"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Loading_Unloading"/>
-      <sheetName val="Collection"/>
-      <sheetName val="Transportation"/>
-      <sheetName val="References"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="PPMO_BOQ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1"/>
-      <sheetData sheetId="1" refreshError="1">
-        <row r="60">
-          <cell r="B60" t="str">
-            <v>Providing and laying of hand pack Stone soling with 150 to 200 mm thick stones and packing with smaller stone on prepared surface as per Drawing and Technical Specifications.</v>
-          </cell>
-        </row>
-        <row r="172">
-          <cell r="B172" t="str">
-            <v>Providing and laying of Plain/Reinforced Cement Concrete in Foundation complete as per Drawing and Technical Specifications., RCC Grade M 20</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink9.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="Datasheet"/>
-      <sheetName val="Abstract"/>
-      <sheetName val="Quantity_Sheet"/>
-      <sheetName val="District_Rate"/>
-      <sheetName val="Equipment_Rate"/>
-      <sheetName val="Summary_of_Rates"/>
-      <sheetName val="rate (roadway)"/>
-      <sheetName val="manhole"/>
-      <sheetName val="bistar"/>
-      <sheetName val="Rate_Analysis"/>
-      <sheetName val="DWC pipe Rate-analysis"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="Sheet2"/>
-      <sheetName val="Sheet3"/>
-      <sheetName val="Sheet4"/>
-      <sheetName val="Loading_Unloading"/>
-      <sheetName val="Collection"/>
-      <sheetName val="Transportation"/>
-      <sheetName val="References"/>
-      <sheetName val="BOQ"/>
-      <sheetName val="PPMO_BOQ"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1">
-        <row r="61">
-          <cell r="B61" t="str">
-            <v>Providing and laying  granular sub-base   on prepared surface, mixing  at OMC, and compacting  to achieve the desired density, complete as per Drawing and Technical Specifications., By Mechanical means</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -5761,68 +5734,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:18" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:18" ht="19.5">
       <c r="A5" s="6"/>
@@ -5833,33 +5806,33 @@
         <v>93</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>69</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:18">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="3"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>100</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
-      <c r="O6" s="189" t="s">
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
+      <c r="O6" s="212" t="s">
         <v>70</v>
       </c>
-      <c r="P6" s="189"/>
-      <c r="Q6" s="189"/>
-      <c r="R6" s="189"/>
+      <c r="P6" s="212"/>
+      <c r="Q6" s="212"/>
+      <c r="R6" s="212"/>
     </row>
     <row r="7" spans="1:18" ht="17.25" thickBot="1">
       <c r="C7" s="5"/>
@@ -5953,7 +5926,7 @@
         <v>35</v>
       </c>
       <c r="J10" s="70">
-        <f>'[2]Table of Content 2'!$H$312</f>
+        <f>'[8]Table of Content 2'!$H$312</f>
         <v>9900</v>
       </c>
       <c r="K10" s="70">
@@ -6040,7 +6013,7 @@
         <v>40</v>
       </c>
       <c r="J14" s="70">
-        <f>'[2]Table of Content 2'!$H$314</f>
+        <f>'[8]Table of Content 2'!$H$314</f>
         <v>97.2</v>
       </c>
       <c r="K14" s="70">
@@ -6156,7 +6129,7 @@
         <v>35</v>
       </c>
       <c r="J19" s="73">
-        <f>'[2]Table of Content 2'!$H$43</f>
+        <f>'[8]Table of Content 2'!$H$43</f>
         <v>14911.97</v>
       </c>
       <c r="K19" s="73">
@@ -6178,7 +6151,7 @@
       <c r="I20" s="24"/>
       <c r="J20" s="73"/>
       <c r="K20" s="73">
-        <f>'[2]Update Descrip'!$G$397*H19*0.13</f>
+        <f>'[8]Update Descrip'!$G$397*H19*0.13</f>
         <v>359.82026615853664</v>
       </c>
       <c r="L20" s="25"/>
@@ -6196,7 +6169,7 @@
       <c r="I21" s="72"/>
       <c r="J21" s="73"/>
       <c r="K21" s="73">
-        <f>'[2]Update Descrip'!$G$398*H19*0.13</f>
+        <f>'[8]Update Descrip'!$G$398*H19*0.13</f>
         <v>175.0255935365854</v>
       </c>
       <c r="L21" s="25"/>
@@ -6214,7 +6187,7 @@
       <c r="I22" s="24"/>
       <c r="J22" s="73"/>
       <c r="K22" s="73">
-        <f>'[2]Update Descrip'!$G$396*H19*0.13</f>
+        <f>'[8]Update Descrip'!$G$396*H19*0.13</f>
         <v>2185.4811248780493</v>
       </c>
       <c r="L22" s="25"/>
@@ -6303,7 +6276,7 @@
         <v>18</v>
       </c>
       <c r="J26" s="73">
-        <f>'[2]Table of Content 2'!$H$77/1000</f>
+        <f>'[8]Table of Content 2'!$H$77/1000</f>
         <v>130.21</v>
       </c>
       <c r="K26" s="73">
@@ -6427,7 +6400,7 @@
         <v>24</v>
       </c>
       <c r="J31" s="73">
-        <f>'[2]Table of Content 2'!$H$67</f>
+        <f>'[8]Table of Content 2'!$H$67</f>
         <v>17107.900000000001</v>
       </c>
       <c r="K31" s="73">
@@ -6449,7 +6422,7 @@
       <c r="I32" s="24"/>
       <c r="J32" s="73"/>
       <c r="K32" s="73">
-        <f>'[2]Update Descrip'!$G$676*H31*0.13</f>
+        <f>'[8]Update Descrip'!$G$676*H31*0.13</f>
         <v>2279.3764500000002</v>
       </c>
       <c r="L32" s="25"/>
@@ -6467,7 +6440,7 @@
       <c r="I33" s="24"/>
       <c r="J33" s="73"/>
       <c r="K33" s="73">
-        <f>'[2]Update Descrip'!$G$679*H31*0.13</f>
+        <f>'[8]Update Descrip'!$G$679*H31*0.13</f>
         <v>420.72746625000002</v>
       </c>
       <c r="L33" s="25"/>
@@ -6485,7 +6458,7 @@
       <c r="I34" s="24"/>
       <c r="J34" s="73"/>
       <c r="K34" s="73">
-        <f>('[2]Update Descrip'!$G$677+'[2]Update Descrip'!$G$678)*H31*0.13</f>
+        <f>('[8]Update Descrip'!$G$677+'[8]Update Descrip'!$G$678)*H31*0.13</f>
         <v>1166.4725962500002</v>
       </c>
       <c r="L34" s="25"/>
@@ -6530,7 +6503,7 @@
         <v>23</v>
       </c>
       <c r="J36" s="73">
-        <f>'[2]Table of Content 2'!$H$155</f>
+        <f>'[8]Table of Content 2'!$H$155</f>
         <v>692.38</v>
       </c>
       <c r="K36" s="72">
@@ -6552,7 +6525,7 @@
       <c r="I37" s="74"/>
       <c r="J37" s="73"/>
       <c r="K37" s="69">
-        <f>'[2]Update Descrip'!$G$1804/10*H36*0.13</f>
+        <f>'[8]Update Descrip'!$G$1804/10*H36*0.13</f>
         <v>329.24326500000001</v>
       </c>
       <c r="L37" s="25"/>
@@ -6570,7 +6543,7 @@
       <c r="I38" s="74"/>
       <c r="J38" s="73"/>
       <c r="K38" s="69">
-        <f>'[2]Update Descrip'!$G$1805/10*H36*0.13</f>
+        <f>'[8]Update Descrip'!$G$1805/10*H36*0.13</f>
         <v>79.196130000000011</v>
       </c>
       <c r="L38" s="25"/>
@@ -6588,7 +6561,7 @@
       <c r="I39" s="74"/>
       <c r="J39" s="73"/>
       <c r="K39" s="69">
-        <f>'[2]Update Descrip'!$G$1806/10*H36*0.13</f>
+        <f>'[8]Update Descrip'!$G$1806/10*H36*0.13</f>
         <v>227.54978999999997</v>
       </c>
       <c r="L39" s="25"/>
@@ -6675,7 +6648,7 @@
         <v>40</v>
       </c>
       <c r="J43" s="73">
-        <f>'[2]Table of Content 2'!$H$215</f>
+        <f>'[8]Table of Content 2'!$H$215</f>
         <v>402.23</v>
       </c>
       <c r="K43" s="73">
@@ -6697,7 +6670,7 @@
       <c r="I44" s="24"/>
       <c r="J44" s="75"/>
       <c r="K44" s="73">
-        <f>'[2]Update Descrip'!$G$2611/100*H43*0.13</f>
+        <f>'[8]Update Descrip'!$G$2611/100*H43*0.13</f>
         <v>227.0931975</v>
       </c>
       <c r="L44" s="25"/>
@@ -6715,7 +6688,7 @@
       <c r="I45" s="24"/>
       <c r="J45" s="75"/>
       <c r="K45" s="73">
-        <f>'[2]Update Descrip'!$G$2612/100*H43*0.13</f>
+        <f>'[8]Update Descrip'!$G$2612/100*H43*0.13</f>
         <v>107.0617275</v>
       </c>
       <c r="L45" s="25"/>
@@ -6827,7 +6800,7 @@
         <v>40</v>
       </c>
       <c r="J50" s="72">
-        <f>'[2]Table of Content 2'!$H$187</f>
+        <f>'[8]Table of Content 2'!$H$187</f>
         <v>286.77</v>
       </c>
       <c r="K50" s="72">
@@ -6849,7 +6822,7 @@
       <c r="I51" s="72"/>
       <c r="J51" s="72"/>
       <c r="K51" s="72">
-        <f>'[2]Update Descrip'!$H$2269/10*H50*0.13</f>
+        <f>'[8]Update Descrip'!$H$2269/10*H50*0.13</f>
         <v>359.29296000000005</v>
       </c>
       <c r="L51" s="25"/>
@@ -7075,7 +7048,7 @@
         <v>90</v>
       </c>
       <c r="J63" s="70">
-        <f>'[3]Table of Content 2'!$H$329</f>
+        <f>'[9]Table of Content 2'!$H$329</f>
         <v>68.400000000000006</v>
       </c>
       <c r="K63" s="70">
@@ -7174,7 +7147,7 @@
         <v>91</v>
       </c>
       <c r="J67" s="73">
-        <f>'[2]Table of Content 2'!$H$412</f>
+        <f>'[8]Table of Content 2'!$H$412</f>
         <v>2761</v>
       </c>
       <c r="K67" s="73">
@@ -7432,68 +7405,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
       <c r="A5" s="6"/>
@@ -7501,27 +7474,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>210</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:14">
       <c r="C7" s="5"/>
@@ -8355,11 +8328,11 @@
       <c r="C45" s="134" t="s">
         <v>212</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="222">
         <f>+K43</f>
         <v>49124.74305248</v>
       </c>
-      <c r="E45" s="182"/>
+      <c r="E45" s="222"/>
       <c r="G45" s="64"/>
       <c r="I45" s="2"/>
       <c r="J45" s="1"/>
@@ -8368,11 +8341,11 @@
       <c r="C46" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D46" s="182">
+      <c r="D46" s="222">
         <f>13%*D45</f>
         <v>6386.2165968223999</v>
       </c>
-      <c r="E46" s="182"/>
+      <c r="E46" s="222"/>
       <c r="G46" s="64"/>
       <c r="I46" s="2"/>
       <c r="J46" s="1"/>
@@ -8381,11 +8354,11 @@
       <c r="C47" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D47" s="182">
+      <c r="D47" s="222">
         <f>SUM(D45:E46)</f>
         <v>55510.9596493024</v>
       </c>
-      <c r="E47" s="183"/>
+      <c r="E47" s="233"/>
       <c r="G47" s="62"/>
     </row>
   </sheetData>
@@ -8432,68 +8405,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>213</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
       <c r="A5" s="6"/>
@@ -8501,27 +8474,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>224</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:14">
       <c r="C7" s="5"/>
@@ -8915,7 +8888,7 @@
     <row r="24" spans="2:14">
       <c r="B24" s="155"/>
       <c r="C24" s="171"/>
-      <c r="D24" s="213">
+      <c r="D24" s="182">
         <v>36</v>
       </c>
       <c r="E24" s="135">
@@ -9317,11 +9290,11 @@
       <c r="C43" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D43" s="182">
+      <c r="D43" s="222">
         <f>+K41</f>
         <v>70809.500691152003</v>
       </c>
-      <c r="E43" s="182"/>
+      <c r="E43" s="222"/>
       <c r="G43" s="64"/>
       <c r="I43" s="2"/>
       <c r="J43" s="1"/>
@@ -9330,11 +9303,11 @@
       <c r="C44" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="182">
+      <c r="D44" s="222">
         <f>13%*D43</f>
         <v>9205.2350898497607</v>
       </c>
-      <c r="E44" s="182"/>
+      <c r="E44" s="222"/>
       <c r="G44" s="64"/>
       <c r="I44" s="2"/>
       <c r="J44" s="1"/>
@@ -9343,11 +9316,11 @@
       <c r="C45" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="222">
         <f>SUM(D43:E44)</f>
         <v>80014.735781001771</v>
       </c>
-      <c r="E45" s="183"/>
+      <c r="E45" s="233"/>
       <c r="G45" s="62"/>
     </row>
   </sheetData>
@@ -9393,102 +9366,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
-      <c r="K1" s="190"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
     </row>
     <row r="2" spans="1:13" ht="25.5">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="207" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
-      <c r="K2" s="191"/>
-    </row>
-    <row r="3" spans="1:13" s="215" customFormat="1">
-      <c r="A3" s="214" t="s">
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="207"/>
+      <c r="K2" s="207"/>
+    </row>
+    <row r="3" spans="1:13" s="183" customFormat="1">
+      <c r="A3" s="208" t="s">
         <v>214</v>
       </c>
-      <c r="B3" s="214"/>
-      <c r="C3" s="214"/>
-      <c r="D3" s="214"/>
-      <c r="E3" s="214"/>
-      <c r="F3" s="214"/>
-      <c r="G3" s="214"/>
-      <c r="H3" s="214"/>
-      <c r="I3" s="214"/>
-      <c r="J3" s="214"/>
-      <c r="K3" s="214"/>
-    </row>
-    <row r="4" spans="1:13" s="215" customFormat="1">
-      <c r="A4" s="214" t="s">
+      <c r="B3" s="208"/>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="208"/>
+      <c r="F3" s="208"/>
+      <c r="G3" s="208"/>
+      <c r="H3" s="208"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+    </row>
+    <row r="4" spans="1:13" s="183" customFormat="1">
+      <c r="A4" s="208" t="s">
         <v>53</v>
       </c>
-      <c r="B4" s="214"/>
-      <c r="C4" s="214"/>
-      <c r="D4" s="214"/>
-      <c r="E4" s="214"/>
-      <c r="F4" s="214"/>
-      <c r="G4" s="214"/>
-      <c r="H4" s="214"/>
-      <c r="I4" s="214"/>
-      <c r="J4" s="214"/>
-      <c r="K4" s="214"/>
+      <c r="B4" s="208"/>
+      <c r="C4" s="208"/>
+      <c r="D4" s="208"/>
+      <c r="E4" s="208"/>
+      <c r="F4" s="208"/>
+      <c r="G4" s="208"/>
+      <c r="H4" s="208"/>
+      <c r="I4" s="208"/>
+      <c r="J4" s="208"/>
+      <c r="K4" s="208"/>
     </row>
     <row r="5" spans="1:13" ht="18.75">
-      <c r="A5" s="192" t="s">
+      <c r="A5" s="209" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="192"/>
-      <c r="C5" s="192"/>
-      <c r="D5" s="192"/>
-      <c r="E5" s="192"/>
-      <c r="F5" s="192"/>
-      <c r="G5" s="192"/>
-      <c r="H5" s="192"/>
-      <c r="I5" s="192"/>
-      <c r="J5" s="192"/>
-      <c r="K5" s="192"/>
+      <c r="B5" s="209"/>
+      <c r="C5" s="209"/>
+      <c r="D5" s="209"/>
+      <c r="E5" s="209"/>
+      <c r="F5" s="209"/>
+      <c r="G5" s="209"/>
+      <c r="H5" s="209"/>
+      <c r="I5" s="209"/>
+      <c r="J5" s="209"/>
+      <c r="K5" s="209"/>
     </row>
     <row r="6" spans="1:13" ht="18.75">
       <c r="A6" s="31" t="s">
         <v>215</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="194">
+      <c r="C6" s="210">
         <f>F37</f>
         <v>70809.500691152003</v>
       </c>
-      <c r="D6" s="195"/>
-      <c r="E6" s="216"/>
+      <c r="D6" s="211"/>
+      <c r="E6" s="184"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31"/>
       <c r="H6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="I6" s="31"/>
-      <c r="J6" s="194">
+      <c r="J6" s="210">
         <f>I37</f>
         <v>70309.500691152003</v>
       </c>
-      <c r="K6" s="195"/>
+      <c r="K6" s="211"/>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="32" t="s">
@@ -9497,99 +9470,99 @@
       <c r="B7" s="32"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
-      <c r="F7" s="196"/>
-      <c r="G7" s="196"/>
-      <c r="I7" s="217" t="s">
+      <c r="F7" s="201"/>
+      <c r="G7" s="201"/>
+      <c r="I7" s="202" t="s">
         <v>217</v>
       </c>
-      <c r="J7" s="217"/>
-      <c r="K7" s="217"/>
+      <c r="J7" s="202"/>
+      <c r="K7" s="202"/>
     </row>
     <row r="8" spans="1:13" ht="15.75">
-      <c r="A8" s="218" t="s">
+      <c r="A8" s="203" t="s">
         <v>220</v>
       </c>
-      <c r="B8" s="218"/>
-      <c r="C8" s="218"/>
-      <c r="D8" s="218"/>
-      <c r="E8" s="218"/>
-      <c r="F8" s="218"/>
-      <c r="I8" s="197" t="s">
+      <c r="B8" s="203"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="203"/>
+      <c r="F8" s="203"/>
+      <c r="I8" s="204" t="s">
         <v>218</v>
       </c>
-      <c r="J8" s="197"/>
-      <c r="K8" s="197"/>
+      <c r="J8" s="204"/>
+      <c r="K8" s="204"/>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="219" t="str">
+      <c r="A9" s="205" t="str">
         <f>E!B6</f>
         <v>Location:- Shankharapur Municipality- 1</v>
       </c>
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="I9" s="197" t="s">
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
+      <c r="D9" s="205"/>
+      <c r="E9" s="205"/>
+      <c r="F9" s="205"/>
+      <c r="I9" s="204" t="s">
         <v>219</v>
       </c>
-      <c r="J9" s="197"/>
-      <c r="K9" s="197"/>
+      <c r="J9" s="204"/>
+      <c r="K9" s="204"/>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" s="220" t="s">
+      <c r="A11" s="199" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="220" t="s">
+      <c r="B11" s="199" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="220" t="s">
+      <c r="C11" s="199" t="s">
         <v>7</v>
       </c>
-      <c r="D11" s="221" t="s">
+      <c r="D11" s="200" t="s">
         <v>61</v>
       </c>
-      <c r="E11" s="221"/>
-      <c r="F11" s="221"/>
-      <c r="G11" s="221" t="s">
+      <c r="E11" s="200"/>
+      <c r="F11" s="200"/>
+      <c r="G11" s="200" t="s">
         <v>62</v>
       </c>
-      <c r="H11" s="221"/>
-      <c r="I11" s="221"/>
-      <c r="J11" s="220" t="s">
+      <c r="H11" s="200"/>
+      <c r="I11" s="200"/>
+      <c r="J11" s="199" t="s">
         <v>63</v>
       </c>
-      <c r="K11" s="222" t="s">
+      <c r="K11" s="198" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" s="220"/>
-      <c r="B12" s="220"/>
-      <c r="C12" s="220"/>
-      <c r="D12" s="223" t="s">
+      <c r="A12" s="199"/>
+      <c r="B12" s="199"/>
+      <c r="C12" s="199"/>
+      <c r="D12" s="185" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="223" t="s">
+      <c r="E12" s="185" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="223" t="s">
+      <c r="F12" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="G12" s="223" t="s">
+      <c r="G12" s="185" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="223" t="s">
+      <c r="H12" s="185" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="223" t="s">
+      <c r="I12" s="185" t="s">
         <v>9</v>
       </c>
-      <c r="J12" s="220"/>
-      <c r="K12" s="222"/>
-    </row>
-    <row r="13" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A13" s="224">
+      <c r="J12" s="199"/>
+      <c r="K12" s="198"/>
+    </row>
+    <row r="13" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A13" s="186">
         <f>E!B9</f>
         <v>1</v>
       </c>
@@ -9597,59 +9570,59 @@
         <f>E!C9</f>
         <v>;fn sf7</v>
       </c>
-      <c r="C13" s="225" t="str">
+      <c r="C13" s="187" t="str">
         <f>E!I13</f>
         <v>cum</v>
       </c>
-      <c r="D13" s="225">
+      <c r="D13" s="187">
         <f>E!H13</f>
         <v>6.4131199999999999E-2</v>
       </c>
-      <c r="E13" s="225">
+      <c r="E13" s="187">
         <f>E!J13</f>
         <v>247293.58499999996</v>
       </c>
-      <c r="F13" s="225">
+      <c r="F13" s="187">
         <f>D13*E13</f>
         <v>15859.234358351998</v>
       </c>
-      <c r="G13" s="225">
+      <c r="G13" s="187">
         <f>V!H13</f>
         <v>6.4131199999999999E-2</v>
       </c>
-      <c r="H13" s="225">
+      <c r="H13" s="187">
         <f>V!J13</f>
         <v>247293.58499999996</v>
       </c>
-      <c r="I13" s="225">
+      <c r="I13" s="187">
         <f>G13*H13</f>
         <v>15859.234358351998</v>
       </c>
-      <c r="J13" s="226">
+      <c r="J13" s="188">
         <f>I13-F13</f>
         <v>0</v>
       </c>
-      <c r="K13" s="227"/>
-      <c r="M13" s="215">
+      <c r="K13" s="189"/>
+      <c r="M13" s="183">
         <f>1.25*F13</f>
         <v>19824.042947939997</v>
       </c>
     </row>
-    <row r="14" spans="1:13" s="215" customFormat="1">
-      <c r="A14" s="228"/>
-      <c r="B14" s="229"/>
-      <c r="C14" s="225"/>
-      <c r="D14" s="225"/>
-      <c r="E14" s="225"/>
-      <c r="F14" s="225"/>
-      <c r="G14" s="225"/>
-      <c r="H14" s="225"/>
-      <c r="I14" s="225"/>
-      <c r="J14" s="226"/>
-      <c r="K14" s="227"/>
-    </row>
-    <row r="15" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A15" s="224">
+    <row r="14" spans="1:13" s="183" customFormat="1">
+      <c r="A14" s="190"/>
+      <c r="B14" s="191"/>
+      <c r="C14" s="187"/>
+      <c r="D14" s="187"/>
+      <c r="E14" s="187"/>
+      <c r="F14" s="187"/>
+      <c r="G14" s="187"/>
+      <c r="H14" s="187"/>
+      <c r="I14" s="187"/>
+      <c r="J14" s="188"/>
+      <c r="K14" s="189"/>
+    </row>
+    <row r="15" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A15" s="186">
         <f>E!B15</f>
         <v>2</v>
       </c>
@@ -9657,238 +9630,238 @@
         <f>E!C15</f>
         <v>kmnfdsf] sAhf #Æ ;fOh</v>
       </c>
-      <c r="C15" s="225" t="str">
+      <c r="C15" s="187" t="str">
         <f>E!I15</f>
         <v>no.</v>
       </c>
-      <c r="D15" s="225">
+      <c r="D15" s="187">
         <f>E!H15</f>
         <v>17</v>
       </c>
-      <c r="E15" s="225">
+      <c r="E15" s="187">
         <f>E!J15</f>
         <v>17.25</v>
       </c>
-      <c r="F15" s="225">
+      <c r="F15" s="187">
         <f>D15*E15</f>
         <v>293.25</v>
       </c>
-      <c r="G15" s="225">
+      <c r="G15" s="187">
         <f>V!H15</f>
         <v>17</v>
       </c>
-      <c r="H15" s="225">
+      <c r="H15" s="187">
         <f>V!J15</f>
         <v>17.25</v>
       </c>
-      <c r="I15" s="225">
+      <c r="I15" s="187">
         <f>G15*H15</f>
         <v>293.25</v>
       </c>
-      <c r="J15" s="226">
+      <c r="J15" s="188">
         <f>I15-F15</f>
         <v>0</v>
       </c>
-      <c r="K15" s="227"/>
-      <c r="M15" s="215">
+      <c r="K15" s="189"/>
+      <c r="M15" s="183">
         <f t="shared" ref="M15:M33" si="0">1.25*F15</f>
         <v>366.5625</v>
       </c>
     </row>
-    <row r="16" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A16" s="224"/>
-      <c r="B16" s="230"/>
-      <c r="C16" s="225"/>
-      <c r="D16" s="225"/>
-      <c r="E16" s="225"/>
-      <c r="F16" s="225"/>
-      <c r="G16" s="225"/>
-      <c r="H16" s="225"/>
-      <c r="I16" s="225"/>
-      <c r="J16" s="226"/>
-      <c r="K16" s="227"/>
-    </row>
-    <row r="17" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A17" s="224">
+    <row r="16" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A16" s="186"/>
+      <c r="B16" s="192"/>
+      <c r="C16" s="187"/>
+      <c r="D16" s="187"/>
+      <c r="E16" s="187"/>
+      <c r="F16" s="187"/>
+      <c r="G16" s="187"/>
+      <c r="H16" s="187"/>
+      <c r="I16" s="187"/>
+      <c r="J16" s="188"/>
+      <c r="K16" s="189"/>
+    </row>
+    <row r="17" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A17" s="186">
         <f>E!B17</f>
         <v>3</v>
       </c>
-      <c r="B17" s="230" t="str">
+      <c r="B17" s="192" t="str">
         <f>E!C17</f>
         <v>Gate hook</v>
       </c>
-      <c r="C17" s="225" t="str">
+      <c r="C17" s="187" t="str">
         <f>E!I17</f>
         <v>no.</v>
       </c>
-      <c r="D17" s="225">
+      <c r="D17" s="187">
         <f>E!H17</f>
         <v>12</v>
       </c>
-      <c r="E17" s="225">
+      <c r="E17" s="187">
         <f>E!J17</f>
         <v>37.949999999999996</v>
       </c>
-      <c r="F17" s="225">
+      <c r="F17" s="187">
         <f>D17*E17</f>
         <v>455.4</v>
       </c>
-      <c r="G17" s="225">
+      <c r="G17" s="187">
         <f>V!H17</f>
         <v>12</v>
       </c>
-      <c r="H17" s="225">
+      <c r="H17" s="187">
         <f>V!J17</f>
         <v>37.949999999999996</v>
       </c>
-      <c r="I17" s="225">
+      <c r="I17" s="187">
         <f>G17*H17</f>
         <v>455.4</v>
       </c>
-      <c r="J17" s="226">
+      <c r="J17" s="188">
         <f>I17-F17</f>
         <v>0</v>
       </c>
-      <c r="K17" s="227"/>
-      <c r="M17" s="215">
+      <c r="K17" s="189"/>
+      <c r="M17" s="183">
         <f t="shared" si="0"/>
         <v>569.25</v>
       </c>
     </row>
-    <row r="18" spans="1:13" s="215" customFormat="1">
-      <c r="A18" s="228"/>
-      <c r="B18" s="229"/>
-      <c r="C18" s="225"/>
-      <c r="D18" s="225"/>
-      <c r="E18" s="225"/>
-      <c r="F18" s="225"/>
-      <c r="G18" s="225"/>
-      <c r="H18" s="225"/>
-      <c r="I18" s="225"/>
-      <c r="J18" s="226"/>
-      <c r="K18" s="227"/>
-    </row>
-    <row r="19" spans="1:13" s="215" customFormat="1" ht="16.5">
-      <c r="A19" s="224">
+    <row r="18" spans="1:13" s="183" customFormat="1">
+      <c r="A18" s="190"/>
+      <c r="B18" s="191"/>
+      <c r="C18" s="187"/>
+      <c r="D18" s="187"/>
+      <c r="E18" s="187"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="188"/>
+      <c r="K18" s="189"/>
+    </row>
+    <row r="19" spans="1:13" s="183" customFormat="1" ht="16.5">
+      <c r="A19" s="186">
         <f>E!B19</f>
         <v>4</v>
       </c>
       <c r="B19" s="174" t="s">
         <v>199</v>
       </c>
-      <c r="C19" s="225" t="str">
+      <c r="C19" s="187" t="str">
         <f>E!I19</f>
         <v>no.</v>
       </c>
-      <c r="D19" s="225">
+      <c r="D19" s="187">
         <f>E!H19</f>
         <v>21</v>
       </c>
-      <c r="E19" s="225">
+      <c r="E19" s="187">
         <f>E!J19</f>
         <v>50.599999999999994</v>
       </c>
-      <c r="F19" s="225">
+      <c r="F19" s="187">
         <f>D19*E19</f>
         <v>1062.5999999999999</v>
       </c>
-      <c r="G19" s="225">
+      <c r="G19" s="187">
         <f>V!H19</f>
         <v>21</v>
       </c>
-      <c r="H19" s="225">
+      <c r="H19" s="187">
         <f>V!J19</f>
         <v>50.599999999999994</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="187">
         <f>G19*H19</f>
         <v>1062.5999999999999</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="188">
         <f>I19-F19</f>
         <v>0</v>
       </c>
-      <c r="K19" s="227"/>
-      <c r="M19" s="215">
+      <c r="K19" s="189"/>
+      <c r="M19" s="183">
         <f t="shared" ref="M19" si="1">1.25*F19</f>
         <v>1328.25</v>
       </c>
     </row>
-    <row r="20" spans="1:13" s="215" customFormat="1">
-      <c r="A20" s="228"/>
-      <c r="B20" s="229"/>
-      <c r="C20" s="225"/>
-      <c r="D20" s="225"/>
-      <c r="E20" s="225"/>
-      <c r="F20" s="225"/>
-      <c r="G20" s="225"/>
-      <c r="H20" s="225"/>
-      <c r="I20" s="225"/>
-      <c r="J20" s="226"/>
-      <c r="K20" s="227"/>
-    </row>
-    <row r="21" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A21" s="224">
+    <row r="20" spans="1:13" s="183" customFormat="1">
+      <c r="A20" s="190"/>
+      <c r="B20" s="191"/>
+      <c r="C20" s="187"/>
+      <c r="D20" s="187"/>
+      <c r="E20" s="187"/>
+      <c r="F20" s="187"/>
+      <c r="G20" s="187"/>
+      <c r="H20" s="187"/>
+      <c r="I20" s="187"/>
+      <c r="J20" s="188"/>
+      <c r="K20" s="189"/>
+    </row>
+    <row r="21" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A21" s="186">
         <f>E!B21</f>
         <v>5</v>
       </c>
-      <c r="B21" s="230" t="str">
+      <c r="B21" s="192" t="str">
         <f>E!C21</f>
         <v>Handle (ordinary)</v>
       </c>
-      <c r="C21" s="225" t="str">
+      <c r="C21" s="187" t="str">
         <f>E!I21</f>
         <v>no.</v>
       </c>
-      <c r="D21" s="225">
+      <c r="D21" s="187">
         <f>E!H21</f>
         <v>8</v>
       </c>
-      <c r="E21" s="225">
+      <c r="E21" s="187">
         <f>E!J21</f>
         <v>39.099999999999994</v>
       </c>
-      <c r="F21" s="225">
+      <c r="F21" s="187">
         <f>D21*E21</f>
         <v>312.79999999999995</v>
       </c>
-      <c r="G21" s="225">
+      <c r="G21" s="187">
         <f>V!H21</f>
         <v>8</v>
       </c>
-      <c r="H21" s="225">
+      <c r="H21" s="187">
         <f>V!J21</f>
         <v>39.099999999999994</v>
       </c>
-      <c r="I21" s="225">
+      <c r="I21" s="187">
         <f>G21*H21</f>
         <v>312.79999999999995</v>
       </c>
-      <c r="J21" s="226">
+      <c r="J21" s="188">
         <f>I21-F21</f>
         <v>0</v>
       </c>
-      <c r="K21" s="227"/>
-      <c r="M21" s="215">
+      <c r="K21" s="189"/>
+      <c r="M21" s="183">
         <f t="shared" ref="M21" si="2">1.25*F21</f>
         <v>390.99999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:13" s="215" customFormat="1">
-      <c r="A22" s="228"/>
-      <c r="B22" s="229"/>
-      <c r="C22" s="225"/>
-      <c r="D22" s="225"/>
-      <c r="E22" s="225"/>
-      <c r="F22" s="225"/>
-      <c r="G22" s="225"/>
-      <c r="H22" s="225"/>
-      <c r="I22" s="225"/>
-      <c r="J22" s="226"/>
-      <c r="K22" s="227"/>
-    </row>
-    <row r="23" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A23" s="224">
+    <row r="22" spans="1:13" s="183" customFormat="1">
+      <c r="A22" s="190"/>
+      <c r="B22" s="191"/>
+      <c r="C22" s="187"/>
+      <c r="D22" s="187"/>
+      <c r="E22" s="187"/>
+      <c r="F22" s="187"/>
+      <c r="G22" s="187"/>
+      <c r="H22" s="187"/>
+      <c r="I22" s="187"/>
+      <c r="J22" s="188"/>
+      <c r="K22" s="189"/>
+    </row>
+    <row r="23" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A23" s="186">
         <f>E!B23</f>
         <v>6</v>
       </c>
@@ -9896,179 +9869,179 @@
         <f>E!C23</f>
         <v>P]gf # dL=dL=</v>
       </c>
-      <c r="C23" s="225" t="str">
+      <c r="C23" s="187" t="str">
         <f>E!I28</f>
         <v>sq.m</v>
       </c>
-      <c r="D23" s="225">
+      <c r="D23" s="187">
         <f>E!H28</f>
         <v>19.043600000000005</v>
       </c>
-      <c r="E23" s="225">
+      <c r="E23" s="187">
         <f>E!J28</f>
         <v>643.44799999999998</v>
       </c>
-      <c r="F23" s="225">
+      <c r="F23" s="187">
         <f>D23*E23</f>
         <v>12253.566332800003</v>
       </c>
-      <c r="G23" s="225">
+      <c r="G23" s="187">
         <f>V!H28</f>
         <v>19.043600000000005</v>
       </c>
-      <c r="H23" s="225">
+      <c r="H23" s="187">
         <f>V!J28</f>
         <v>643.44799999999998</v>
       </c>
-      <c r="I23" s="225">
+      <c r="I23" s="187">
         <f>G23*H23</f>
         <v>12253.566332800003</v>
       </c>
-      <c r="J23" s="226">
+      <c r="J23" s="188">
         <f>I23-F23</f>
         <v>0</v>
       </c>
-      <c r="K23" s="227"/>
-      <c r="M23" s="215">
+      <c r="K23" s="189"/>
+      <c r="M23" s="183">
         <f t="shared" ref="M23" si="3">1.25*F23</f>
         <v>15316.957916000003</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="215" customFormat="1">
-      <c r="A24" s="228"/>
-      <c r="B24" s="229"/>
-      <c r="C24" s="225"/>
-      <c r="D24" s="225"/>
-      <c r="E24" s="225"/>
-      <c r="F24" s="225"/>
-      <c r="G24" s="225"/>
-      <c r="H24" s="225"/>
-      <c r="I24" s="225"/>
-      <c r="J24" s="226"/>
-      <c r="K24" s="227"/>
-    </row>
-    <row r="25" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A25" s="224">
+    <row r="24" spans="1:13" s="183" customFormat="1">
+      <c r="A24" s="190"/>
+      <c r="B24" s="191"/>
+      <c r="C24" s="187"/>
+      <c r="D24" s="187"/>
+      <c r="E24" s="187"/>
+      <c r="F24" s="187"/>
+      <c r="G24" s="187"/>
+      <c r="H24" s="187"/>
+      <c r="I24" s="187"/>
+      <c r="J24" s="188"/>
+      <c r="K24" s="189"/>
+    </row>
+    <row r="25" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A25" s="186">
         <f>E!B30</f>
         <v>7</v>
       </c>
-      <c r="B25" s="230" t="str">
+      <c r="B25" s="192" t="str">
         <f>E!C30</f>
         <v>Wood primer</v>
       </c>
-      <c r="C25" s="225" t="str">
+      <c r="C25" s="187" t="str">
         <f>E!I30</f>
         <v>ltr</v>
       </c>
-      <c r="D25" s="225">
+      <c r="D25" s="187">
         <f>E!H30</f>
         <v>4</v>
       </c>
-      <c r="E25" s="225">
+      <c r="E25" s="187">
         <f>E!J30</f>
         <v>447.34999999999997</v>
       </c>
-      <c r="F25" s="225">
+      <c r="F25" s="187">
         <f>D25*E25</f>
         <v>1789.3999999999999</v>
       </c>
-      <c r="G25" s="225">
+      <c r="G25" s="187">
         <f>V!H30</f>
         <v>4</v>
       </c>
-      <c r="H25" s="225">
+      <c r="H25" s="187">
         <f>V!J30</f>
         <v>447.34999999999997</v>
       </c>
-      <c r="I25" s="225">
+      <c r="I25" s="187">
         <f>G25*H25</f>
         <v>1789.3999999999999</v>
       </c>
-      <c r="J25" s="226">
+      <c r="J25" s="188">
         <f>I25-F25</f>
         <v>0</v>
       </c>
-      <c r="K25" s="227"/>
-      <c r="M25" s="215">
+      <c r="K25" s="189"/>
+      <c r="M25" s="183">
         <f t="shared" ref="M25" si="4">1.25*F25</f>
         <v>2236.75</v>
       </c>
     </row>
-    <row r="26" spans="1:13" s="215" customFormat="1">
-      <c r="A26" s="228"/>
-      <c r="B26" s="229"/>
-      <c r="C26" s="225"/>
-      <c r="D26" s="225"/>
-      <c r="E26" s="225"/>
-      <c r="F26" s="225"/>
-      <c r="G26" s="225"/>
-      <c r="H26" s="225"/>
-      <c r="I26" s="225"/>
-      <c r="J26" s="226"/>
-      <c r="K26" s="227"/>
-    </row>
-    <row r="27" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A27" s="224">
+    <row r="26" spans="1:13" s="183" customFormat="1">
+      <c r="A26" s="190"/>
+      <c r="B26" s="191"/>
+      <c r="C26" s="187"/>
+      <c r="D26" s="187"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="187"/>
+      <c r="J26" s="188"/>
+      <c r="K26" s="189"/>
+    </row>
+    <row r="27" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A27" s="186">
         <f>E!B32</f>
         <v>8</v>
       </c>
-      <c r="B27" s="230" t="str">
+      <c r="B27" s="192" t="str">
         <f>E!C32</f>
         <v>Enamel paints</v>
       </c>
-      <c r="C27" s="225" t="str">
+      <c r="C27" s="187" t="str">
         <f>E!I32</f>
         <v>ltr</v>
       </c>
-      <c r="D27" s="225">
+      <c r="D27" s="187">
         <f>E!H32</f>
         <v>3</v>
       </c>
-      <c r="E27" s="225">
+      <c r="E27" s="187">
         <f>E!J32</f>
         <v>614.09999999999991</v>
       </c>
-      <c r="F27" s="225">
+      <c r="F27" s="187">
         <f>D27*E27</f>
         <v>1842.2999999999997</v>
       </c>
-      <c r="G27" s="225">
+      <c r="G27" s="187">
         <f>V!H32</f>
         <v>3</v>
       </c>
-      <c r="H27" s="225">
+      <c r="H27" s="187">
         <f>V!J32</f>
         <v>614.09999999999991</v>
       </c>
-      <c r="I27" s="225">
+      <c r="I27" s="187">
         <f>G27*H27</f>
         <v>1842.2999999999997</v>
       </c>
-      <c r="J27" s="226">
+      <c r="J27" s="188">
         <f>I27-F27</f>
         <v>0</v>
       </c>
-      <c r="K27" s="227"/>
-      <c r="M27" s="215">
+      <c r="K27" s="189"/>
+      <c r="M27" s="183">
         <f t="shared" ref="M27" si="5">1.25*F27</f>
         <v>2302.8749999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:13" s="215" customFormat="1">
-      <c r="A28" s="228"/>
-      <c r="B28" s="229"/>
-      <c r="C28" s="225"/>
-      <c r="D28" s="225"/>
-      <c r="E28" s="225"/>
-      <c r="F28" s="225"/>
-      <c r="G28" s="225"/>
-      <c r="H28" s="225"/>
-      <c r="I28" s="225"/>
-      <c r="J28" s="226"/>
-      <c r="K28" s="227"/>
-    </row>
-    <row r="29" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A29" s="224">
+    <row r="28" spans="1:13" s="183" customFormat="1">
+      <c r="A28" s="190"/>
+      <c r="B28" s="191"/>
+      <c r="C28" s="187"/>
+      <c r="D28" s="187"/>
+      <c r="E28" s="187"/>
+      <c r="F28" s="187"/>
+      <c r="G28" s="187"/>
+      <c r="H28" s="187"/>
+      <c r="I28" s="187"/>
+      <c r="J28" s="188"/>
+      <c r="K28" s="189"/>
+    </row>
+    <row r="29" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A29" s="186">
         <f>E!B34</f>
         <v>9</v>
       </c>
@@ -10076,307 +10049,320 @@
         <f>E!C34</f>
         <v>tf/lkg t]n</v>
       </c>
-      <c r="C29" s="225" t="str">
+      <c r="C29" s="187" t="str">
         <f>E!I34</f>
         <v>ltr</v>
       </c>
-      <c r="D29" s="225">
+      <c r="D29" s="187">
         <f>E!H34</f>
         <v>5</v>
       </c>
-      <c r="E29" s="225">
+      <c r="E29" s="187">
         <f>E!J34</f>
         <v>254.14999999999998</v>
       </c>
-      <c r="F29" s="225">
+      <c r="F29" s="187">
         <f>D29*E29</f>
         <v>1270.75</v>
       </c>
-      <c r="G29" s="225">
+      <c r="G29" s="187">
         <f>V!H34</f>
         <v>5</v>
       </c>
-      <c r="H29" s="225">
+      <c r="H29" s="187">
         <f>V!J34</f>
         <v>254.14999999999998</v>
       </c>
-      <c r="I29" s="225">
+      <c r="I29" s="187">
         <f>G29*H29</f>
         <v>1270.75</v>
       </c>
-      <c r="J29" s="226">
+      <c r="J29" s="188">
         <f>I29-F29</f>
         <v>0</v>
       </c>
-      <c r="K29" s="227"/>
-      <c r="M29" s="215">
+      <c r="K29" s="189"/>
+      <c r="M29" s="183">
         <f t="shared" ref="M29" si="6">1.25*F29</f>
         <v>1588.4375</v>
       </c>
     </row>
-    <row r="30" spans="1:13" s="215" customFormat="1">
-      <c r="A30" s="228"/>
-      <c r="B30" s="229"/>
-      <c r="C30" s="225"/>
-      <c r="D30" s="225"/>
-      <c r="E30" s="225"/>
-      <c r="F30" s="225"/>
-      <c r="G30" s="225"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="225"/>
-      <c r="J30" s="226"/>
-      <c r="K30" s="227"/>
-    </row>
-    <row r="31" spans="1:13" s="215" customFormat="1" ht="15.75">
-      <c r="A31" s="224">
+    <row r="30" spans="1:13" s="183" customFormat="1">
+      <c r="A30" s="190"/>
+      <c r="B30" s="191"/>
+      <c r="C30" s="187"/>
+      <c r="D30" s="187"/>
+      <c r="E30" s="187"/>
+      <c r="F30" s="187"/>
+      <c r="G30" s="187"/>
+      <c r="H30" s="187"/>
+      <c r="I30" s="187"/>
+      <c r="J30" s="188"/>
+      <c r="K30" s="189"/>
+    </row>
+    <row r="31" spans="1:13" s="183" customFormat="1" ht="15.75">
+      <c r="A31" s="186">
         <f>E!B36</f>
         <v>10</v>
       </c>
-      <c r="B31" s="230" t="str">
+      <c r="B31" s="192" t="str">
         <f>E!C36</f>
         <v>1" thick Paint Brush</v>
       </c>
-      <c r="C31" s="225" t="str">
+      <c r="C31" s="187" t="str">
         <f>E!I36</f>
         <v>no.</v>
       </c>
-      <c r="D31" s="225">
+      <c r="D31" s="187">
         <f>E!H36</f>
         <v>2</v>
       </c>
-      <c r="E31" s="225">
+      <c r="E31" s="187">
         <f>E!J36</f>
         <v>85.1</v>
       </c>
-      <c r="F31" s="225">
+      <c r="F31" s="187">
         <f>D31*E31</f>
         <v>170.2</v>
       </c>
-      <c r="G31" s="225">
+      <c r="G31" s="187">
         <f>V!H36</f>
         <v>2</v>
       </c>
-      <c r="H31" s="225">
+      <c r="H31" s="187">
         <f>V!J36</f>
         <v>85.1</v>
       </c>
-      <c r="I31" s="225">
+      <c r="I31" s="187">
         <f>G31*H31</f>
         <v>170.2</v>
       </c>
-      <c r="J31" s="226">
+      <c r="J31" s="188">
         <f>I31-F31</f>
         <v>0</v>
       </c>
-      <c r="K31" s="227"/>
-      <c r="M31" s="215">
+      <c r="K31" s="189"/>
+      <c r="M31" s="183">
         <f t="shared" ref="M31" si="7">1.25*F31</f>
         <v>212.75</v>
       </c>
     </row>
-    <row r="32" spans="1:13" s="215" customFormat="1">
-      <c r="A32" s="228"/>
-      <c r="B32" s="229"/>
-      <c r="C32" s="225"/>
-      <c r="D32" s="225"/>
-      <c r="E32" s="225"/>
-      <c r="F32" s="225"/>
-      <c r="G32" s="225"/>
-      <c r="H32" s="225"/>
-      <c r="I32" s="225"/>
-      <c r="J32" s="226"/>
-      <c r="K32" s="227"/>
-    </row>
-    <row r="33" spans="1:13" s="215" customFormat="1" ht="31.5">
-      <c r="A33" s="224">
+    <row r="32" spans="1:13" s="183" customFormat="1">
+      <c r="A32" s="190"/>
+      <c r="B32" s="191"/>
+      <c r="C32" s="187"/>
+      <c r="D32" s="187"/>
+      <c r="E32" s="187"/>
+      <c r="F32" s="187"/>
+      <c r="G32" s="187"/>
+      <c r="H32" s="187"/>
+      <c r="I32" s="187"/>
+      <c r="J32" s="188"/>
+      <c r="K32" s="189"/>
+    </row>
+    <row r="33" spans="1:13" s="183" customFormat="1" ht="31.5">
+      <c r="A33" s="186">
         <f>E!B38</f>
         <v>11</v>
       </c>
-      <c r="B33" s="230" t="str">
+      <c r="B33" s="192" t="str">
         <f>E!C38</f>
         <v>Provisional sum for unforseen materials and manpower</v>
       </c>
-      <c r="C33" s="225" t="str">
+      <c r="C33" s="187" t="str">
         <f>E!I38</f>
         <v>PS</v>
       </c>
-      <c r="D33" s="225">
+      <c r="D33" s="187">
         <f>E!H38</f>
         <v>1</v>
       </c>
-      <c r="E33" s="225">
+      <c r="E33" s="187">
         <f>E!J38</f>
         <v>35000</v>
       </c>
-      <c r="F33" s="225">
+      <c r="F33" s="187">
         <f>D33*E33</f>
         <v>35000</v>
       </c>
-      <c r="G33" s="225">
+      <c r="G33" s="187">
         <f>V!H38</f>
         <v>1</v>
       </c>
-      <c r="H33" s="225">
+      <c r="H33" s="187">
         <f>V!J38</f>
         <v>35000</v>
       </c>
-      <c r="I33" s="225">
+      <c r="I33" s="187">
         <f>G33*H33</f>
         <v>35000</v>
       </c>
-      <c r="J33" s="226">
+      <c r="J33" s="188">
         <f>I33-F33</f>
         <v>0</v>
       </c>
-      <c r="K33" s="227"/>
-      <c r="M33" s="215">
+      <c r="K33" s="189"/>
+      <c r="M33" s="183">
         <f t="shared" si="0"/>
         <v>43750</v>
       </c>
     </row>
-    <row r="34" spans="1:13" s="215" customFormat="1">
-      <c r="A34" s="228"/>
-      <c r="B34" s="229"/>
-      <c r="C34" s="225"/>
-      <c r="D34" s="225"/>
-      <c r="E34" s="225"/>
-      <c r="F34" s="225"/>
-      <c r="G34" s="225"/>
-      <c r="H34" s="225"/>
-      <c r="I34" s="225"/>
-      <c r="J34" s="226"/>
-      <c r="K34" s="227"/>
-    </row>
-    <row r="35" spans="1:13" s="215" customFormat="1">
-      <c r="A35" s="224">
+    <row r="34" spans="1:13" s="183" customFormat="1">
+      <c r="A34" s="190"/>
+      <c r="B34" s="191"/>
+      <c r="C34" s="187"/>
+      <c r="D34" s="187"/>
+      <c r="E34" s="187"/>
+      <c r="F34" s="187"/>
+      <c r="G34" s="187"/>
+      <c r="H34" s="187"/>
+      <c r="I34" s="187"/>
+      <c r="J34" s="188"/>
+      <c r="K34" s="189"/>
+    </row>
+    <row r="35" spans="1:13" s="183" customFormat="1">
+      <c r="A35" s="186">
         <f>E!B40</f>
         <v>12</v>
       </c>
-      <c r="B35" s="231" t="str">
+      <c r="B35" s="193" t="str">
         <f>E!C40</f>
         <v>Information Board  and photographs</v>
       </c>
-      <c r="C35" s="225" t="str">
+      <c r="C35" s="187" t="str">
         <f>E!I40</f>
         <v>no.</v>
       </c>
-      <c r="D35" s="225">
+      <c r="D35" s="187">
         <f>E!H40</f>
         <v>1</v>
       </c>
-      <c r="E35" s="225">
+      <c r="E35" s="187">
         <f>E!J40</f>
         <v>500</v>
       </c>
-      <c r="F35" s="225">
+      <c r="F35" s="187">
         <f>D35*E35</f>
         <v>500</v>
       </c>
-      <c r="G35" s="225">
+      <c r="G35" s="187">
         <f>V!D40</f>
         <v>0</v>
       </c>
-      <c r="H35" s="225">
+      <c r="H35" s="187">
         <f>V!J40</f>
         <v>500</v>
       </c>
-      <c r="I35" s="225">
+      <c r="I35" s="187">
         <f>G35*H35</f>
         <v>0</v>
       </c>
-      <c r="J35" s="226">
+      <c r="J35" s="188">
         <f>I35-F35</f>
         <v>-500</v>
       </c>
-      <c r="K35" s="227"/>
-    </row>
-    <row r="36" spans="1:13" s="215" customFormat="1">
-      <c r="A36" s="229"/>
-      <c r="B36" s="229"/>
-      <c r="C36" s="225"/>
-      <c r="D36" s="225"/>
-      <c r="E36" s="225"/>
-      <c r="F36" s="225"/>
-      <c r="G36" s="225"/>
-      <c r="H36" s="225"/>
-      <c r="I36" s="225"/>
-      <c r="J36" s="226"/>
-      <c r="K36" s="227"/>
+      <c r="K35" s="189"/>
+    </row>
+    <row r="36" spans="1:13" s="183" customFormat="1">
+      <c r="A36" s="191"/>
+      <c r="B36" s="191"/>
+      <c r="C36" s="187"/>
+      <c r="D36" s="187"/>
+      <c r="E36" s="187"/>
+      <c r="F36" s="187"/>
+      <c r="G36" s="187"/>
+      <c r="H36" s="187"/>
+      <c r="I36" s="187"/>
+      <c r="J36" s="188"/>
+      <c r="K36" s="189"/>
     </row>
     <row r="37" spans="1:13">
-      <c r="A37" s="232"/>
-      <c r="B37" s="233" t="s">
+      <c r="A37" s="194"/>
+      <c r="B37" s="195" t="s">
         <v>67</v>
       </c>
-      <c r="C37" s="233"/>
-      <c r="D37" s="234"/>
-      <c r="E37" s="234"/>
-      <c r="F37" s="234">
+      <c r="C37" s="195"/>
+      <c r="D37" s="196"/>
+      <c r="E37" s="196"/>
+      <c r="F37" s="196">
         <f>SUM(F13:F35)</f>
         <v>70809.500691152003</v>
       </c>
-      <c r="G37" s="234"/>
-      <c r="H37" s="234"/>
-      <c r="I37" s="234">
+      <c r="G37" s="196"/>
+      <c r="H37" s="196"/>
+      <c r="I37" s="196">
         <f>SUM(I13:I35)</f>
         <v>70309.500691152003</v>
       </c>
-      <c r="J37" s="235">
+      <c r="J37" s="197">
         <f>I37-F37</f>
         <v>-500</v>
       </c>
-      <c r="K37" s="232"/>
+      <c r="K37" s="194"/>
     </row>
     <row r="38" spans="1:13">
-      <c r="A38" s="232"/>
-      <c r="B38" s="233" t="s">
+      <c r="A38" s="194"/>
+      <c r="B38" s="195" t="s">
         <v>171</v>
       </c>
-      <c r="C38" s="232"/>
-      <c r="D38" s="232"/>
-      <c r="E38" s="232"/>
-      <c r="F38" s="234">
+      <c r="C38" s="194"/>
+      <c r="D38" s="194"/>
+      <c r="E38" s="194"/>
+      <c r="F38" s="196">
         <f>13%*F37</f>
         <v>9205.2350898497607</v>
       </c>
-      <c r="G38" s="232"/>
-      <c r="H38" s="232"/>
-      <c r="I38" s="234">
+      <c r="G38" s="194"/>
+      <c r="H38" s="194"/>
+      <c r="I38" s="196">
         <f>13%*I37</f>
         <v>9140.2350898497607</v>
       </c>
-      <c r="J38" s="235">
+      <c r="J38" s="197">
         <f t="shared" ref="J38:J39" si="8">I38-F38</f>
         <v>-65</v>
       </c>
-      <c r="K38" s="232"/>
+      <c r="K38" s="194"/>
     </row>
     <row r="39" spans="1:13">
-      <c r="A39" s="232"/>
-      <c r="B39" s="233" t="s">
+      <c r="A39" s="194"/>
+      <c r="B39" s="195" t="s">
         <v>221</v>
       </c>
-      <c r="C39" s="232"/>
-      <c r="D39" s="232"/>
-      <c r="E39" s="232"/>
-      <c r="F39" s="234">
+      <c r="C39" s="194"/>
+      <c r="D39" s="194"/>
+      <c r="E39" s="194"/>
+      <c r="F39" s="196">
         <f>SUM(F37:F38)</f>
         <v>80014.735781001771</v>
       </c>
-      <c r="G39" s="232"/>
-      <c r="H39" s="232"/>
-      <c r="I39" s="234">
+      <c r="G39" s="194"/>
+      <c r="H39" s="194"/>
+      <c r="I39" s="196">
         <f>SUM(I37:I38)</f>
         <v>79449.735781001771</v>
       </c>
-      <c r="J39" s="235">
+      <c r="J39" s="197">
         <f t="shared" si="8"/>
         <v>-565</v>
       </c>
-      <c r="K39" s="232"/>
+      <c r="K39" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="I9:K9"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
@@ -10384,19 +10370,6 @@
     <mergeCell ref="D11:F11"/>
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="J11:J12"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="A9:F9"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="J6:K6"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10431,68 +10404,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>211</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
       <c r="A5" s="6"/>
@@ -10500,27 +10473,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>222</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:14">
       <c r="C7" s="5"/>
@@ -10914,7 +10887,7 @@
     <row r="24" spans="2:14">
       <c r="B24" s="155"/>
       <c r="C24" s="171"/>
-      <c r="D24" s="213">
+      <c r="D24" s="182">
         <v>36</v>
       </c>
       <c r="E24" s="135">
@@ -11316,11 +11289,11 @@
       <c r="C43" s="134" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="182">
+      <c r="D43" s="222">
         <f>+K41</f>
         <v>70309.500691152003</v>
       </c>
-      <c r="E43" s="182"/>
+      <c r="E43" s="222"/>
       <c r="G43" s="64"/>
       <c r="I43" s="2"/>
       <c r="J43" s="1"/>
@@ -11329,11 +11302,11 @@
       <c r="C44" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="182">
+      <c r="D44" s="222">
         <f>13%*D43</f>
         <v>9140.2350898497607</v>
       </c>
-      <c r="E44" s="182"/>
+      <c r="E44" s="222"/>
       <c r="G44" s="64"/>
       <c r="I44" s="2"/>
       <c r="J44" s="1"/>
@@ -11342,11 +11315,11 @@
       <c r="C45" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="222">
         <f>SUM(D43:E44)</f>
         <v>79449.735781001771</v>
       </c>
-      <c r="E45" s="183"/>
+      <c r="E45" s="233"/>
       <c r="G45" s="62"/>
     </row>
   </sheetData>
@@ -11393,68 +11366,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:14" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>223</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:14" ht="20.25">
       <c r="A5" s="6"/>
@@ -11467,17 +11440,16 @@
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="J6" s="236"/>
-      <c r="K6" s="236"/>
+      <c r="J6" s="1"/>
       <c r="L6" s="181" t="s">
         <v>222</v>
       </c>
@@ -11874,7 +11846,7 @@
     <row r="24" spans="2:14">
       <c r="B24" s="155"/>
       <c r="C24" s="171"/>
-      <c r="D24" s="213">
+      <c r="D24" s="182">
         <v>36</v>
       </c>
       <c r="E24" s="135">
@@ -12276,11 +12248,11 @@
       <c r="C43" s="134" t="s">
         <v>212</v>
       </c>
-      <c r="D43" s="182">
+      <c r="D43" s="222">
         <f>+K41</f>
         <v>70309.500691152003</v>
       </c>
-      <c r="E43" s="182"/>
+      <c r="E43" s="222"/>
       <c r="G43" s="64"/>
       <c r="I43" s="2"/>
       <c r="J43" s="1"/>
@@ -12289,11 +12261,11 @@
       <c r="C44" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D44" s="182">
+      <c r="D44" s="222">
         <f>13%*D43</f>
         <v>9140.2350898497607</v>
       </c>
-      <c r="E44" s="182"/>
+      <c r="E44" s="222"/>
       <c r="G44" s="64"/>
       <c r="I44" s="2"/>
       <c r="J44" s="1"/>
@@ -12302,11 +12274,11 @@
       <c r="C45" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D45" s="182">
+      <c r="D45" s="222">
         <f>SUM(D43:E44)</f>
         <v>79449.735781001771</v>
       </c>
-      <c r="E45" s="183"/>
+      <c r="E45" s="233"/>
       <c r="G45" s="62"/>
     </row>
   </sheetData>
@@ -12351,68 +12323,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -12420,27 +12392,27 @@
         <v>181</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -12734,11 +12706,11 @@
       <c r="C20" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="182">
+      <c r="D20" s="222">
         <f>+K18</f>
         <v>84443.872931622609</v>
       </c>
-      <c r="E20" s="182"/>
+      <c r="E20" s="222"/>
       <c r="G20" s="64"/>
       <c r="I20" s="2"/>
       <c r="J20" s="1"/>
@@ -12747,11 +12719,11 @@
       <c r="C21" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="182">
+      <c r="D21" s="222">
         <f>13%*D20</f>
         <v>10977.703481110939</v>
       </c>
-      <c r="E21" s="182"/>
+      <c r="E21" s="222"/>
       <c r="G21" s="64"/>
       <c r="I21" s="2"/>
       <c r="J21" s="1"/>
@@ -12760,11 +12732,11 @@
       <c r="C22" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="182">
+      <c r="D22" s="222">
         <f>SUM(D20:E21)</f>
         <v>95421.576412733542</v>
       </c>
-      <c r="E22" s="183"/>
+      <c r="E22" s="233"/>
       <c r="G22" s="62"/>
     </row>
   </sheetData>
@@ -12811,68 +12783,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -12880,27 +12852,27 @@
         <v>181</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -13194,11 +13166,11 @@
       <c r="C20" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="182">
+      <c r="D20" s="222">
         <f>+K18</f>
         <v>84443.872931622609</v>
       </c>
-      <c r="E20" s="182"/>
+      <c r="E20" s="222"/>
       <c r="G20" s="64"/>
       <c r="I20" s="2"/>
       <c r="J20" s="1"/>
@@ -13207,11 +13179,11 @@
       <c r="C21" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D21" s="182">
+      <c r="D21" s="222">
         <f>13%*D20</f>
         <v>10977.703481110939</v>
       </c>
-      <c r="E21" s="182"/>
+      <c r="E21" s="222"/>
       <c r="G21" s="64"/>
       <c r="I21" s="2"/>
       <c r="J21" s="1"/>
@@ -13220,11 +13192,11 @@
       <c r="C22" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="182">
+      <c r="D22" s="222">
         <f>SUM(D20:E21)</f>
         <v>95421.576412733542</v>
       </c>
-      <c r="E22" s="183"/>
+      <c r="E22" s="233"/>
       <c r="G22" s="62"/>
     </row>
   </sheetData>
@@ -13268,60 +13240,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="190" t="s">
+      <c r="A1" s="206" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="190"/>
-      <c r="C1" s="190"/>
-      <c r="D1" s="190"/>
-      <c r="E1" s="190"/>
-      <c r="F1" s="190"/>
-      <c r="G1" s="190"/>
-      <c r="H1" s="190"/>
-      <c r="I1" s="190"/>
-      <c r="J1" s="190"/>
+      <c r="B1" s="206"/>
+      <c r="C1" s="206"/>
+      <c r="D1" s="206"/>
+      <c r="E1" s="206"/>
+      <c r="F1" s="206"/>
+      <c r="G1" s="206"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
     </row>
     <row r="2" spans="1:10" ht="25.5">
-      <c r="A2" s="191" t="s">
+      <c r="A2" s="207" t="s">
         <v>52</v>
       </c>
-      <c r="B2" s="191"/>
-      <c r="C2" s="191"/>
-      <c r="D2" s="191"/>
-      <c r="E2" s="191"/>
-      <c r="F2" s="191"/>
-      <c r="G2" s="191"/>
-      <c r="H2" s="191"/>
-      <c r="I2" s="191"/>
-      <c r="J2" s="191"/>
+      <c r="B2" s="207"/>
+      <c r="C2" s="207"/>
+      <c r="D2" s="207"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="207"/>
+      <c r="I2" s="207"/>
+      <c r="J2" s="207"/>
     </row>
     <row r="3" spans="1:10" ht="18.75">
-      <c r="A3" s="192" t="s">
+      <c r="A3" s="209" t="s">
         <v>53</v>
       </c>
-      <c r="B3" s="192"/>
-      <c r="C3" s="192"/>
-      <c r="D3" s="192"/>
-      <c r="E3" s="192"/>
-      <c r="F3" s="192"/>
-      <c r="G3" s="192"/>
-      <c r="H3" s="192"/>
-      <c r="I3" s="192"/>
-      <c r="J3" s="192"/>
+      <c r="B3" s="209"/>
+      <c r="C3" s="209"/>
+      <c r="D3" s="209"/>
+      <c r="E3" s="209"/>
+      <c r="F3" s="209"/>
+      <c r="G3" s="209"/>
+      <c r="H3" s="209"/>
+      <c r="I3" s="209"/>
+      <c r="J3" s="209"/>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="193" t="s">
+      <c r="A4" s="221" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="193"/>
-      <c r="C4" s="193"/>
-      <c r="D4" s="193"/>
-      <c r="E4" s="193"/>
-      <c r="F4" s="193"/>
-      <c r="G4" s="193"/>
-      <c r="H4" s="193"/>
-      <c r="I4" s="193"/>
-      <c r="J4" s="193"/>
+      <c r="B4" s="221"/>
+      <c r="C4" s="221"/>
+      <c r="D4" s="221"/>
+      <c r="E4" s="221"/>
+      <c r="F4" s="221"/>
+      <c r="G4" s="221"/>
+      <c r="H4" s="221"/>
+      <c r="I4" s="221"/>
+      <c r="J4" s="221"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="37"/>
@@ -13340,33 +13312,33 @@
         <v>55</v>
       </c>
       <c r="B6" s="31"/>
-      <c r="C6" s="194" t="e">
+      <c r="C6" s="210" t="e">
         <f>E51</f>
         <v>#REF!</v>
       </c>
-      <c r="D6" s="195"/>
+      <c r="D6" s="211"/>
       <c r="E6" s="31"/>
       <c r="F6" s="31"/>
       <c r="G6" s="31" t="s">
         <v>56</v>
       </c>
       <c r="H6" s="31"/>
-      <c r="I6" s="194" t="e">
+      <c r="I6" s="210" t="e">
         <f>H51</f>
         <v>#REF!</v>
       </c>
-      <c r="J6" s="195"/>
+      <c r="J6" s="211"/>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="32"/>
       <c r="B7" s="32"/>
-      <c r="C7" s="196"/>
-      <c r="D7" s="196"/>
-      <c r="E7" s="196"/>
-      <c r="F7" s="196"/>
-      <c r="H7" s="197"/>
-      <c r="I7" s="197"/>
-      <c r="J7" s="197"/>
+      <c r="C7" s="201"/>
+      <c r="D7" s="201"/>
+      <c r="E7" s="201"/>
+      <c r="F7" s="201"/>
+      <c r="H7" s="204"/>
+      <c r="I7" s="204"/>
+      <c r="J7" s="204"/>
     </row>
     <row r="8" spans="1:10" ht="16.5">
       <c r="A8" t="s">
@@ -13393,32 +13365,32 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="198" t="s">
+      <c r="A10" s="218" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="198" t="s">
+      <c r="B10" s="218" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="200" t="s">
+      <c r="C10" s="220" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="200"/>
-      <c r="E10" s="200"/>
-      <c r="F10" s="200" t="s">
+      <c r="D10" s="220"/>
+      <c r="E10" s="220"/>
+      <c r="F10" s="220" t="s">
         <v>62</v>
       </c>
-      <c r="G10" s="200"/>
-      <c r="H10" s="200"/>
-      <c r="I10" s="198" t="s">
+      <c r="G10" s="220"/>
+      <c r="H10" s="220"/>
+      <c r="I10" s="218" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="198" t="s">
+      <c r="J10" s="218" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="199"/>
-      <c r="B11" s="199"/>
+      <c r="A11" s="219"/>
+      <c r="B11" s="219"/>
       <c r="C11" s="39" t="s">
         <v>64</v>
       </c>
@@ -13437,8 +13409,8 @@
       <c r="H11" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="I11" s="199"/>
-      <c r="J11" s="199"/>
+      <c r="I11" s="219"/>
+      <c r="J11" s="219"/>
     </row>
     <row r="12" spans="1:10" ht="15.75">
       <c r="A12" s="47">
@@ -14365,6 +14337,12 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="I6:J6"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:J7"/>
@@ -14374,12 +14352,6 @@
     <mergeCell ref="F10:H10"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="J10:J11"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="88" orientation="landscape" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -14416,68 +14388,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -14485,27 +14457,27 @@
         <v>168</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -16381,7 +16353,7 @@
       <c r="K91" s="130"/>
       <c r="L91" s="131"/>
     </row>
-    <row r="92" spans="2:12" ht="66.75">
+    <row r="92" spans="2:12" ht="79.5">
       <c r="B92" s="127">
         <v>11</v>
       </c>
@@ -17663,10 +17635,10 @@
       <c r="C156" s="124" t="s">
         <v>12</v>
       </c>
-      <c r="D156" s="202" t="s">
+      <c r="D156" s="224" t="s">
         <v>71</v>
       </c>
-      <c r="E156" s="202"/>
+      <c r="E156" s="224"/>
       <c r="F156" s="124" t="s">
         <v>72</v>
       </c>
@@ -17676,11 +17648,11 @@
       <c r="C157" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D157" s="182">
+      <c r="D157" s="222">
         <f>+K154</f>
         <v>877810.68270516139</v>
       </c>
-      <c r="E157" s="182"/>
+      <c r="E157" s="222"/>
       <c r="F157" s="152"/>
       <c r="H157" s="64"/>
     </row>
@@ -17688,10 +17660,10 @@
       <c r="C158" s="134" t="s">
         <v>14</v>
       </c>
-      <c r="D158" s="182">
+      <c r="D158" s="222">
         <v>200000</v>
       </c>
-      <c r="E158" s="182"/>
+      <c r="E158" s="222"/>
       <c r="F158" s="153">
         <v>100</v>
       </c>
@@ -17701,11 +17673,11 @@
       <c r="C159" s="134" t="s">
         <v>19</v>
       </c>
-      <c r="D159" s="182">
+      <c r="D159" s="222">
         <f>0.95*D158</f>
         <v>190000</v>
       </c>
-      <c r="E159" s="182"/>
+      <c r="E159" s="222"/>
       <c r="F159" s="153">
         <f>D159/D157*100</f>
         <v>21.644758231293604</v>
@@ -17716,11 +17688,11 @@
       <c r="C160" s="134" t="s">
         <v>15</v>
       </c>
-      <c r="D160" s="182">
+      <c r="D160" s="222">
         <f>D157-D159</f>
         <v>687810.68270516139</v>
       </c>
-      <c r="E160" s="182"/>
+      <c r="E160" s="222"/>
       <c r="F160" s="153">
         <f>D160/D158*100</f>
         <v>343.90534135258071</v>
@@ -17731,11 +17703,11 @@
       <c r="C161" s="134" t="s">
         <v>20</v>
       </c>
-      <c r="D161" s="182">
+      <c r="D161" s="222">
         <f>F161*D158/100</f>
         <v>4000</v>
       </c>
-      <c r="E161" s="182"/>
+      <c r="E161" s="222"/>
       <c r="F161" s="153">
         <v>2</v>
       </c>
@@ -17745,11 +17717,11 @@
       <c r="C162" s="134" t="s">
         <v>21</v>
       </c>
-      <c r="D162" s="201">
+      <c r="D162" s="223">
         <f>F162*D158/100</f>
         <v>6000</v>
       </c>
-      <c r="E162" s="201"/>
+      <c r="E162" s="223"/>
       <c r="F162" s="153">
         <v>3</v>
       </c>
@@ -17760,6 +17732,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="D161:E161"/>
+    <mergeCell ref="D162:E162"/>
+    <mergeCell ref="D156:E156"/>
+    <mergeCell ref="D157:E157"/>
+    <mergeCell ref="D158:E158"/>
+    <mergeCell ref="D159:E159"/>
+    <mergeCell ref="D160:E160"/>
     <mergeCell ref="B6:G6"/>
     <mergeCell ref="I6:L6"/>
     <mergeCell ref="A1:L1"/>
@@ -17767,13 +17746,6 @@
     <mergeCell ref="A3:L3"/>
     <mergeCell ref="A4:L4"/>
     <mergeCell ref="K5:L5"/>
-    <mergeCell ref="D161:E161"/>
-    <mergeCell ref="D162:E162"/>
-    <mergeCell ref="D156:E156"/>
-    <mergeCell ref="D157:E157"/>
-    <mergeCell ref="D158:E158"/>
-    <mergeCell ref="D159:E159"/>
-    <mergeCell ref="D160:E160"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.51181102362204722" right="0.51181102362204722" top="0.39370078740157483" bottom="0.70866141732283472" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -17802,29 +17774,29 @@
       <c r="A1" s="90">
         <v>152</v>
       </c>
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="225" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
     </row>
     <row r="2" spans="1:8" ht="15.75">
       <c r="A2" s="91" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="205" t="s">
+      <c r="B2" s="227" t="s">
         <v>108</v>
       </c>
-      <c r="C2" s="206"/>
-      <c r="D2" s="206"/>
-      <c r="E2" s="206"/>
-      <c r="F2" s="206"/>
-      <c r="G2" s="206"/>
-      <c r="H2" s="206"/>
+      <c r="C2" s="228"/>
+      <c r="D2" s="228"/>
+      <c r="E2" s="228"/>
+      <c r="F2" s="228"/>
+      <c r="G2" s="228"/>
+      <c r="H2" s="228"/>
     </row>
     <row r="3" spans="1:8" ht="31.5">
       <c r="A3" s="92"/>
@@ -17852,7 +17824,7 @@
     </row>
     <row r="4" spans="1:8" ht="16.5">
       <c r="A4" s="92"/>
-      <c r="B4" s="207" t="s">
+      <c r="B4" s="229" t="s">
         <v>116</v>
       </c>
       <c r="C4" s="94" t="s">
@@ -17875,7 +17847,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.5">
       <c r="A5" s="92"/>
-      <c r="B5" s="208"/>
+      <c r="B5" s="230"/>
       <c r="C5" s="99" t="s">
         <v>119</v>
       </c>
@@ -17899,7 +17871,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.5">
       <c r="A6" s="92"/>
-      <c r="B6" s="209" t="s">
+      <c r="B6" s="231" t="s">
         <v>120</v>
       </c>
       <c r="C6" s="96" t="s">
@@ -17923,7 +17895,7 @@
     </row>
     <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="92"/>
-      <c r="B7" s="210"/>
+      <c r="B7" s="232"/>
       <c r="C7" s="99" t="s">
         <v>123</v>
       </c>
@@ -18048,68 +18020,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -18117,27 +18089,27 @@
         <v>173</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -18482,11 +18454,11 @@
       <c r="C22" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="182">
+      <c r="D22" s="222">
         <f>+K20</f>
         <v>152392.78213992011</v>
       </c>
-      <c r="E22" s="182"/>
+      <c r="E22" s="222"/>
       <c r="G22" s="64"/>
       <c r="I22" s="2"/>
       <c r="J22" s="1"/>
@@ -18495,11 +18467,11 @@
       <c r="C23" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D23" s="182">
+      <c r="D23" s="222">
         <f>13%*D22</f>
         <v>19811.061678189613</v>
       </c>
-      <c r="E23" s="182"/>
+      <c r="E23" s="222"/>
       <c r="G23" s="64"/>
       <c r="I23" s="2"/>
       <c r="J23" s="1"/>
@@ -18508,11 +18480,11 @@
       <c r="C24" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="182">
+      <c r="D24" s="222">
         <f>SUM(D22:E23)</f>
         <v>172203.84381810972</v>
       </c>
-      <c r="E24" s="183"/>
+      <c r="E24" s="233"/>
       <c r="G24" s="62"/>
     </row>
   </sheetData>
@@ -18559,68 +18531,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -18628,27 +18600,27 @@
         <v>173</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>174</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -19226,11 +19198,11 @@
       <c r="C32" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D32" s="182">
+      <c r="D32" s="222">
         <f>+K30</f>
         <v>136152.90338529783</v>
       </c>
-      <c r="E32" s="182"/>
+      <c r="E32" s="222"/>
       <c r="G32" s="64"/>
       <c r="I32" s="2"/>
       <c r="J32" s="1"/>
@@ -19239,11 +19211,11 @@
       <c r="C33" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D33" s="182">
+      <c r="D33" s="222">
         <f>13%*D32</f>
         <v>17699.87744008872</v>
       </c>
-      <c r="E33" s="182"/>
+      <c r="E33" s="222"/>
       <c r="G33" s="64"/>
       <c r="I33" s="2"/>
       <c r="J33" s="1"/>
@@ -19252,11 +19224,11 @@
       <c r="C34" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D34" s="182">
+      <c r="D34" s="222">
         <f>SUM(D32:E33)</f>
         <v>153852.78082538655</v>
       </c>
-      <c r="E34" s="183"/>
+      <c r="E34" s="233"/>
       <c r="G34" s="62"/>
     </row>
   </sheetData>
@@ -19302,68 +19274,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -19371,27 +19343,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -19607,11 +19579,11 @@
       <c r="C17" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="182">
+      <c r="D17" s="222">
         <f>+K15</f>
         <v>82403.803018409788</v>
       </c>
-      <c r="E17" s="182"/>
+      <c r="E17" s="222"/>
       <c r="G17" s="64"/>
       <c r="I17" s="2"/>
       <c r="J17" s="1"/>
@@ -19620,11 +19592,11 @@
       <c r="C18" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D18" s="182">
+      <c r="D18" s="222">
         <f>13%*D17</f>
         <v>10712.494392393273</v>
       </c>
-      <c r="E18" s="182"/>
+      <c r="E18" s="222"/>
       <c r="G18" s="64"/>
       <c r="I18" s="2"/>
       <c r="J18" s="1"/>
@@ -19633,11 +19605,11 @@
       <c r="C19" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D19" s="182">
+      <c r="D19" s="222">
         <f>SUM(D17:E18)</f>
         <v>93116.297410803061</v>
       </c>
-      <c r="E19" s="183"/>
+      <c r="E19" s="233"/>
       <c r="G19" s="62"/>
     </row>
   </sheetData>
@@ -19684,68 +19656,68 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="184" t="s">
+      <c r="A1" s="214" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="184"/>
-      <c r="C1" s="184"/>
-      <c r="D1" s="184"/>
-      <c r="E1" s="184"/>
-      <c r="F1" s="184"/>
-      <c r="G1" s="184"/>
-      <c r="H1" s="184"/>
-      <c r="I1" s="184"/>
-      <c r="J1" s="184"/>
-      <c r="K1" s="184"/>
-      <c r="L1" s="184"/>
+      <c r="B1" s="214"/>
+      <c r="C1" s="214"/>
+      <c r="D1" s="214"/>
+      <c r="E1" s="214"/>
+      <c r="F1" s="214"/>
+      <c r="G1" s="214"/>
+      <c r="H1" s="214"/>
+      <c r="I1" s="214"/>
+      <c r="J1" s="214"/>
+      <c r="K1" s="214"/>
+      <c r="L1" s="214"/>
     </row>
     <row r="2" spans="1:12" ht="20.25">
-      <c r="A2" s="185" t="s">
+      <c r="A2" s="215" t="s">
         <v>16</v>
       </c>
-      <c r="B2" s="185"/>
-      <c r="C2" s="185"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="185"/>
-      <c r="F2" s="185"/>
-      <c r="G2" s="185"/>
-      <c r="H2" s="185"/>
-      <c r="I2" s="185"/>
-      <c r="J2" s="185"/>
-      <c r="K2" s="185"/>
-      <c r="L2" s="185"/>
+      <c r="B2" s="215"/>
+      <c r="C2" s="215"/>
+      <c r="D2" s="215"/>
+      <c r="E2" s="215"/>
+      <c r="F2" s="215"/>
+      <c r="G2" s="215"/>
+      <c r="H2" s="215"/>
+      <c r="I2" s="215"/>
+      <c r="J2" s="215"/>
+      <c r="K2" s="215"/>
+      <c r="L2" s="215"/>
     </row>
     <row r="3" spans="1:12">
-      <c r="A3" s="184" t="s">
+      <c r="A3" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="184"/>
-      <c r="C3" s="184"/>
-      <c r="D3" s="184"/>
-      <c r="E3" s="184"/>
-      <c r="F3" s="184"/>
-      <c r="G3" s="184"/>
-      <c r="H3" s="184"/>
-      <c r="I3" s="184"/>
-      <c r="J3" s="184"/>
-      <c r="K3" s="184"/>
-      <c r="L3" s="184"/>
+      <c r="B3" s="214"/>
+      <c r="C3" s="214"/>
+      <c r="D3" s="214"/>
+      <c r="E3" s="214"/>
+      <c r="F3" s="214"/>
+      <c r="G3" s="214"/>
+      <c r="H3" s="214"/>
+      <c r="I3" s="214"/>
+      <c r="J3" s="214"/>
+      <c r="K3" s="214"/>
+      <c r="L3" s="214"/>
     </row>
     <row r="4" spans="1:12">
-      <c r="A4" s="186" t="s">
+      <c r="A4" s="216" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="186"/>
-      <c r="C4" s="186"/>
-      <c r="D4" s="186"/>
-      <c r="E4" s="186"/>
-      <c r="F4" s="186"/>
-      <c r="G4" s="186"/>
-      <c r="H4" s="186"/>
-      <c r="I4" s="186"/>
-      <c r="J4" s="186"/>
-      <c r="K4" s="186"/>
-      <c r="L4" s="186"/>
+      <c r="B4" s="216"/>
+      <c r="C4" s="216"/>
+      <c r="D4" s="216"/>
+      <c r="E4" s="216"/>
+      <c r="F4" s="216"/>
+      <c r="G4" s="216"/>
+      <c r="H4" s="216"/>
+      <c r="I4" s="216"/>
+      <c r="J4" s="216"/>
+      <c r="K4" s="216"/>
+      <c r="L4" s="216"/>
     </row>
     <row r="5" spans="1:12" ht="20.25">
       <c r="A5" s="6"/>
@@ -19753,27 +19725,27 @@
         <v>180</v>
       </c>
       <c r="H5" s="6"/>
-      <c r="K5" s="187" t="s">
+      <c r="K5" s="217" t="s">
         <v>101</v>
       </c>
-      <c r="L5" s="187"/>
+      <c r="L5" s="217"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="B6" s="188" t="s">
+      <c r="B6" s="213" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="188"/>
-      <c r="D6" s="188"/>
-      <c r="E6" s="188"/>
-      <c r="F6" s="188"/>
-      <c r="G6" s="188"/>
+      <c r="C6" s="213"/>
+      <c r="D6" s="213"/>
+      <c r="E6" s="213"/>
+      <c r="F6" s="213"/>
+      <c r="G6" s="213"/>
       <c r="H6" s="113"/>
-      <c r="I6" s="189" t="s">
+      <c r="I6" s="212" t="s">
         <v>182</v>
       </c>
-      <c r="J6" s="189"/>
-      <c r="K6" s="189"/>
-      <c r="L6" s="189"/>
+      <c r="J6" s="212"/>
+      <c r="K6" s="212"/>
+      <c r="L6" s="212"/>
     </row>
     <row r="7" spans="1:12">
       <c r="C7" s="5"/>
@@ -20424,11 +20396,11 @@
       <c r="C37" s="134" t="s">
         <v>13</v>
       </c>
-      <c r="D37" s="182">
+      <c r="D37" s="222">
         <f>+K35</f>
         <v>56595.388680275566</v>
       </c>
-      <c r="E37" s="182"/>
+      <c r="E37" s="222"/>
       <c r="G37" s="64"/>
       <c r="I37" s="2"/>
       <c r="J37" s="1"/>
@@ -20437,11 +20409,11 @@
       <c r="C38" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="D38" s="182">
+      <c r="D38" s="222">
         <f>13%*D37</f>
         <v>7357.4005284358236</v>
       </c>
-      <c r="E38" s="182"/>
+      <c r="E38" s="222"/>
       <c r="G38" s="64"/>
       <c r="I38" s="2"/>
       <c r="J38" s="1"/>
@@ -20450,11 +20422,11 @@
       <c r="C39" s="151" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="182">
+      <c r="D39" s="222">
         <f>SUM(D37:E38)</f>
         <v>63952.789208711387</v>
       </c>
-      <c r="E39" s="183"/>
+      <c r="E39" s="233"/>
       <c r="G39" s="62"/>
     </row>
   </sheetData>
@@ -20494,41 +20466,41 @@
         <f>#REF!+1</f>
         <v>#REF!</v>
       </c>
-      <c r="B1" s="203" t="s">
+      <c r="B1" s="225" t="s">
         <v>183</v>
       </c>
-      <c r="C1" s="204"/>
-      <c r="D1" s="204"/>
-      <c r="E1" s="204"/>
-      <c r="F1" s="204"/>
-      <c r="G1" s="204"/>
-      <c r="H1" s="204"/>
+      <c r="C1" s="226"/>
+      <c r="D1" s="226"/>
+      <c r="E1" s="226"/>
+      <c r="F1" s="226"/>
+      <c r="G1" s="226"/>
+      <c r="H1" s="226"/>
     </row>
     <row r="2" spans="1:8" ht="19.5">
       <c r="A2" s="170" t="s">
         <v>184</v>
       </c>
-      <c r="B2" s="203" t="s">
+      <c r="B2" s="225" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="204"/>
-      <c r="D2" s="204"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="204"/>
+      <c r="C2" s="226"/>
+      <c r="D2" s="226"/>
+      <c r="E2" s="226"/>
+      <c r="F2" s="226"/>
+      <c r="G2" s="226"/>
+      <c r="H2" s="226"/>
     </row>
     <row r="3" spans="1:8" ht="15.75">
       <c r="A3" s="92"/>
-      <c r="B3" s="206" t="s">
+      <c r="B3" s="228" t="s">
         <v>185</v>
       </c>
-      <c r="C3" s="206"/>
-      <c r="D3" s="206"/>
-      <c r="E3" s="206"/>
-      <c r="F3" s="206"/>
-      <c r="G3" s="206"/>
-      <c r="H3" s="206"/>
+      <c r="C3" s="228"/>
+      <c r="D3" s="228"/>
+      <c r="E3" s="228"/>
+      <c r="F3" s="228"/>
+      <c r="G3" s="228"/>
+      <c r="H3" s="228"/>
     </row>
     <row r="4" spans="1:8" ht="63">
       <c r="A4" s="92"/>
@@ -20556,7 +20528,7 @@
     </row>
     <row r="5" spans="1:8" ht="16.5">
       <c r="A5" s="92"/>
-      <c r="B5" s="207" t="s">
+      <c r="B5" s="229" t="s">
         <v>116</v>
       </c>
       <c r="C5" s="94" t="s">
@@ -20579,7 +20551,7 @@
     </row>
     <row r="6" spans="1:8" ht="16.5">
       <c r="A6" s="92"/>
-      <c r="B6" s="211"/>
+      <c r="B6" s="234"/>
       <c r="C6" s="99" t="s">
         <v>119</v>
       </c>
@@ -20603,7 +20575,7 @@
     </row>
     <row r="7" spans="1:8" ht="16.5">
       <c r="A7" s="92"/>
-      <c r="B7" s="209" t="s">
+      <c r="B7" s="231" t="s">
         <v>120</v>
       </c>
       <c r="C7" s="96" t="s">
@@ -20626,7 +20598,7 @@
     </row>
     <row r="8" spans="1:8" ht="16.5">
       <c r="A8" s="92"/>
-      <c r="B8" s="212"/>
+      <c r="B8" s="235"/>
       <c r="C8" s="163" t="s">
         <v>196</v>
       </c>
@@ -20647,7 +20619,7 @@
     </row>
     <row r="9" spans="1:8" ht="16.5">
       <c r="A9" s="92"/>
-      <c r="B9" s="212"/>
+      <c r="B9" s="235"/>
       <c r="C9" s="163" t="s">
         <v>188</v>
       </c>
@@ -20668,7 +20640,7 @@
     </row>
     <row r="10" spans="1:8" ht="16.5">
       <c r="A10" s="92"/>
-      <c r="B10" s="212"/>
+      <c r="B10" s="235"/>
       <c r="C10" s="163" t="s">
         <v>189</v>
       </c>
@@ -20689,7 +20661,7 @@
     </row>
     <row r="11" spans="1:8" ht="16.5">
       <c r="A11" s="92"/>
-      <c r="B11" s="212"/>
+      <c r="B11" s="235"/>
       <c r="C11" s="163" t="s">
         <v>190</v>
       </c>
@@ -20710,7 +20682,7 @@
     </row>
     <row r="12" spans="1:8" ht="16.5">
       <c r="A12" s="92"/>
-      <c r="B12" s="210"/>
+      <c r="B12" s="232"/>
       <c r="C12" s="99" t="s">
         <v>191</v>
       </c>
